--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="81">
   <si>
     <t>Date</t>
   </si>
@@ -256,14 +256,21 @@
   </si>
   <si>
     <t>168.80</t>
+  </si>
+  <si>
+    <t>Area (ha)</t>
+  </si>
+  <si>
+    <t>TCH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -314,12 +321,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,13 +631,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -639,16 +649,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45376</v>
       </c>
@@ -658,14 +674,21 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
+        <v>19.686</v>
+      </c>
+      <c r="E2" s="4">
+        <v>95</v>
+      </c>
+      <c r="F2">
         <v>1870.17</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45376</v>
       </c>
@@ -675,14 +698,21 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
+        <v>9.1349999999999998</v>
+      </c>
+      <c r="E3" s="4">
+        <v>70</v>
+      </c>
+      <c r="F3">
         <v>639.44999999999993</v>
       </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45376</v>
       </c>
@@ -692,14 +722,21 @@
       <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="E4" s="4">
+        <v>82</v>
+      </c>
+      <c r="F4">
         <v>926.6</v>
       </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45376</v>
       </c>
@@ -709,14 +746,21 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
+        <v>16.341999999999999</v>
+      </c>
+      <c r="E5" s="4">
+        <v>34.08701505323706</v>
+      </c>
+      <c r="F5">
         <v>557.04999999999995</v>
       </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45376</v>
       </c>
@@ -726,14 +770,21 @@
       <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
+        <v>17.327999999999999</v>
+      </c>
+      <c r="E6" s="4">
+        <v>85.000000000000014</v>
+      </c>
+      <c r="F6">
         <v>1472.88</v>
       </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45376</v>
       </c>
@@ -743,14 +794,21 @@
       <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
+        <v>15.696999999999999</v>
+      </c>
+      <c r="E7" s="4">
+        <v>93.438555137924439</v>
+      </c>
+      <c r="F7">
         <v>1466.7049999999999</v>
       </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45376</v>
       </c>
@@ -760,14 +818,21 @@
       <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
+        <v>19.280999999999999</v>
+      </c>
+      <c r="E8" s="4">
+        <v>84.529329391629062</v>
+      </c>
+      <c r="F8">
         <v>1629.81</v>
       </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45376</v>
       </c>
@@ -777,14 +842,21 @@
       <c r="C9" t="s">
         <v>12</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="3">
+        <v>17.605</v>
+      </c>
+      <c r="E9" s="4">
+        <v>77.814257313263283</v>
+      </c>
+      <c r="F9">
         <v>1369.92</v>
       </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45376</v>
       </c>
@@ -794,14 +866,21 @@
       <c r="C10" t="s">
         <v>10</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
+        <v>31.706</v>
+      </c>
+      <c r="E10" s="4">
+        <v>75</v>
+      </c>
+      <c r="F10">
         <v>2377.9499999999998</v>
       </c>
-      <c r="F10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45376</v>
       </c>
@@ -811,14 +890,21 @@
       <c r="C11" t="s">
         <v>7</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="3">
+        <v>21.465</v>
+      </c>
+      <c r="E11" s="4">
+        <v>70</v>
+      </c>
+      <c r="F11">
         <v>1502.55</v>
       </c>
-      <c r="F11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45376</v>
       </c>
@@ -828,14 +914,21 @@
       <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
+        <v>42.033000000000001</v>
+      </c>
+      <c r="E12" s="4">
+        <v>90.000000000000028</v>
+      </c>
+      <c r="F12">
         <v>3782.9700000000012</v>
       </c>
-      <c r="F12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45376</v>
       </c>
@@ -845,14 +938,21 @@
       <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
+        <v>23.658000000000001</v>
+      </c>
+      <c r="E13" s="4">
+        <v>74.999999999999986</v>
+      </c>
+      <c r="F13">
         <v>1774.35</v>
       </c>
-      <c r="F13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45376</v>
       </c>
@@ -862,14 +962,21 @@
       <c r="C14" t="s">
         <v>12</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="3">
+        <v>35.624000000000002</v>
+      </c>
+      <c r="E14" s="4">
+        <v>92.407927240062875</v>
+      </c>
+      <c r="F14">
         <v>3291.94</v>
       </c>
-      <c r="F14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45376</v>
       </c>
@@ -879,14 +986,21 @@
       <c r="C15" t="s">
         <v>12</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="3">
+        <v>14.504</v>
+      </c>
+      <c r="E15" s="4">
+        <v>50.000000000000007</v>
+      </c>
+      <c r="F15">
         <v>725.2</v>
       </c>
-      <c r="F15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45376</v>
       </c>
@@ -896,14 +1010,21 @@
       <c r="C16" t="s">
         <v>10</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="3">
+        <v>25.122</v>
+      </c>
+      <c r="E16" s="4">
+        <v>13.888225459756388</v>
+      </c>
+      <c r="F16">
         <v>348.9</v>
       </c>
-      <c r="F16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45376</v>
       </c>
@@ -913,14 +1034,21 @@
       <c r="C17" t="s">
         <v>18</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="3">
+        <v>4.1950000000000003</v>
+      </c>
+      <c r="E17" s="4">
+        <v>84.999999999999986</v>
+      </c>
+      <c r="F17">
         <v>356.57499999999999</v>
       </c>
-      <c r="F17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45376</v>
       </c>
@@ -930,14 +1058,21 @@
       <c r="C18" t="s">
         <v>14</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="3">
+        <v>16.079000000000001</v>
+      </c>
+      <c r="E18" s="4">
+        <v>60</v>
+      </c>
+      <c r="F18">
         <v>964.74</v>
       </c>
-      <c r="F18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45376</v>
       </c>
@@ -947,14 +1082,21 @@
       <c r="C19" t="s">
         <v>14</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="3">
+        <v>14.065</v>
+      </c>
+      <c r="E19" s="4">
+        <v>90</v>
+      </c>
+      <c r="F19">
         <v>1265.8499999999999</v>
       </c>
-      <c r="F19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>45376</v>
       </c>
@@ -964,14 +1106,21 @@
       <c r="C20" t="s">
         <v>12</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="3">
+        <v>16.888999999999999</v>
+      </c>
+      <c r="E20" s="4">
+        <v>70</v>
+      </c>
+      <c r="F20">
         <v>1182.23</v>
       </c>
-      <c r="F20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="4"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>45376</v>
       </c>
@@ -981,14 +1130,21 @@
       <c r="C21" t="s">
         <v>10</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
+        <v>23.146999999999998</v>
+      </c>
+      <c r="E21" s="4">
+        <v>70</v>
+      </c>
+      <c r="F21">
         <v>1620.29</v>
       </c>
-      <c r="F21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H21" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="4"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>45376</v>
       </c>
@@ -998,14 +1154,21 @@
       <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="3">
+        <v>18.552</v>
+      </c>
+      <c r="E22" s="4">
+        <v>59.999999999999993</v>
+      </c>
+      <c r="F22">
         <v>1113.1199999999999</v>
       </c>
-      <c r="F22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H22" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="4"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>45376</v>
       </c>
@@ -1015,14 +1178,21 @@
       <c r="C23" t="s">
         <v>14</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="3">
+        <v>24.803999999999998</v>
+      </c>
+      <c r="E23" s="4">
+        <v>90.000000000000014</v>
+      </c>
+      <c r="F23">
         <v>2232.36</v>
       </c>
-      <c r="F23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="4"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>45376</v>
       </c>
@@ -1032,14 +1202,21 @@
       <c r="C24" t="s">
         <v>12</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="3">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E24" s="4">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="F24">
         <v>1053.25</v>
       </c>
-      <c r="F24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H24" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="4"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45376</v>
       </c>
@@ -1049,14 +1226,21 @@
       <c r="C25" t="s">
         <v>14</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="3">
+        <v>25.193000000000001</v>
+      </c>
+      <c r="E25" s="4">
+        <v>81.626046917794625</v>
+      </c>
+      <c r="F25">
         <v>2056.4050000000002</v>
       </c>
-      <c r="F25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H25" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="4"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>45376</v>
       </c>
@@ -1066,14 +1250,21 @@
       <c r="C26" t="s">
         <v>12</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="3">
+        <v>18.324999999999999</v>
+      </c>
+      <c r="E26" s="4">
+        <v>80</v>
+      </c>
+      <c r="F26">
         <v>1466</v>
       </c>
-      <c r="F26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H26" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="4"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>45376</v>
       </c>
@@ -1083,14 +1274,21 @@
       <c r="C27" t="s">
         <v>10</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="3">
+        <v>24.106999999999999</v>
+      </c>
+      <c r="E27" s="4">
+        <v>75</v>
+      </c>
+      <c r="F27">
         <v>1808.0250000000001</v>
       </c>
-      <c r="F27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H27" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="4"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>45376</v>
       </c>
@@ -1100,14 +1298,21 @@
       <c r="C28" t="s">
         <v>14</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="3">
+        <v>13.993</v>
+      </c>
+      <c r="E28" s="4">
+        <v>89.999999999999986</v>
+      </c>
+      <c r="F28">
         <v>1259.3699999999999</v>
       </c>
-      <c r="F28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M28" s="4"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>45376</v>
       </c>
@@ -1117,14 +1322,21 @@
       <c r="C29" t="s">
         <v>12</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="3">
+        <v>23.161999999999999</v>
+      </c>
+      <c r="E29" s="4">
+        <v>50</v>
+      </c>
+      <c r="F29">
         <v>1158.0999999999999</v>
       </c>
-      <c r="F29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H29" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="4"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>45376</v>
       </c>
@@ -1134,14 +1346,21 @@
       <c r="C30" t="s">
         <v>12</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="3">
+        <v>8.423</v>
+      </c>
+      <c r="E30" s="4">
+        <v>95.139498990858371</v>
+      </c>
+      <c r="F30">
         <v>801.36</v>
       </c>
-      <c r="F30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H30" t="s">
+        <v>8</v>
+      </c>
+      <c r="M30" s="4"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>45376</v>
       </c>
@@ -1151,14 +1370,21 @@
       <c r="C31" t="s">
         <v>12</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="3">
+        <v>21.858000000000001</v>
+      </c>
+      <c r="E31" s="4">
+        <v>43.043736846921036</v>
+      </c>
+      <c r="F31">
         <v>940.85</v>
       </c>
-      <c r="F31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H31" t="s">
+        <v>8</v>
+      </c>
+      <c r="M31" s="4"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>45376</v>
       </c>
@@ -1168,14 +1394,21 @@
       <c r="C32" t="s">
         <v>14</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="3">
+        <v>25.047000000000001</v>
+      </c>
+      <c r="E32" s="4">
+        <v>90</v>
+      </c>
+      <c r="F32">
         <v>2254.23</v>
       </c>
-      <c r="F32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H32" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="4"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>45376</v>
       </c>
@@ -1185,14 +1418,21 @@
       <c r="C33" t="s">
         <v>14</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="3">
+        <v>21.138000000000002</v>
+      </c>
+      <c r="E33" s="4">
+        <v>70</v>
+      </c>
+      <c r="F33">
         <v>1479.66</v>
       </c>
-      <c r="F33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="4"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>45376</v>
       </c>
@@ -1202,14 +1442,21 @@
       <c r="C34" t="s">
         <v>10</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="3">
+        <v>24.542999999999999</v>
+      </c>
+      <c r="E34" s="4">
+        <v>80</v>
+      </c>
+      <c r="F34">
         <v>1963.44</v>
       </c>
-      <c r="F34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H34" t="s">
+        <v>8</v>
+      </c>
+      <c r="M34" s="4"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>45376</v>
       </c>
@@ -1219,14 +1466,21 @@
       <c r="C35" t="s">
         <v>14</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="3">
+        <v>12.795999999999999</v>
+      </c>
+      <c r="E35" s="4">
+        <v>78.780869021569245</v>
+      </c>
+      <c r="F35">
         <v>1008.08</v>
       </c>
-      <c r="F35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H35" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="4"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>45376</v>
       </c>
@@ -1236,14 +1490,21 @@
       <c r="C36" t="s">
         <v>12</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="3">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="E36" s="4">
+        <v>60</v>
+      </c>
+      <c r="F36">
         <v>586.79999999999995</v>
       </c>
-      <c r="F36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H36" t="s">
+        <v>8</v>
+      </c>
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>45376</v>
       </c>
@@ -1253,14 +1514,21 @@
       <c r="C37" t="s">
         <v>10</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="3">
+        <v>11.125</v>
+      </c>
+      <c r="E37" s="4">
+        <v>80</v>
+      </c>
+      <c r="F37">
         <v>890</v>
       </c>
-      <c r="F37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H37" t="s">
+        <v>8</v>
+      </c>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>45376</v>
       </c>
@@ -1270,14 +1538,21 @@
       <c r="C38" t="s">
         <v>10</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="3">
+        <v>10.439</v>
+      </c>
+      <c r="E38" s="4">
+        <v>90</v>
+      </c>
+      <c r="F38">
         <v>939.51</v>
       </c>
-      <c r="F38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H38" t="s">
+        <v>8</v>
+      </c>
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>45376</v>
       </c>
@@ -1287,14 +1562,21 @@
       <c r="C39" t="s">
         <v>10</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="3">
+        <v>7.1740000000000004</v>
+      </c>
+      <c r="E39" s="4">
+        <v>89.999999999999986</v>
+      </c>
+      <c r="F39">
         <v>645.66</v>
       </c>
-      <c r="F39" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H39" t="s">
+        <v>8</v>
+      </c>
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>45376</v>
       </c>
@@ -1304,14 +1586,21 @@
       <c r="C40" t="s">
         <v>12</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="3">
+        <v>8.7379999999999995</v>
+      </c>
+      <c r="E40" s="4">
+        <v>65</v>
+      </c>
+      <c r="F40">
         <v>567.97</v>
       </c>
-      <c r="F40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H40" t="s">
+        <v>8</v>
+      </c>
+      <c r="M40" s="4"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>45376</v>
       </c>
@@ -1321,14 +1610,21 @@
       <c r="C41" t="s">
         <v>14</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="3">
+        <v>13.321</v>
+      </c>
+      <c r="E41" s="4">
+        <v>54.999999999999993</v>
+      </c>
+      <c r="F41">
         <v>732.65499999999986</v>
       </c>
-      <c r="F41" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H41" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>45376</v>
       </c>
@@ -1338,14 +1634,21 @@
       <c r="C42" t="s">
         <v>12</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="3">
+        <v>18.931000000000001</v>
+      </c>
+      <c r="E42" s="4">
+        <v>45</v>
+      </c>
+      <c r="F42">
         <v>851.8950000000001</v>
       </c>
-      <c r="F42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M42" s="4"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>45376</v>
       </c>
@@ -1355,14 +1658,21 @@
       <c r="C43" t="s">
         <v>14</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="H43" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>45376</v>
       </c>
@@ -1372,14 +1682,21 @@
       <c r="C44" t="s">
         <v>14</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="3">
+        <v>25.213999999999999</v>
+      </c>
+      <c r="E44" s="4">
+        <v>35.339097326881884</v>
+      </c>
+      <c r="F44">
         <v>891.03999999999985</v>
       </c>
-      <c r="F44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H44" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45376</v>
       </c>
@@ -1389,14 +1706,21 @@
       <c r="C45" t="s">
         <v>14</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="3">
+        <v>7.4450000000000003</v>
+      </c>
+      <c r="E45" s="4">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="F45">
         <v>335.02499999999998</v>
       </c>
-      <c r="F45" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H45" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45376</v>
       </c>
@@ -1406,14 +1730,21 @@
       <c r="C46" t="s">
         <v>14</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="E46" s="4">
+        <v>56.480314960629926</v>
+      </c>
+      <c r="F46">
         <v>71.73</v>
       </c>
-      <c r="F46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H46" t="s">
+        <v>8</v>
+      </c>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>45376</v>
       </c>
@@ -1423,28 +1754,42 @@
       <c r="C47" t="s">
         <v>14</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="3">
+        <v>2.8849999999999998</v>
+      </c>
+      <c r="E47" s="4">
+        <v>30</v>
+      </c>
+      <c r="F47">
         <v>86.55</v>
       </c>
-      <c r="F47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H47" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45376</v>
       </c>
       <c r="B48" t="s">
         <v>59</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="3">
         <v>0</v>
       </c>
-      <c r="F48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E48" s="4">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="H48" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="4"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>45376</v>
       </c>
@@ -1454,14 +1799,21 @@
       <c r="C49" t="s">
         <v>14</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="3">
+        <v>15.798</v>
+      </c>
+      <c r="E49" s="4">
+        <v>34.538549183440942</v>
+      </c>
+      <c r="F49">
         <v>545.64</v>
       </c>
-      <c r="F49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H49" t="s">
+        <v>8</v>
+      </c>
+      <c r="M49" s="4"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>45376</v>
       </c>
@@ -1471,14 +1823,21 @@
       <c r="C50" t="s">
         <v>14</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="3">
+        <v>5.3449999999999998</v>
+      </c>
+      <c r="E50" s="4">
+        <v>24.658559401309638</v>
+      </c>
+      <c r="F50">
         <v>131.80000000000001</v>
       </c>
-      <c r="F50" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H50" t="s">
+        <v>8</v>
+      </c>
+      <c r="M50" s="4"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>45376</v>
       </c>
@@ -1488,28 +1847,42 @@
       <c r="C51" t="s">
         <v>12</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="3">
+        <v>4.0940000000000003</v>
+      </c>
+      <c r="E51" s="4">
+        <v>47.936003908158277</v>
+      </c>
+      <c r="F51">
         <v>196.25</v>
       </c>
-      <c r="F51" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H51" t="s">
+        <v>8</v>
+      </c>
+      <c r="M51" s="4"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>45376</v>
       </c>
       <c r="B52" t="s">
         <v>63</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="3">
         <v>0</v>
       </c>
-      <c r="F52" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E52" s="4">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="H52" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="4"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>45376</v>
       </c>
@@ -1519,14 +1892,21 @@
       <c r="C53" t="s">
         <v>12</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="3">
+        <v>3.07</v>
+      </c>
+      <c r="E53" s="4">
+        <v>48.371335504885998</v>
+      </c>
+      <c r="F53">
         <v>148.5</v>
       </c>
-      <c r="F53" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H53" t="s">
+        <v>8</v>
+      </c>
+      <c r="M53" s="4"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>45736</v>
       </c>
@@ -1536,17 +1916,24 @@
       <c r="C54" t="s">
         <v>7</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="3">
+        <v>19.686</v>
+      </c>
+      <c r="E54" s="4">
+        <v>105.00000000000001</v>
+      </c>
+      <c r="F54">
         <v>2067.0300000000002</v>
       </c>
-      <c r="E54" t="s">
+      <c r="G54" t="s">
         <v>65</v>
       </c>
-      <c r="F54" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H54" t="s">
+        <v>66</v>
+      </c>
+      <c r="M54" s="4"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>45736</v>
       </c>
@@ -1556,17 +1943,24 @@
       <c r="C55" t="s">
         <v>18</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="3">
+        <v>9.1349999999999998</v>
+      </c>
+      <c r="E55" s="4">
+        <v>88</v>
+      </c>
+      <c r="F55">
         <v>803.88</v>
       </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>67</v>
       </c>
-      <c r="F55" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H55" t="s">
+        <v>66</v>
+      </c>
+      <c r="M55" s="4"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>45736</v>
       </c>
@@ -1576,17 +1970,24 @@
       <c r="C56" t="s">
         <v>12</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="E56" s="4">
+        <v>89.899999999999991</v>
+      </c>
+      <c r="F56">
         <v>1015.87</v>
       </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
         <v>68</v>
       </c>
-      <c r="F56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H56" t="s">
+        <v>66</v>
+      </c>
+      <c r="M56" s="4"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>45736</v>
       </c>
@@ -1596,17 +1997,24 @@
       <c r="C57" t="s">
         <v>14</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="3">
+        <v>10.141</v>
+      </c>
+      <c r="E57" s="4">
+        <v>89.925056700522632</v>
+      </c>
+      <c r="F57">
         <v>911.93</v>
       </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>69</v>
       </c>
-      <c r="F57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H57" t="s">
+        <v>66</v>
+      </c>
+      <c r="M57" s="4"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>45736</v>
       </c>
@@ -1616,17 +2024,24 @@
       <c r="C58" t="s">
         <v>10</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="3">
+        <v>17.327999999999999</v>
+      </c>
+      <c r="E58" s="4">
+        <v>96.000115420129276</v>
+      </c>
+      <c r="F58">
         <v>1663.49</v>
       </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>65</v>
       </c>
-      <c r="F58" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H58" t="s">
+        <v>66</v>
+      </c>
+      <c r="M58" s="4"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>70</v>
       </c>
@@ -1636,14 +2051,21 @@
       <c r="C59" t="s">
         <v>12</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="3">
+        <v>15.439</v>
+      </c>
+      <c r="E59" s="4">
+        <v>97.999870457931209</v>
+      </c>
+      <c r="F59">
         <v>1513.02</v>
       </c>
-      <c r="F59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H59" t="s">
+        <v>66</v>
+      </c>
+      <c r="M59" s="4"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -1653,17 +2075,24 @@
       <c r="C60" t="s">
         <v>18</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="3">
+        <v>18.895</v>
+      </c>
+      <c r="E60" s="4">
+        <v>90</v>
+      </c>
+      <c r="F60">
         <v>1700.55</v>
       </c>
-      <c r="E60" t="s">
+      <c r="G60" t="s">
         <v>71</v>
       </c>
-      <c r="F60" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H60" t="s">
+        <v>66</v>
+      </c>
+      <c r="M60" s="4"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -1673,14 +2102,21 @@
       <c r="C61" t="s">
         <v>12</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="3">
+        <v>17.123999999999999</v>
+      </c>
+      <c r="E61" s="4">
+        <v>90.000000000000014</v>
+      </c>
+      <c r="F61">
         <v>1541.16</v>
       </c>
-      <c r="F61" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H61" t="s">
+        <v>66</v>
+      </c>
+      <c r="M61" s="4"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1690,14 +2126,21 @@
       <c r="C62" t="s">
         <v>10</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="3">
+        <v>31.706</v>
+      </c>
+      <c r="E62" s="4">
+        <v>90</v>
+      </c>
+      <c r="F62">
         <v>2853.54</v>
       </c>
-      <c r="F62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H62" t="s">
+        <v>66</v>
+      </c>
+      <c r="M62" s="4"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -1707,14 +2150,21 @@
       <c r="C63" t="s">
         <v>7</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="3">
+        <v>21.465</v>
+      </c>
+      <c r="E63" s="4">
+        <v>85.00023293733986</v>
+      </c>
+      <c r="F63">
         <v>1824.53</v>
       </c>
-      <c r="F63" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H63" t="s">
+        <v>66</v>
+      </c>
+      <c r="M63" s="4"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>70</v>
       </c>
@@ -1724,14 +2174,21 @@
       <c r="C64" t="s">
         <v>23</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="3">
+        <v>42.033000000000001</v>
+      </c>
+      <c r="E64" s="4">
+        <v>105.00011895415507</v>
+      </c>
+      <c r="F64">
         <v>4413.47</v>
       </c>
-      <c r="F64" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H64" t="s">
+        <v>66</v>
+      </c>
+      <c r="M64" s="4"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -1741,14 +2198,21 @@
       <c r="C65" t="s">
         <v>7</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="3">
+        <v>23.658000000000001</v>
+      </c>
+      <c r="E65" s="4">
+        <v>80</v>
+      </c>
+      <c r="F65">
         <v>1892.64</v>
       </c>
-      <c r="F65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H65" t="s">
+        <v>66</v>
+      </c>
+      <c r="M65" s="4"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -1758,17 +2222,24 @@
       <c r="C66" t="s">
         <v>12</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="3">
+        <v>34.652000000000001</v>
+      </c>
+      <c r="E66" s="4">
+        <v>99.999999999999986</v>
+      </c>
+      <c r="F66">
         <v>3465.2</v>
       </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>71</v>
       </c>
-      <c r="F66" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H66" t="s">
+        <v>66</v>
+      </c>
+      <c r="M66" s="4"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -1778,14 +2249,21 @@
       <c r="C67" t="s">
         <v>12</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="3">
+        <v>14.504</v>
+      </c>
+      <c r="E67" s="4">
+        <v>62.000137892995035</v>
+      </c>
+      <c r="F67">
         <v>899.25</v>
       </c>
-      <c r="F67" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H67" t="s">
+        <v>66</v>
+      </c>
+      <c r="M67" s="4"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -1795,17 +2273,24 @@
       <c r="C68" t="s">
         <v>10</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="3">
+        <v>25.122</v>
+      </c>
+      <c r="E68" s="4">
+        <v>65</v>
+      </c>
+      <c r="F68">
         <v>1632.93</v>
       </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
         <v>71</v>
       </c>
-      <c r="F68" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H68" t="s">
+        <v>66</v>
+      </c>
+      <c r="M68" s="4"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -1815,17 +2300,24 @@
       <c r="C69" t="s">
         <v>18</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="3">
+        <v>4.1950000000000003</v>
+      </c>
+      <c r="E69" s="4">
+        <v>111.99999999999999</v>
+      </c>
+      <c r="F69">
         <v>469.84</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
         <v>71</v>
       </c>
-      <c r="F69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H69" t="s">
+        <v>66</v>
+      </c>
+      <c r="M69" s="4"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -1835,14 +2327,21 @@
       <c r="C70" t="s">
         <v>14</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="3">
+        <v>16.079000000000001</v>
+      </c>
+      <c r="E70" s="4">
+        <v>50</v>
+      </c>
+      <c r="F70">
         <v>803.95</v>
       </c>
-      <c r="F70" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H70" t="s">
+        <v>66</v>
+      </c>
+      <c r="M70" s="4"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -1852,14 +2351,21 @@
       <c r="C71" t="s">
         <v>12</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="3">
+        <v>14.065</v>
+      </c>
+      <c r="E71" s="4">
+        <v>95.000355492356917</v>
+      </c>
+      <c r="F71">
         <v>1336.18</v>
       </c>
-      <c r="F71" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H71" t="s">
+        <v>66</v>
+      </c>
+      <c r="M71" s="4"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>70</v>
       </c>
@@ -1869,14 +2375,21 @@
       <c r="C72" t="s">
         <v>12</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="3">
+        <v>16.888999999999999</v>
+      </c>
+      <c r="E72" s="4">
+        <v>70</v>
+      </c>
+      <c r="F72">
         <v>1182.23</v>
       </c>
-      <c r="F72" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H72" t="s">
+        <v>66</v>
+      </c>
+      <c r="M72" s="4"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -1886,17 +2399,24 @@
       <c r="C73" t="s">
         <v>12</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="3">
+        <v>23.146999999999998</v>
+      </c>
+      <c r="E73" s="4">
+        <v>58.560072579599954</v>
+      </c>
+      <c r="F73">
         <v>1355.49</v>
       </c>
-      <c r="E73" t="s">
+      <c r="G73" t="s">
         <v>73</v>
       </c>
-      <c r="F73" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H73" t="s">
+        <v>66</v>
+      </c>
+      <c r="M73" s="4"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -1906,14 +2426,21 @@
       <c r="C74" t="s">
         <v>14</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="3">
+        <v>18.552</v>
+      </c>
+      <c r="E74" s="4">
+        <v>50</v>
+      </c>
+      <c r="F74">
         <v>927.6</v>
       </c>
-      <c r="F74" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H74" t="s">
+        <v>66</v>
+      </c>
+      <c r="M74" s="4"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>72</v>
       </c>
@@ -1923,14 +2450,21 @@
       <c r="C75" t="s">
         <v>14</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="3">
+        <v>24.803999999999998</v>
+      </c>
+      <c r="E75" s="4">
+        <v>82.000080632156113</v>
+      </c>
+      <c r="F75">
         <v>2033.93</v>
       </c>
-      <c r="F75" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H75" t="s">
+        <v>66</v>
+      </c>
+      <c r="M75" s="4"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>72</v>
       </c>
@@ -1940,14 +2474,21 @@
       <c r="C76" t="s">
         <v>12</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="3">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E76" s="4">
+        <v>50.000000000000007</v>
+      </c>
+      <c r="F76">
         <v>957.5</v>
       </c>
-      <c r="F76" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H76" t="s">
+        <v>66</v>
+      </c>
+      <c r="M76" s="4"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>72</v>
       </c>
@@ -1957,14 +2498,21 @@
       <c r="C77" t="s">
         <v>7</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="3">
+        <v>25.193000000000001</v>
+      </c>
+      <c r="E77" s="4">
+        <v>80</v>
+      </c>
+      <c r="F77">
         <v>2015.44</v>
       </c>
-      <c r="F77" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H77" t="s">
+        <v>66</v>
+      </c>
+      <c r="M77" s="4"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>72</v>
       </c>
@@ -1974,14 +2522,21 @@
       <c r="C78" t="s">
         <v>12</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="3">
+        <v>18.324999999999999</v>
+      </c>
+      <c r="E78" s="4">
+        <v>70</v>
+      </c>
+      <c r="F78">
         <v>1282.75</v>
       </c>
-      <c r="F78" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H78" t="s">
+        <v>66</v>
+      </c>
+      <c r="M78" s="4"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>72</v>
       </c>
@@ -1991,14 +2546,21 @@
       <c r="C79" t="s">
         <v>10</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="3">
+        <v>24.106999999999999</v>
+      </c>
+      <c r="E79" s="4">
+        <v>70</v>
+      </c>
+      <c r="F79">
         <v>1687.49</v>
       </c>
-      <c r="F79" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H79" t="s">
+        <v>66</v>
+      </c>
+      <c r="M79" s="4"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>72</v>
       </c>
@@ -2008,17 +2570,24 @@
       <c r="C80" t="s">
         <v>14</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="3">
+        <v>13.993</v>
+      </c>
+      <c r="E80" s="4">
+        <v>86.999928535696426</v>
+      </c>
+      <c r="F80">
         <v>1217.3900000000001</v>
       </c>
-      <c r="E80" t="s">
+      <c r="G80" t="s">
         <v>74</v>
       </c>
-      <c r="F80" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H80" t="s">
+        <v>66</v>
+      </c>
+      <c r="M80" s="4"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>72</v>
       </c>
@@ -2028,17 +2597,24 @@
       <c r="C81" t="s">
         <v>12</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="3">
+        <v>23.161999999999999</v>
+      </c>
+      <c r="E81" s="4">
+        <v>80</v>
+      </c>
+      <c r="F81">
         <v>1852.96</v>
       </c>
-      <c r="E81" t="s">
+      <c r="G81" t="s">
         <v>73</v>
       </c>
-      <c r="F81" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H81" t="s">
+        <v>66</v>
+      </c>
+      <c r="M81" s="4"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>72</v>
       </c>
@@ -2048,14 +2624,21 @@
       <c r="C82" t="s">
         <v>12</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="3">
+        <v>8.9039999999999999</v>
+      </c>
+      <c r="E82" s="4">
+        <v>100</v>
+      </c>
+      <c r="F82">
         <v>890.4</v>
       </c>
-      <c r="F82" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H82" t="s">
+        <v>66</v>
+      </c>
+      <c r="M82" s="4"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>72</v>
       </c>
@@ -2065,17 +2648,24 @@
       <c r="C83" t="s">
         <v>12</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="3">
+        <v>21.858000000000001</v>
+      </c>
+      <c r="E83" s="4">
+        <v>70</v>
+      </c>
+      <c r="F83">
         <v>1530.06</v>
       </c>
-      <c r="E83" t="s">
+      <c r="G83" t="s">
         <v>71</v>
       </c>
-      <c r="F83" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H83" t="s">
+        <v>66</v>
+      </c>
+      <c r="M83" s="4"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>72</v>
       </c>
@@ -2085,14 +2675,21 @@
       <c r="C84" t="s">
         <v>14</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="3">
+        <v>25.047000000000001</v>
+      </c>
+      <c r="E84" s="4">
+        <v>90</v>
+      </c>
+      <c r="F84">
         <v>2254.23</v>
       </c>
-      <c r="F84" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H84" t="s">
+        <v>66</v>
+      </c>
+      <c r="M84" s="4"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>72</v>
       </c>
@@ -2102,14 +2699,21 @@
       <c r="C85" t="s">
         <v>14</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="3">
+        <v>21.138000000000002</v>
+      </c>
+      <c r="E85" s="4">
+        <v>85</v>
+      </c>
+      <c r="F85">
         <v>1796.73</v>
       </c>
-      <c r="F85" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H85" t="s">
+        <v>66</v>
+      </c>
+      <c r="M85" s="4"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>72</v>
       </c>
@@ -2119,14 +2723,21 @@
       <c r="C86" t="s">
         <v>10</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="3">
+        <v>24.542999999999999</v>
+      </c>
+      <c r="E86" s="4">
+        <v>80</v>
+      </c>
+      <c r="F86">
         <v>1963.44</v>
       </c>
-      <c r="F86" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H86" t="s">
+        <v>66</v>
+      </c>
+      <c r="M86" s="4"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>72</v>
       </c>
@@ -2136,17 +2747,24 @@
       <c r="C87" t="s">
         <v>18</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="3">
+        <v>12.601000000000001</v>
+      </c>
+      <c r="E87" s="4">
+        <v>90.160304737719215</v>
+      </c>
+      <c r="F87">
         <v>1136.1099999999999</v>
       </c>
-      <c r="E87" t="s">
+      <c r="G87" t="s">
         <v>73</v>
       </c>
-      <c r="F87" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H87" t="s">
+        <v>66</v>
+      </c>
+      <c r="M87" s="4"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>72</v>
       </c>
@@ -2156,17 +2774,24 @@
       <c r="C88" t="s">
         <v>12</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="3">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="E88" s="4">
+        <v>70</v>
+      </c>
+      <c r="F88">
         <v>684.6</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>75</v>
       </c>
-      <c r="F88" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H88" t="s">
+        <v>66</v>
+      </c>
+      <c r="M88" s="4"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>72</v>
       </c>
@@ -2176,17 +2801,24 @@
       <c r="C89" t="s">
         <v>10</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="3">
+        <v>11.125</v>
+      </c>
+      <c r="E89" s="4">
+        <v>79.900224719101118</v>
+      </c>
+      <c r="F89">
         <v>888.89</v>
       </c>
-      <c r="E89" t="s">
+      <c r="G89" t="s">
         <v>75</v>
       </c>
-      <c r="F89" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H89" t="s">
+        <v>66</v>
+      </c>
+      <c r="M89" s="4"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>72</v>
       </c>
@@ -2196,14 +2828,21 @@
       <c r="C90" t="s">
         <v>10</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="3">
+        <v>10.439</v>
+      </c>
+      <c r="E90" s="4">
+        <v>100.00000000000001</v>
+      </c>
+      <c r="F90">
         <v>1043.9000000000001</v>
       </c>
-      <c r="F90" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H90" t="s">
+        <v>66</v>
+      </c>
+      <c r="M90" s="4"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>72</v>
       </c>
@@ -2213,14 +2852,21 @@
       <c r="C91" t="s">
         <v>10</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="3">
+        <v>7.1740000000000004</v>
+      </c>
+      <c r="E91" s="4">
+        <v>99.999999999999986</v>
+      </c>
+      <c r="F91">
         <v>717.4</v>
       </c>
-      <c r="F91" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H91" t="s">
+        <v>66</v>
+      </c>
+      <c r="M91" s="4"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>72</v>
       </c>
@@ -2230,17 +2876,24 @@
       <c r="C92" t="s">
         <v>12</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="3">
+        <v>8.7379999999999995</v>
+      </c>
+      <c r="E92" s="4">
+        <v>50</v>
+      </c>
+      <c r="F92">
         <v>436.9</v>
       </c>
-      <c r="E92" t="s">
+      <c r="G92" t="s">
         <v>74</v>
       </c>
-      <c r="F92" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H92" t="s">
+        <v>66</v>
+      </c>
+      <c r="M92" s="4"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>72</v>
       </c>
@@ -2250,14 +2903,21 @@
       <c r="C93" t="s">
         <v>14</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="3">
+        <v>13.321</v>
+      </c>
+      <c r="E93" s="4">
+        <v>60</v>
+      </c>
+      <c r="F93">
         <v>799.26</v>
       </c>
-      <c r="F93" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H93" t="s">
+        <v>66</v>
+      </c>
+      <c r="M93" s="4"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>72</v>
       </c>
@@ -2267,17 +2927,24 @@
       <c r="C94" t="s">
         <v>12</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="3">
+        <v>13.906000000000001</v>
+      </c>
+      <c r="E94" s="4">
+        <v>30</v>
+      </c>
+      <c r="F94">
         <v>417.18</v>
       </c>
-      <c r="E94" t="s">
+      <c r="G94" t="s">
         <v>76</v>
       </c>
-      <c r="F94" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H94" t="s">
+        <v>66</v>
+      </c>
+      <c r="M94" s="4"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>72</v>
       </c>
@@ -2287,17 +2954,24 @@
       <c r="C95" t="s">
         <v>14</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="3">
+        <v>2.4460000000000002</v>
+      </c>
+      <c r="E95" s="4">
+        <v>40</v>
+      </c>
+      <c r="F95">
         <v>97.84</v>
       </c>
-      <c r="E95" t="s">
+      <c r="G95" t="s">
         <v>73</v>
       </c>
-      <c r="F95" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H95" t="s">
+        <v>66</v>
+      </c>
+      <c r="M95" s="4"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>72</v>
       </c>
@@ -2307,17 +2981,24 @@
       <c r="C96" t="s">
         <v>14</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="3">
+        <v>8.907</v>
+      </c>
+      <c r="E96" s="4">
+        <v>25.00056135623667</v>
+      </c>
+      <c r="F96">
         <v>222.68</v>
       </c>
-      <c r="E96" t="s">
+      <c r="G96" t="s">
         <v>76</v>
       </c>
-      <c r="F96" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H96" t="s">
+        <v>66</v>
+      </c>
+      <c r="M96" s="4"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>72</v>
       </c>
@@ -2327,14 +3008,21 @@
       <c r="C97" t="s">
         <v>14</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="3">
+        <v>7.4450000000000003</v>
+      </c>
+      <c r="E97" s="4">
+        <v>35.000671591672258</v>
+      </c>
+      <c r="F97">
         <v>260.58</v>
       </c>
-      <c r="F97" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H97" t="s">
+        <v>66</v>
+      </c>
+      <c r="M97" s="4"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>72</v>
       </c>
@@ -2344,17 +3032,24 @@
       <c r="C98" t="s">
         <v>14</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="E98" s="4">
+        <v>65.897637795275585</v>
+      </c>
+      <c r="F98">
         <v>83.69</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>77</v>
       </c>
-      <c r="F98" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H98" t="s">
+        <v>66</v>
+      </c>
+      <c r="M98" s="4"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>72</v>
       </c>
@@ -2364,14 +3059,21 @@
       <c r="C99" t="s">
         <v>14</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="3">
+        <v>2.8849999999999998</v>
+      </c>
+      <c r="E99" s="4">
+        <v>45.001733102253041</v>
+      </c>
+      <c r="F99">
         <v>129.83000000000001</v>
       </c>
-      <c r="F99" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H99" t="s">
+        <v>66</v>
+      </c>
+      <c r="M99" s="4"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>72</v>
       </c>
@@ -2381,14 +3083,21 @@
       <c r="C100" t="s">
         <v>14</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="3">
+        <v>18.957999999999998</v>
+      </c>
+      <c r="E100" s="4">
+        <v>25</v>
+      </c>
+      <c r="F100">
         <v>473.95</v>
       </c>
-      <c r="F100" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H100" t="s">
+        <v>66</v>
+      </c>
+      <c r="M100" s="4"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>72</v>
       </c>
@@ -2398,14 +3107,21 @@
       <c r="C101" t="s">
         <v>14</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="3">
+        <v>1.9119999999999999</v>
+      </c>
+      <c r="E101" s="4">
+        <v>25</v>
+      </c>
+      <c r="F101">
         <v>47.8</v>
       </c>
-      <c r="F101" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H101" t="s">
+        <v>66</v>
+      </c>
+      <c r="M101" s="4"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>72</v>
       </c>
@@ -2415,14 +3131,21 @@
       <c r="C102" t="s">
         <v>7</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="3">
+        <v>3.9249999999999998</v>
+      </c>
+      <c r="E102" s="4">
+        <v>55.001273885350322</v>
+      </c>
+      <c r="F102">
         <v>215.88</v>
       </c>
-      <c r="F102" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H102" t="s">
+        <v>66</v>
+      </c>
+      <c r="M102" s="4"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>72</v>
       </c>
@@ -2432,12 +3155,19 @@
       <c r="C103" t="s">
         <v>7</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="3">
+        <v>3.069</v>
+      </c>
+      <c r="E103" s="4">
+        <v>55.001629195177586</v>
+      </c>
+      <c r="F103" t="s">
         <v>78</v>
       </c>
-      <c r="F103" t="s">
-        <v>66</v>
-      </c>
+      <c r="H103" t="s">
+        <v>66</v>
+      </c>
+      <c r="M103" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -270,7 +270,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -327,7 +327,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -963,7 +963,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="3">
-        <v>35.624000000000002</v>
+        <v>33.844000000000001</v>
       </c>
       <c r="E14" s="4">
         <v>92.407927240062875</v>
@@ -2223,7 +2223,7 @@
         <v>12</v>
       </c>
       <c r="D66" s="3">
-        <v>34.652000000000001</v>
+        <v>33.844000000000001</v>
       </c>
       <c r="E66" s="4">
         <v>99.999999999999986</v>

--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -3036,7 +3036,7 @@
         <v>1.27</v>
       </c>
       <c r="E98" s="4">
-        <v>65.897637795275585</v>
+        <v>35</v>
       </c>
       <c r="F98">
         <v>83.69</v>

--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -2424,7 +2424,7 @@
         <v>33</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D74" s="3">
         <v>18.552</v>

--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -1998,7 +1998,7 @@
         <v>14</v>
       </c>
       <c r="D57" s="3">
-        <v>10.141</v>
+        <v>11.141</v>
       </c>
       <c r="E57" s="4">
         <v>89.925056700522632</v>
@@ -2175,7 +2175,7 @@
         <v>23</v>
       </c>
       <c r="D64" s="3">
-        <v>42.033000000000001</v>
+        <v>41.633000000000003</v>
       </c>
       <c r="E64" s="4">
         <v>105.00011895415507</v>
@@ -2271,7 +2271,7 @@
         <v>27</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D68" s="3">
         <v>25.122</v>
@@ -2400,7 +2400,7 @@
         <v>12</v>
       </c>
       <c r="D73" s="3">
-        <v>23.146999999999998</v>
+        <v>22.911999999999999</v>
       </c>
       <c r="E73" s="4">
         <v>58.560072579599954</v>
@@ -2748,7 +2748,7 @@
         <v>18</v>
       </c>
       <c r="D87" s="3">
-        <v>12.601000000000001</v>
+        <v>12.577999999999999</v>
       </c>
       <c r="E87" s="4">
         <v>90.160304737719215</v>
@@ -3084,7 +3084,7 @@
         <v>14</v>
       </c>
       <c r="D100" s="3">
-        <v>18.957999999999998</v>
+        <v>19.189</v>
       </c>
       <c r="E100" s="4">
         <v>25</v>

--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -49,6 +49,9 @@
     <t>2026-01-09</t>
   </si>
   <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
     <t>DG01000</t>
   </si>
   <si>
@@ -284,6 +287,36 @@
   </si>
   <si>
     <t xml:space="preserve">Good time cut &amp; field operation done timely </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good irrigation application </t>
+  </si>
+  <si>
+    <t>Will not go above last years TCH. Late start of follow-up activities</t>
+  </si>
+  <si>
+    <t>Time field was cut in 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Late cut, no irrigation to start follow-up activities </t>
+  </si>
+  <si>
+    <t>Ratoon 1 and harvested early due to malicious fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New plant, but poorly germinated  </t>
+  </si>
+  <si>
+    <t>Plant cane</t>
+  </si>
+  <si>
+    <t>Attacked by BB, late fert. application due to no irrigation water as the field was cut near the end of the year</t>
+  </si>
+  <si>
+    <t>Good cane stand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follow-up activities done on time </t>
   </si>
   <si>
     <t>2024/25</t>
@@ -654,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -688,10 +721,10 @@
         <v>45376</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2">
         <v>19.686</v>
@@ -703,7 +736,7 @@
         <v>1870.17</v>
       </c>
       <c r="H2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -711,10 +744,10 @@
         <v>45376</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>9.135</v>
@@ -726,7 +759,7 @@
         <v>639.4499999999999</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -734,10 +767,10 @@
         <v>45376</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D4">
         <v>11.3</v>
@@ -749,7 +782,7 @@
         <v>926.6</v>
       </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -757,10 +790,10 @@
         <v>45376</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5">
         <v>16.342</v>
@@ -772,7 +805,7 @@
         <v>557.05</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -780,10 +813,10 @@
         <v>45376</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6">
         <v>17.328</v>
@@ -795,7 +828,7 @@
         <v>1472.88</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -803,10 +836,10 @@
         <v>45376</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7">
         <v>15.697</v>
@@ -818,7 +851,7 @@
         <v>1466.705</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -826,10 +859,10 @@
         <v>45376</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>19.281</v>
@@ -841,7 +874,7 @@
         <v>1629.81</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -849,10 +882,10 @@
         <v>45376</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9">
         <v>17.605</v>
@@ -864,7 +897,7 @@
         <v>1369.92</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -872,10 +905,10 @@
         <v>45376</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D10">
         <v>31.706</v>
@@ -887,7 +920,7 @@
         <v>2377.95</v>
       </c>
       <c r="H10" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -895,10 +928,10 @@
         <v>45376</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11">
         <v>21.465</v>
@@ -910,7 +943,7 @@
         <v>1502.55</v>
       </c>
       <c r="H11" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -918,10 +951,10 @@
         <v>45376</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D12">
         <v>42.033</v>
@@ -933,7 +966,7 @@
         <v>3782.970000000001</v>
       </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -941,10 +974,10 @@
         <v>45376</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13">
         <v>23.658</v>
@@ -956,7 +989,7 @@
         <v>1774.35</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -964,10 +997,10 @@
         <v>45376</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14">
         <v>33.844</v>
@@ -979,7 +1012,7 @@
         <v>3291.94</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -987,10 +1020,10 @@
         <v>45376</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15">
         <v>14.504</v>
@@ -1002,7 +1035,7 @@
         <v>725.2</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1010,10 +1043,10 @@
         <v>45376</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16">
         <v>25.122</v>
@@ -1025,7 +1058,7 @@
         <v>348.9</v>
       </c>
       <c r="H16" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1033,10 +1066,10 @@
         <v>45376</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17">
         <v>4.195</v>
@@ -1048,7 +1081,7 @@
         <v>356.575</v>
       </c>
       <c r="H17" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1056,10 +1089,10 @@
         <v>45376</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18">
         <v>16.079</v>
@@ -1071,7 +1104,7 @@
         <v>964.74</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1079,10 +1112,10 @@
         <v>45376</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19">
         <v>14.065</v>
@@ -1094,7 +1127,7 @@
         <v>1265.85</v>
       </c>
       <c r="H19" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1102,10 +1135,10 @@
         <v>45376</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20">
         <v>16.889</v>
@@ -1117,7 +1150,7 @@
         <v>1182.23</v>
       </c>
       <c r="H20" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1125,10 +1158,10 @@
         <v>45376</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D21">
         <v>23.147</v>
@@ -1140,7 +1173,7 @@
         <v>1620.29</v>
       </c>
       <c r="H21" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1148,10 +1181,10 @@
         <v>45376</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D22">
         <v>18.552</v>
@@ -1163,7 +1196,7 @@
         <v>1113.12</v>
       </c>
       <c r="H22" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1171,10 +1204,10 @@
         <v>45376</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D23">
         <v>24.804</v>
@@ -1186,7 +1219,7 @@
         <v>2232.36</v>
       </c>
       <c r="H23" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1194,10 +1227,10 @@
         <v>45376</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24">
         <v>19.15</v>
@@ -1209,7 +1242,7 @@
         <v>1053.25</v>
       </c>
       <c r="H24" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1217,10 +1250,10 @@
         <v>45376</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25">
         <v>25.193</v>
@@ -1232,7 +1265,7 @@
         <v>2056.405</v>
       </c>
       <c r="H25" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1240,10 +1273,10 @@
         <v>45376</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26">
         <v>18.325</v>
@@ -1255,7 +1288,7 @@
         <v>1466</v>
       </c>
       <c r="H26" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1263,10 +1296,10 @@
         <v>45376</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27">
         <v>24.107</v>
@@ -1278,7 +1311,7 @@
         <v>1808.025</v>
       </c>
       <c r="H27" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1286,10 +1319,10 @@
         <v>45376</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D28">
         <v>13.993</v>
@@ -1301,7 +1334,7 @@
         <v>1259.37</v>
       </c>
       <c r="H28" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1309,10 +1342,10 @@
         <v>45376</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D29">
         <v>23.162</v>
@@ -1324,7 +1357,7 @@
         <v>1158.1</v>
       </c>
       <c r="H29" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1332,10 +1365,10 @@
         <v>45376</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D30">
         <v>8.423</v>
@@ -1347,7 +1380,7 @@
         <v>801.36</v>
       </c>
       <c r="H30" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1355,10 +1388,10 @@
         <v>45376</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D31">
         <v>21.858</v>
@@ -1370,7 +1403,7 @@
         <v>940.85</v>
       </c>
       <c r="H31" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1378,10 +1411,10 @@
         <v>45376</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D32">
         <v>25.047</v>
@@ -1393,7 +1426,7 @@
         <v>2254.23</v>
       </c>
       <c r="H32" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1401,10 +1434,10 @@
         <v>45376</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D33">
         <v>21.138</v>
@@ -1416,7 +1449,7 @@
         <v>1479.66</v>
       </c>
       <c r="H33" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1424,10 +1457,10 @@
         <v>45376</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D34">
         <v>24.543</v>
@@ -1439,7 +1472,7 @@
         <v>1963.44</v>
       </c>
       <c r="H34" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1447,10 +1480,10 @@
         <v>45376</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D35">
         <v>12.796</v>
@@ -1462,7 +1495,7 @@
         <v>1008.08</v>
       </c>
       <c r="H35" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1470,10 +1503,10 @@
         <v>45376</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D36">
         <v>9.779999999999999</v>
@@ -1485,7 +1518,7 @@
         <v>586.8</v>
       </c>
       <c r="H36" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1493,10 +1526,10 @@
         <v>45376</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D37">
         <v>11.125</v>
@@ -1508,7 +1541,7 @@
         <v>890</v>
       </c>
       <c r="H37" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1516,10 +1549,10 @@
         <v>45376</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D38">
         <v>10.439</v>
@@ -1531,7 +1564,7 @@
         <v>939.51</v>
       </c>
       <c r="H38" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1539,10 +1572,10 @@
         <v>45376</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D39">
         <v>7.174</v>
@@ -1554,7 +1587,7 @@
         <v>645.66</v>
       </c>
       <c r="H39" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1562,10 +1595,10 @@
         <v>45376</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D40">
         <v>8.738</v>
@@ -1577,7 +1610,7 @@
         <v>567.97</v>
       </c>
       <c r="H40" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1585,10 +1618,10 @@
         <v>45376</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D41">
         <v>13.321</v>
@@ -1600,7 +1633,7 @@
         <v>732.6549999999999</v>
       </c>
       <c r="H41" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1608,10 +1641,10 @@
         <v>45376</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D42">
         <v>18.931</v>
@@ -1623,7 +1656,7 @@
         <v>851.8950000000001</v>
       </c>
       <c r="H42" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1631,10 +1664,10 @@
         <v>45376</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1646,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1654,10 +1687,10 @@
         <v>45376</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D44">
         <v>25.214</v>
@@ -1669,7 +1702,7 @@
         <v>891.0399999999998</v>
       </c>
       <c r="H44" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1677,10 +1710,10 @@
         <v>45376</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D45">
         <v>7.445</v>
@@ -1692,7 +1725,7 @@
         <v>335.025</v>
       </c>
       <c r="H45" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1700,10 +1733,10 @@
         <v>45376</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D46">
         <v>1.27</v>
@@ -1715,7 +1748,7 @@
         <v>71.73</v>
       </c>
       <c r="H46" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1723,10 +1756,10 @@
         <v>45376</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D47">
         <v>2.885</v>
@@ -1738,7 +1771,7 @@
         <v>86.55</v>
       </c>
       <c r="H47" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1746,7 +1779,7 @@
         <v>45376</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -1758,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1766,10 +1799,10 @@
         <v>45376</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D49">
         <v>15.798</v>
@@ -1781,7 +1814,7 @@
         <v>545.64</v>
       </c>
       <c r="H49" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1789,10 +1822,10 @@
         <v>45376</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D50">
         <v>5.345</v>
@@ -1804,7 +1837,7 @@
         <v>131.8</v>
       </c>
       <c r="H50" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1812,10 +1845,10 @@
         <v>45376</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D51">
         <v>4.094</v>
@@ -1827,7 +1860,7 @@
         <v>196.25</v>
       </c>
       <c r="H51" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1835,7 +1868,7 @@
         <v>45376</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -1847,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1855,10 +1888,10 @@
         <v>45376</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D53">
         <v>3.07</v>
@@ -1870,7 +1903,7 @@
         <v>148.5</v>
       </c>
       <c r="H53" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1878,10 +1911,10 @@
         <v>45736</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D54">
         <v>19.686</v>
@@ -1893,10 +1926,10 @@
         <v>2067.03</v>
       </c>
       <c r="G54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H54" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1904,10 +1937,10 @@
         <v>45736</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D55">
         <v>9.135</v>
@@ -1919,10 +1952,10 @@
         <v>803.88</v>
       </c>
       <c r="G55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H55" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1930,10 +1963,10 @@
         <v>45736</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D56">
         <v>11.3</v>
@@ -1945,10 +1978,10 @@
         <v>1015.87</v>
       </c>
       <c r="G56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H56" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1956,10 +1989,10 @@
         <v>45736</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D57">
         <v>11.141</v>
@@ -1971,10 +2004,10 @@
         <v>911.9299999999999</v>
       </c>
       <c r="G57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H57" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -1982,10 +2015,10 @@
         <v>45736</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D58">
         <v>17.328</v>
@@ -1997,10 +2030,10 @@
         <v>1663.49</v>
       </c>
       <c r="G58" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H58" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2008,10 +2041,10 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D59">
         <v>15.439</v>
@@ -2023,7 +2056,7 @@
         <v>1513.02</v>
       </c>
       <c r="H59" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2031,10 +2064,10 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D60">
         <v>18.895</v>
@@ -2046,10 +2079,10 @@
         <v>1700.55</v>
       </c>
       <c r="G60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H60" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2057,10 +2090,10 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C61" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D61">
         <v>17.124</v>
@@ -2072,7 +2105,7 @@
         <v>1541.16</v>
       </c>
       <c r="H61" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2080,10 +2113,10 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D62">
         <v>31.706</v>
@@ -2095,7 +2128,7 @@
         <v>2853.54</v>
       </c>
       <c r="H62" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2103,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D63">
         <v>21.465</v>
@@ -2118,7 +2151,7 @@
         <v>1824.53</v>
       </c>
       <c r="H63" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2126,10 +2159,10 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D64">
         <v>41.633</v>
@@ -2141,7 +2174,7 @@
         <v>4413.47</v>
       </c>
       <c r="H64" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2149,10 +2182,10 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D65">
         <v>23.658</v>
@@ -2164,7 +2197,7 @@
         <v>1892.64</v>
       </c>
       <c r="H65" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2172,10 +2205,10 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D66">
         <v>33.844</v>
@@ -2187,10 +2220,10 @@
         <v>3465.2</v>
       </c>
       <c r="G66" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H66" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2198,10 +2231,10 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D67">
         <v>14.504</v>
@@ -2213,7 +2246,7 @@
         <v>899.25</v>
       </c>
       <c r="H67" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2221,10 +2254,10 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D68">
         <v>25.122</v>
@@ -2236,10 +2269,10 @@
         <v>1632.93</v>
       </c>
       <c r="G68" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H68" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2247,10 +2280,10 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C69" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D69">
         <v>4.195</v>
@@ -2262,10 +2295,10 @@
         <v>469.84</v>
       </c>
       <c r="G69" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H69" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2273,10 +2306,10 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D70">
         <v>16.079</v>
@@ -2288,7 +2321,7 @@
         <v>803.95</v>
       </c>
       <c r="H70" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2296,10 +2329,10 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C71" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D71">
         <v>14.065</v>
@@ -2311,7 +2344,7 @@
         <v>1336.18</v>
       </c>
       <c r="H71" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2319,10 +2352,10 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D72">
         <v>16.889</v>
@@ -2334,7 +2367,7 @@
         <v>1182.23</v>
       </c>
       <c r="H72" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2342,10 +2375,10 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C73" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D73">
         <v>22.912</v>
@@ -2357,10 +2390,10 @@
         <v>1355.49</v>
       </c>
       <c r="G73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2368,10 +2401,10 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D74">
         <v>18.552</v>
@@ -2383,7 +2416,7 @@
         <v>927.6</v>
       </c>
       <c r="H74" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2391,10 +2424,10 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C75" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D75">
         <v>24.804</v>
@@ -2406,7 +2439,7 @@
         <v>2033.93</v>
       </c>
       <c r="H75" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2414,10 +2447,10 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C76" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D76">
         <v>19.15</v>
@@ -2429,7 +2462,7 @@
         <v>957.5</v>
       </c>
       <c r="H76" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2437,10 +2470,10 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D77">
         <v>25.193</v>
@@ -2452,7 +2485,7 @@
         <v>2015.44</v>
       </c>
       <c r="H77" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2460,10 +2493,10 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C78" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D78">
         <v>18.325</v>
@@ -2475,7 +2508,7 @@
         <v>1282.75</v>
       </c>
       <c r="H78" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2483,10 +2516,10 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C79" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D79">
         <v>24.107</v>
@@ -2498,7 +2531,7 @@
         <v>1687.49</v>
       </c>
       <c r="H79" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2506,10 +2539,10 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C80" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D80">
         <v>13.993</v>
@@ -2521,10 +2554,10 @@
         <v>1217.39</v>
       </c>
       <c r="G80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H80" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2532,10 +2565,10 @@
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D81">
         <v>23.162</v>
@@ -2547,10 +2580,10 @@
         <v>1852.96</v>
       </c>
       <c r="G81" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H81" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2558,10 +2591,10 @@
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C82" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D82">
         <v>8.904</v>
@@ -2573,7 +2606,7 @@
         <v>890.4</v>
       </c>
       <c r="H82" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2581,10 +2614,10 @@
         <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C83" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D83">
         <v>21.858</v>
@@ -2596,10 +2629,10 @@
         <v>1530.06</v>
       </c>
       <c r="G83" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H83" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2607,10 +2640,10 @@
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C84" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D84">
         <v>25.047</v>
@@ -2622,7 +2655,7 @@
         <v>2254.23</v>
       </c>
       <c r="H84" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2630,10 +2663,10 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C85" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D85">
         <v>21.138</v>
@@ -2645,7 +2678,7 @@
         <v>1796.73</v>
       </c>
       <c r="H85" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2653,10 +2686,10 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C86" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D86">
         <v>24.543</v>
@@ -2668,7 +2701,7 @@
         <v>1963.44</v>
       </c>
       <c r="H86" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2676,10 +2709,10 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C87" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D87">
         <v>12.578</v>
@@ -2691,10 +2724,10 @@
         <v>1136.11</v>
       </c>
       <c r="G87" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H87" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2702,10 +2735,10 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C88" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D88">
         <v>9.779999999999999</v>
@@ -2717,10 +2750,10 @@
         <v>684.6</v>
       </c>
       <c r="G88" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H88" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2728,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C89" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D89">
         <v>11.125</v>
@@ -2743,10 +2776,10 @@
         <v>888.89</v>
       </c>
       <c r="G89" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2754,10 +2787,10 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C90" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D90">
         <v>10.439</v>
@@ -2769,7 +2802,7 @@
         <v>1043.9</v>
       </c>
       <c r="H90" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2777,10 +2810,10 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D91">
         <v>7.174</v>
@@ -2792,7 +2825,7 @@
         <v>717.4</v>
       </c>
       <c r="H91" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2800,10 +2833,10 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C92" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D92">
         <v>8.738</v>
@@ -2815,10 +2848,10 @@
         <v>436.9</v>
       </c>
       <c r="G92" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H92" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2826,10 +2859,10 @@
         <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C93" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D93">
         <v>13.321</v>
@@ -2841,7 +2874,7 @@
         <v>799.26</v>
       </c>
       <c r="H93" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -2849,10 +2882,10 @@
         <v>9</v>
       </c>
       <c r="B94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D94">
         <v>13.906</v>
@@ -2864,10 +2897,10 @@
         <v>417.18</v>
       </c>
       <c r="G94" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H94" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -2875,10 +2908,10 @@
         <v>9</v>
       </c>
       <c r="B95" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C95" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D95">
         <v>2.446</v>
@@ -2890,10 +2923,10 @@
         <v>97.84</v>
       </c>
       <c r="G95" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H95" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -2901,10 +2934,10 @@
         <v>9</v>
       </c>
       <c r="B96" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C96" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D96">
         <v>8.907</v>
@@ -2916,10 +2949,10 @@
         <v>222.68</v>
       </c>
       <c r="G96" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H96" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -2927,10 +2960,10 @@
         <v>9</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D97">
         <v>7.445</v>
@@ -2942,7 +2975,7 @@
         <v>260.58</v>
       </c>
       <c r="H97" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -2950,10 +2983,10 @@
         <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C98" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D98">
         <v>1.27</v>
@@ -2965,10 +2998,10 @@
         <v>83.69</v>
       </c>
       <c r="G98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -2976,10 +3009,10 @@
         <v>9</v>
       </c>
       <c r="B99" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C99" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D99">
         <v>2.885</v>
@@ -2991,7 +3024,7 @@
         <v>129.83</v>
       </c>
       <c r="H99" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -2999,10 +3032,10 @@
         <v>9</v>
       </c>
       <c r="B100" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C100" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D100">
         <v>19.189</v>
@@ -3014,7 +3047,7 @@
         <v>473.95</v>
       </c>
       <c r="H100" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3022,10 +3055,10 @@
         <v>9</v>
       </c>
       <c r="B101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D101">
         <v>1.912</v>
@@ -3037,7 +3070,7 @@
         <v>47.8</v>
       </c>
       <c r="H101" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3045,10 +3078,10 @@
         <v>9</v>
       </c>
       <c r="B102" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C102" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D102">
         <v>3.925</v>
@@ -3060,7 +3093,7 @@
         <v>215.88</v>
       </c>
       <c r="H102" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3068,10 +3101,10 @@
         <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C103" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D103">
         <v>3.069</v>
@@ -3083,7 +3116,7 @@
         <v>168.8</v>
       </c>
       <c r="H103" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3091,10 +3124,10 @@
         <v>10</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D104">
         <v>19.686</v>
@@ -3106,10 +3139,10 @@
         <v>2342.63</v>
       </c>
       <c r="G104" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H104" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3117,10 +3150,10 @@
         <v>10</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D105">
         <v>9.135</v>
@@ -3132,10 +3165,10 @@
         <v>895.23</v>
       </c>
       <c r="G105" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -3143,10 +3176,10 @@
         <v>10</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D106">
         <v>11.3</v>
@@ -3158,10 +3191,10 @@
         <v>1186.5</v>
       </c>
       <c r="G106" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3169,10 +3202,10 @@
         <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C107" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D107">
         <v>11.141</v>
@@ -3184,10 +3217,10 @@
         <v>1336.92</v>
       </c>
       <c r="G107" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H107" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -3195,10 +3228,10 @@
         <v>10</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C108" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D108">
         <v>17.328</v>
@@ -3210,10 +3243,10 @@
         <v>1819.44</v>
       </c>
       <c r="G108" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H108" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3221,10 +3254,10 @@
         <v>10</v>
       </c>
       <c r="B109" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D109">
         <v>15.439</v>
@@ -3236,10 +3269,10 @@
         <v>1868.12</v>
       </c>
       <c r="G109" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H109" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -3247,10 +3280,10 @@
         <v>10</v>
       </c>
       <c r="B110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C110" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D110">
         <v>18.895</v>
@@ -3262,10 +3295,10 @@
         <v>2078.45</v>
       </c>
       <c r="G110" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H110" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -3273,10 +3306,10 @@
         <v>10</v>
       </c>
       <c r="B111" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C111" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D111">
         <v>17.124</v>
@@ -3288,10 +3321,10 @@
         <v>1763.77</v>
       </c>
       <c r="G111" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H111" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3299,10 +3332,10 @@
         <v>10</v>
       </c>
       <c r="B112" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C112" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D112">
         <v>31.706</v>
@@ -3314,10 +3347,10 @@
         <v>3170.6</v>
       </c>
       <c r="G112" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H112" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3325,10 +3358,10 @@
         <v>10</v>
       </c>
       <c r="B113" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C113" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D113">
         <v>21.465</v>
@@ -3340,10 +3373,10 @@
         <v>1996.24</v>
       </c>
       <c r="G113" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H113" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -3351,10 +3384,10 @@
         <v>10</v>
       </c>
       <c r="B114" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C114" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D114">
         <v>41.633</v>
@@ -3366,10 +3399,10 @@
         <v>4579.63</v>
       </c>
       <c r="G114" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H114" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -3377,10 +3410,10 @@
         <v>10</v>
       </c>
       <c r="B115" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C115" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D115">
         <v>33.844</v>
@@ -3392,10 +3425,647 @@
         <v>4399.72</v>
       </c>
       <c r="G115" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H115" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>11</v>
+      </c>
+      <c r="B116" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" t="s">
+        <v>66</v>
+      </c>
+      <c r="D116">
+        <v>14.504</v>
+      </c>
+      <c r="E116">
+        <v>96</v>
+      </c>
+      <c r="F116">
+        <v>1392.38</v>
+      </c>
+      <c r="G116" t="s">
+        <v>82</v>
+      </c>
+      <c r="H116" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117" t="s">
+        <v>65</v>
+      </c>
+      <c r="D117">
+        <v>25.122</v>
+      </c>
+      <c r="E117">
+        <v>85</v>
+      </c>
+      <c r="F117">
+        <v>2135.37</v>
+      </c>
+      <c r="H117" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118">
+        <v>4.195</v>
+      </c>
+      <c r="E118">
+        <v>125</v>
+      </c>
+      <c r="F118">
+        <v>524.38</v>
+      </c>
+      <c r="G118" t="s">
+        <v>91</v>
+      </c>
+      <c r="H118" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" t="s">
+        <v>28</v>
+      </c>
+      <c r="C119" t="s">
+        <v>67</v>
+      </c>
+      <c r="D119">
+        <v>16.079</v>
+      </c>
+      <c r="E119">
+        <v>61</v>
+      </c>
+      <c r="F119">
+        <v>980.8200000000001</v>
+      </c>
+      <c r="G119" t="s">
         <v>92</v>
+      </c>
+      <c r="H119" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>11</v>
+      </c>
+      <c r="B120" t="s">
+        <v>29</v>
+      </c>
+      <c r="C120" t="s">
+        <v>66</v>
+      </c>
+      <c r="D120">
+        <v>14.065</v>
+      </c>
+      <c r="E120">
+        <v>98</v>
+      </c>
+      <c r="F120">
+        <v>1378.37</v>
+      </c>
+      <c r="G120" t="s">
+        <v>93</v>
+      </c>
+      <c r="H120" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121" t="s">
+        <v>66</v>
+      </c>
+      <c r="D121">
+        <v>16.889</v>
+      </c>
+      <c r="E121">
+        <v>46</v>
+      </c>
+      <c r="F121">
+        <v>776.89</v>
+      </c>
+      <c r="G121" t="s">
+        <v>94</v>
+      </c>
+      <c r="H121" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" t="s">
+        <v>31</v>
+      </c>
+      <c r="C122" t="s">
+        <v>66</v>
+      </c>
+      <c r="D122">
+        <v>22.912</v>
+      </c>
+      <c r="E122">
+        <v>110</v>
+      </c>
+      <c r="F122">
+        <v>2520.32</v>
+      </c>
+      <c r="G122" t="s">
+        <v>95</v>
+      </c>
+      <c r="H122" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C123" t="s">
+        <v>66</v>
+      </c>
+      <c r="D123">
+        <v>18.552</v>
+      </c>
+      <c r="E123">
+        <v>73</v>
+      </c>
+      <c r="F123">
+        <v>1354.3</v>
+      </c>
+      <c r="H123" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>11</v>
+      </c>
+      <c r="B124" t="s">
+        <v>33</v>
+      </c>
+      <c r="C124" t="s">
+        <v>67</v>
+      </c>
+      <c r="D124">
+        <v>24.804</v>
+      </c>
+      <c r="E124">
+        <v>83</v>
+      </c>
+      <c r="F124">
+        <v>2058.73</v>
+      </c>
+      <c r="H124" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" t="s">
+        <v>66</v>
+      </c>
+      <c r="D125">
+        <v>19.15</v>
+      </c>
+      <c r="E125">
+        <v>55</v>
+      </c>
+      <c r="F125">
+        <v>1053.25</v>
+      </c>
+      <c r="H125" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" t="s">
+        <v>35</v>
+      </c>
+      <c r="C126" t="s">
+        <v>64</v>
+      </c>
+      <c r="D126">
+        <v>25.193</v>
+      </c>
+      <c r="E126">
+        <v>80</v>
+      </c>
+      <c r="F126">
+        <v>2015.44</v>
+      </c>
+      <c r="H126" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>11</v>
+      </c>
+      <c r="B127" t="s">
+        <v>36</v>
+      </c>
+      <c r="C127" t="s">
+        <v>66</v>
+      </c>
+      <c r="D127">
+        <v>18.325</v>
+      </c>
+      <c r="E127">
+        <v>90</v>
+      </c>
+      <c r="F127">
+        <v>1649.25</v>
+      </c>
+      <c r="H127" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>11</v>
+      </c>
+      <c r="B128" t="s">
+        <v>37</v>
+      </c>
+      <c r="C128" t="s">
+        <v>65</v>
+      </c>
+      <c r="D128">
+        <v>24.107</v>
+      </c>
+      <c r="E128">
+        <v>65</v>
+      </c>
+      <c r="F128">
+        <v>1566.95</v>
+      </c>
+      <c r="G128" t="s">
+        <v>96</v>
+      </c>
+      <c r="H128" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>11</v>
+      </c>
+      <c r="B129" t="s">
+        <v>38</v>
+      </c>
+      <c r="C129" t="s">
+        <v>65</v>
+      </c>
+      <c r="D129">
+        <v>13.993</v>
+      </c>
+      <c r="E129">
+        <v>95</v>
+      </c>
+      <c r="F129">
+        <v>1329.34</v>
+      </c>
+      <c r="G129" t="s">
+        <v>97</v>
+      </c>
+      <c r="H129" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>11</v>
+      </c>
+      <c r="B130" t="s">
+        <v>39</v>
+      </c>
+      <c r="C130" t="s">
+        <v>66</v>
+      </c>
+      <c r="D130">
+        <v>23.162</v>
+      </c>
+      <c r="E130">
+        <v>65</v>
+      </c>
+      <c r="F130">
+        <v>1505.53</v>
+      </c>
+      <c r="G130" t="s">
+        <v>98</v>
+      </c>
+      <c r="H130" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>11</v>
+      </c>
+      <c r="B131" t="s">
+        <v>40</v>
+      </c>
+      <c r="C131" t="s">
+        <v>66</v>
+      </c>
+      <c r="D131">
+        <v>8.904</v>
+      </c>
+      <c r="E131">
+        <v>106</v>
+      </c>
+      <c r="F131">
+        <v>943.8200000000001</v>
+      </c>
+      <c r="G131" t="s">
+        <v>99</v>
+      </c>
+      <c r="H131" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>11</v>
+      </c>
+      <c r="B132" t="s">
+        <v>41</v>
+      </c>
+      <c r="C132" t="s">
+        <v>66</v>
+      </c>
+      <c r="D132">
+        <v>21.858</v>
+      </c>
+      <c r="E132">
+        <v>75</v>
+      </c>
+      <c r="F132">
+        <v>1639.35</v>
+      </c>
+      <c r="H132" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>11</v>
+      </c>
+      <c r="B133" t="s">
+        <v>42</v>
+      </c>
+      <c r="C133" t="s">
+        <v>67</v>
+      </c>
+      <c r="D133">
+        <v>25.047</v>
+      </c>
+      <c r="E133">
+        <v>97</v>
+      </c>
+      <c r="F133">
+        <v>2429.56</v>
+      </c>
+      <c r="H133" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>11</v>
+      </c>
+      <c r="B134" t="s">
+        <v>43</v>
+      </c>
+      <c r="C134" t="s">
+        <v>67</v>
+      </c>
+      <c r="D134">
+        <v>21.138</v>
+      </c>
+      <c r="E134">
+        <v>92</v>
+      </c>
+      <c r="F134">
+        <v>1944.7</v>
+      </c>
+      <c r="G134" t="s">
+        <v>100</v>
+      </c>
+      <c r="H134" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" t="s">
+        <v>44</v>
+      </c>
+      <c r="C135" t="s">
+        <v>65</v>
+      </c>
+      <c r="D135">
+        <v>24.543</v>
+      </c>
+      <c r="E135">
+        <v>95</v>
+      </c>
+      <c r="F135">
+        <v>2331.59</v>
+      </c>
+      <c r="H135" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" t="s">
+        <v>45</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136">
+        <v>12.578</v>
+      </c>
+      <c r="E136">
+        <v>105</v>
+      </c>
+      <c r="F136">
+        <v>1320.69</v>
+      </c>
+      <c r="H136" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>11</v>
+      </c>
+      <c r="B137" t="s">
+        <v>46</v>
+      </c>
+      <c r="C137" t="s">
+        <v>66</v>
+      </c>
+      <c r="D137">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E137">
+        <v>95</v>
+      </c>
+      <c r="F137">
+        <v>929.1</v>
+      </c>
+      <c r="G137" t="s">
+        <v>82</v>
+      </c>
+      <c r="H137" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>11</v>
+      </c>
+      <c r="B138" t="s">
+        <v>47</v>
+      </c>
+      <c r="C138" t="s">
+        <v>65</v>
+      </c>
+      <c r="D138">
+        <v>11.125</v>
+      </c>
+      <c r="E138">
+        <v>95</v>
+      </c>
+      <c r="F138">
+        <v>1056.88</v>
+      </c>
+      <c r="H138" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" t="s">
+        <v>48</v>
+      </c>
+      <c r="C139" t="s">
+        <v>65</v>
+      </c>
+      <c r="D139">
+        <v>10.439</v>
+      </c>
+      <c r="E139">
+        <v>115</v>
+      </c>
+      <c r="F139">
+        <v>1200.48</v>
+      </c>
+      <c r="H139" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>11</v>
+      </c>
+      <c r="B140" t="s">
+        <v>49</v>
+      </c>
+      <c r="C140" t="s">
+        <v>65</v>
+      </c>
+      <c r="D140">
+        <v>7.174</v>
+      </c>
+      <c r="E140">
+        <v>115</v>
+      </c>
+      <c r="F140">
+        <v>825.01</v>
+      </c>
+      <c r="H140" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>11</v>
+      </c>
+      <c r="B141" t="s">
+        <v>50</v>
+      </c>
+      <c r="C141" t="s">
+        <v>66</v>
+      </c>
+      <c r="D141">
+        <v>8.738</v>
+      </c>
+      <c r="E141">
+        <v>60</v>
+      </c>
+      <c r="F141">
+        <v>524.28</v>
+      </c>
+      <c r="G141" t="s">
+        <v>82</v>
+      </c>
+      <c r="H141" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -331,11 +336,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,6 +404,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -445,7 +458,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -477,9 +490,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -511,6 +525,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -686,11 +701,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H141"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -716,7 +734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45376</v>
       </c>
@@ -739,7 +757,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45376</v>
       </c>
@@ -750,19 +768,19 @@
         <v>65</v>
       </c>
       <c r="D3">
-        <v>9.135</v>
+        <v>9.1349999999999998</v>
       </c>
       <c r="E3">
         <v>70</v>
       </c>
       <c r="F3">
-        <v>639.4499999999999</v>
+        <v>639.44999999999993</v>
       </c>
       <c r="H3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45376</v>
       </c>
@@ -785,7 +803,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45376</v>
       </c>
@@ -796,19 +814,19 @@
         <v>67</v>
       </c>
       <c r="D5">
-        <v>16.342</v>
+        <v>16.341999999999999</v>
       </c>
       <c r="E5">
         <v>34.08701505323706</v>
       </c>
       <c r="F5">
-        <v>557.05</v>
+        <v>557.04999999999995</v>
       </c>
       <c r="H5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45376</v>
       </c>
@@ -819,10 +837,10 @@
         <v>65</v>
       </c>
       <c r="D6">
-        <v>17.328</v>
+        <v>17.327999999999999</v>
       </c>
       <c r="E6">
-        <v>85.00000000000001</v>
+        <v>85.000000000000014</v>
       </c>
       <c r="F6">
         <v>1472.88</v>
@@ -831,7 +849,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45376</v>
       </c>
@@ -842,19 +860,19 @@
         <v>66</v>
       </c>
       <c r="D7">
-        <v>15.697</v>
+        <v>15.696999999999999</v>
       </c>
       <c r="E7">
-        <v>93.43855513792444</v>
+        <v>93.438555137924439</v>
       </c>
       <c r="F7">
-        <v>1466.705</v>
+        <v>1466.7049999999999</v>
       </c>
       <c r="H7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45376</v>
       </c>
@@ -865,10 +883,10 @@
         <v>68</v>
       </c>
       <c r="D8">
-        <v>19.281</v>
+        <v>19.280999999999999</v>
       </c>
       <c r="E8">
-        <v>84.52932939162906</v>
+        <v>84.529329391629062</v>
       </c>
       <c r="F8">
         <v>1629.81</v>
@@ -877,7 +895,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45376</v>
       </c>
@@ -891,7 +909,7 @@
         <v>17.605</v>
       </c>
       <c r="E9">
-        <v>77.81425731326328</v>
+        <v>77.814257313263283</v>
       </c>
       <c r="F9">
         <v>1369.92</v>
@@ -900,7 +918,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45376</v>
       </c>
@@ -917,13 +935,13 @@
         <v>75</v>
       </c>
       <c r="F10">
-        <v>2377.95</v>
+        <v>2377.9499999999998</v>
       </c>
       <c r="H10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45376</v>
       </c>
@@ -946,7 +964,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45376</v>
       </c>
@@ -957,19 +975,19 @@
         <v>69</v>
       </c>
       <c r="D12">
-        <v>42.033</v>
+        <v>42.033000000000001</v>
       </c>
       <c r="E12">
-        <v>90.00000000000003</v>
+        <v>90.000000000000028</v>
       </c>
       <c r="F12">
-        <v>3782.970000000001</v>
+        <v>3782.9700000000012</v>
       </c>
       <c r="H12" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45376</v>
       </c>
@@ -980,10 +998,10 @@
         <v>64</v>
       </c>
       <c r="D13">
-        <v>23.658</v>
+        <v>23.658000000000001</v>
       </c>
       <c r="E13">
-        <v>74.99999999999999</v>
+        <v>74.999999999999986</v>
       </c>
       <c r="F13">
         <v>1774.35</v>
@@ -992,7 +1010,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45376</v>
       </c>
@@ -1003,10 +1021,10 @@
         <v>66</v>
       </c>
       <c r="D14">
-        <v>33.844</v>
+        <v>33.844000000000001</v>
       </c>
       <c r="E14">
-        <v>92.40792724006288</v>
+        <v>92.407927240062875</v>
       </c>
       <c r="F14">
         <v>3291.94</v>
@@ -1015,7 +1033,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45376</v>
       </c>
@@ -1029,7 +1047,7 @@
         <v>14.504</v>
       </c>
       <c r="E15">
-        <v>50.00000000000001</v>
+        <v>50.000000000000007</v>
       </c>
       <c r="F15">
         <v>725.2</v>
@@ -1038,7 +1056,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45376</v>
       </c>
@@ -1061,7 +1079,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45376</v>
       </c>
@@ -1072,19 +1090,19 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>4.195</v>
+        <v>4.1950000000000003</v>
       </c>
       <c r="E17">
-        <v>84.99999999999999</v>
+        <v>84.999999999999986</v>
       </c>
       <c r="F17">
-        <v>356.575</v>
+        <v>356.57499999999999</v>
       </c>
       <c r="H17" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45376</v>
       </c>
@@ -1095,7 +1113,7 @@
         <v>67</v>
       </c>
       <c r="D18">
-        <v>16.079</v>
+        <v>16.079000000000001</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1107,7 +1125,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45376</v>
       </c>
@@ -1124,13 +1142,13 @@
         <v>90</v>
       </c>
       <c r="F19">
-        <v>1265.85</v>
+        <v>1265.8499999999999</v>
       </c>
       <c r="H19" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>45376</v>
       </c>
@@ -1141,7 +1159,7 @@
         <v>66</v>
       </c>
       <c r="D20">
-        <v>16.889</v>
+        <v>16.888999999999999</v>
       </c>
       <c r="E20">
         <v>70</v>
@@ -1153,7 +1171,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>45376</v>
       </c>
@@ -1164,7 +1182,7 @@
         <v>65</v>
       </c>
       <c r="D21">
-        <v>23.147</v>
+        <v>23.146999999999998</v>
       </c>
       <c r="E21">
         <v>70</v>
@@ -1176,7 +1194,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>45376</v>
       </c>
@@ -1190,16 +1208,16 @@
         <v>18.552</v>
       </c>
       <c r="E22">
-        <v>59.99999999999999</v>
+        <v>59.999999999999993</v>
       </c>
       <c r="F22">
-        <v>1113.12</v>
+        <v>1113.1199999999999</v>
       </c>
       <c r="H22" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>45376</v>
       </c>
@@ -1210,10 +1228,10 @@
         <v>67</v>
       </c>
       <c r="D23">
-        <v>24.804</v>
+        <v>24.803999999999998</v>
       </c>
       <c r="E23">
-        <v>90.00000000000001</v>
+        <v>90.000000000000014</v>
       </c>
       <c r="F23">
         <v>2232.36</v>
@@ -1222,7 +1240,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>45376</v>
       </c>
@@ -1233,10 +1251,10 @@
         <v>66</v>
       </c>
       <c r="D24">
-        <v>19.15</v>
+        <v>19.149999999999999</v>
       </c>
       <c r="E24">
-        <v>55.00000000000001</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="F24">
         <v>1053.25</v>
@@ -1245,7 +1263,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45376</v>
       </c>
@@ -1256,19 +1274,19 @@
         <v>67</v>
       </c>
       <c r="D25">
-        <v>25.193</v>
+        <v>25.193000000000001</v>
       </c>
       <c r="E25">
-        <v>81.62604691779462</v>
+        <v>81.626046917794625</v>
       </c>
       <c r="F25">
-        <v>2056.405</v>
+        <v>2056.4050000000002</v>
       </c>
       <c r="H25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>45376</v>
       </c>
@@ -1279,7 +1297,7 @@
         <v>66</v>
       </c>
       <c r="D26">
-        <v>18.325</v>
+        <v>18.324999999999999</v>
       </c>
       <c r="E26">
         <v>80</v>
@@ -1291,7 +1309,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>45376</v>
       </c>
@@ -1302,19 +1320,19 @@
         <v>65</v>
       </c>
       <c r="D27">
-        <v>24.107</v>
+        <v>24.106999999999999</v>
       </c>
       <c r="E27">
         <v>75</v>
       </c>
       <c r="F27">
-        <v>1808.025</v>
+        <v>1808.0250000000001</v>
       </c>
       <c r="H27" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>45376</v>
       </c>
@@ -1328,16 +1346,16 @@
         <v>13.993</v>
       </c>
       <c r="E28">
-        <v>89.99999999999999</v>
+        <v>89.999999999999986</v>
       </c>
       <c r="F28">
-        <v>1259.37</v>
+        <v>1259.3699999999999</v>
       </c>
       <c r="H28" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>45376</v>
       </c>
@@ -1348,19 +1366,19 @@
         <v>66</v>
       </c>
       <c r="D29">
-        <v>23.162</v>
+        <v>23.161999999999999</v>
       </c>
       <c r="E29">
         <v>50</v>
       </c>
       <c r="F29">
-        <v>1158.1</v>
+        <v>1158.0999999999999</v>
       </c>
       <c r="H29" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>45376</v>
       </c>
@@ -1374,7 +1392,7 @@
         <v>8.423</v>
       </c>
       <c r="E30">
-        <v>95.13949899085837</v>
+        <v>95.139498990858371</v>
       </c>
       <c r="F30">
         <v>801.36</v>
@@ -1383,7 +1401,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>45376</v>
       </c>
@@ -1394,10 +1412,10 @@
         <v>66</v>
       </c>
       <c r="D31">
-        <v>21.858</v>
+        <v>21.858000000000001</v>
       </c>
       <c r="E31">
-        <v>43.04373684692104</v>
+        <v>43.043736846921043</v>
       </c>
       <c r="F31">
         <v>940.85</v>
@@ -1406,7 +1424,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>45376</v>
       </c>
@@ -1417,7 +1435,7 @@
         <v>67</v>
       </c>
       <c r="D32">
-        <v>25.047</v>
+        <v>25.047000000000001</v>
       </c>
       <c r="E32">
         <v>90</v>
@@ -1429,7 +1447,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>45376</v>
       </c>
@@ -1440,7 +1458,7 @@
         <v>67</v>
       </c>
       <c r="D33">
-        <v>21.138</v>
+        <v>21.138000000000002</v>
       </c>
       <c r="E33">
         <v>70</v>
@@ -1452,7 +1470,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>45376</v>
       </c>
@@ -1463,7 +1481,7 @@
         <v>65</v>
       </c>
       <c r="D34">
-        <v>24.543</v>
+        <v>24.542999999999999</v>
       </c>
       <c r="E34">
         <v>80</v>
@@ -1475,7 +1493,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>45376</v>
       </c>
@@ -1486,10 +1504,10 @@
         <v>67</v>
       </c>
       <c r="D35">
-        <v>12.796</v>
+        <v>12.795999999999999</v>
       </c>
       <c r="E35">
-        <v>78.78086902156925</v>
+        <v>78.780869021569245</v>
       </c>
       <c r="F35">
         <v>1008.08</v>
@@ -1498,7 +1516,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>45376</v>
       </c>
@@ -1509,19 +1527,19 @@
         <v>66</v>
       </c>
       <c r="D36">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="E36">
         <v>60</v>
       </c>
       <c r="F36">
-        <v>586.8</v>
+        <v>586.79999999999995</v>
       </c>
       <c r="H36" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>45376</v>
       </c>
@@ -1544,7 +1562,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>45376</v>
       </c>
@@ -1567,7 +1585,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>45376</v>
       </c>
@@ -1578,10 +1596,10 @@
         <v>65</v>
       </c>
       <c r="D39">
-        <v>7.174</v>
+        <v>7.1740000000000004</v>
       </c>
       <c r="E39">
-        <v>89.99999999999999</v>
+        <v>89.999999999999986</v>
       </c>
       <c r="F39">
         <v>645.66</v>
@@ -1590,7 +1608,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>45376</v>
       </c>
@@ -1601,7 +1619,7 @@
         <v>66</v>
       </c>
       <c r="D40">
-        <v>8.738</v>
+        <v>8.7379999999999995</v>
       </c>
       <c r="E40">
         <v>65</v>
@@ -1613,7 +1631,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>45376</v>
       </c>
@@ -1627,16 +1645,16 @@
         <v>13.321</v>
       </c>
       <c r="E41">
-        <v>54.99999999999999</v>
+        <v>54.999999999999993</v>
       </c>
       <c r="F41">
-        <v>732.6549999999999</v>
+        <v>732.65499999999986</v>
       </c>
       <c r="H41" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>45376</v>
       </c>
@@ -1647,7 +1665,7 @@
         <v>66</v>
       </c>
       <c r="D42">
-        <v>18.931</v>
+        <v>18.931000000000001</v>
       </c>
       <c r="E42">
         <v>45</v>
@@ -1659,7 +1677,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>45376</v>
       </c>
@@ -1682,7 +1700,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>45376</v>
       </c>
@@ -1693,19 +1711,19 @@
         <v>67</v>
       </c>
       <c r="D44">
-        <v>25.214</v>
+        <v>25.213999999999999</v>
       </c>
       <c r="E44">
-        <v>35.33909732688188</v>
+        <v>35.339097326881877</v>
       </c>
       <c r="F44">
-        <v>891.0399999999998</v>
+        <v>891.03999999999985</v>
       </c>
       <c r="H44" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45376</v>
       </c>
@@ -1716,19 +1734,19 @@
         <v>67</v>
       </c>
       <c r="D45">
-        <v>7.445</v>
+        <v>7.4450000000000003</v>
       </c>
       <c r="E45">
-        <v>44.99999999999999</v>
+        <v>44.999999999999993</v>
       </c>
       <c r="F45">
-        <v>335.025</v>
+        <v>335.02499999999998</v>
       </c>
       <c r="H45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45376</v>
       </c>
@@ -1742,7 +1760,7 @@
         <v>1.27</v>
       </c>
       <c r="E46">
-        <v>56.48031496062993</v>
+        <v>56.480314960629933</v>
       </c>
       <c r="F46">
         <v>71.73</v>
@@ -1751,7 +1769,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>45376</v>
       </c>
@@ -1762,7 +1780,7 @@
         <v>67</v>
       </c>
       <c r="D47">
-        <v>2.885</v>
+        <v>2.8849999999999998</v>
       </c>
       <c r="E47">
         <v>30</v>
@@ -1774,7 +1792,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45376</v>
       </c>
@@ -1794,7 +1812,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>45376</v>
       </c>
@@ -1808,7 +1826,7 @@
         <v>15.798</v>
       </c>
       <c r="E49">
-        <v>34.53854918344094</v>
+        <v>34.538549183440942</v>
       </c>
       <c r="F49">
         <v>545.64</v>
@@ -1817,7 +1835,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>45376</v>
       </c>
@@ -1828,19 +1846,19 @@
         <v>67</v>
       </c>
       <c r="D50">
-        <v>5.345</v>
+        <v>5.3449999999999998</v>
       </c>
       <c r="E50">
-        <v>24.65855940130964</v>
+        <v>24.658559401309638</v>
       </c>
       <c r="F50">
-        <v>131.8</v>
+        <v>131.80000000000001</v>
       </c>
       <c r="H50" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>45376</v>
       </c>
@@ -1851,10 +1869,10 @@
         <v>66</v>
       </c>
       <c r="D51">
-        <v>4.094</v>
+        <v>4.0940000000000003</v>
       </c>
       <c r="E51">
-        <v>47.93600390815828</v>
+        <v>47.936003908158277</v>
       </c>
       <c r="F51">
         <v>196.25</v>
@@ -1863,7 +1881,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>45376</v>
       </c>
@@ -1883,7 +1901,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>45376</v>
       </c>
@@ -1897,7 +1915,7 @@
         <v>3.07</v>
       </c>
       <c r="E53">
-        <v>48.371335504886</v>
+        <v>48.371335504885998</v>
       </c>
       <c r="F53">
         <v>148.5</v>
@@ -1906,7 +1924,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>45736</v>
       </c>
@@ -1923,7 +1941,7 @@
         <v>105</v>
       </c>
       <c r="F54">
-        <v>2067.03</v>
+        <v>2067.0300000000002</v>
       </c>
       <c r="G54" t="s">
         <v>70</v>
@@ -1932,7 +1950,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>45736</v>
       </c>
@@ -1943,7 +1961,7 @@
         <v>68</v>
       </c>
       <c r="D55">
-        <v>9.135</v>
+        <v>9.1349999999999998</v>
       </c>
       <c r="E55">
         <v>88</v>
@@ -1958,7 +1976,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>45736</v>
       </c>
@@ -1972,7 +1990,7 @@
         <v>11.3</v>
       </c>
       <c r="E56">
-        <v>89.89999999999999</v>
+        <v>89.899999999999991</v>
       </c>
       <c r="F56">
         <v>1015.87</v>
@@ -1984,7 +2002,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>45736</v>
       </c>
@@ -1998,10 +2016,10 @@
         <v>11.141</v>
       </c>
       <c r="E57">
-        <v>89.92505670052263</v>
+        <v>89.925056700522632</v>
       </c>
       <c r="F57">
-        <v>911.9299999999999</v>
+        <v>911.93</v>
       </c>
       <c r="G57" t="s">
         <v>73</v>
@@ -2010,7 +2028,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>45736</v>
       </c>
@@ -2021,10 +2039,10 @@
         <v>65</v>
       </c>
       <c r="D58">
-        <v>17.328</v>
+        <v>17.327999999999999</v>
       </c>
       <c r="E58">
-        <v>96.00011542012928</v>
+        <v>96.000115420129276</v>
       </c>
       <c r="F58">
         <v>1663.49</v>
@@ -2036,7 +2054,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -2050,7 +2068,7 @@
         <v>15.439</v>
       </c>
       <c r="E59">
-        <v>97.99987045793121</v>
+        <v>97.999870457931209</v>
       </c>
       <c r="F59">
         <v>1513.02</v>
@@ -2059,7 +2077,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2103,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -2096,10 +2114,10 @@
         <v>66</v>
       </c>
       <c r="D61">
-        <v>17.124</v>
+        <v>17.123999999999999</v>
       </c>
       <c r="E61">
-        <v>90.00000000000001</v>
+        <v>90.000000000000014</v>
       </c>
       <c r="F61">
         <v>1541.16</v>
@@ -2108,7 +2126,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -2131,7 +2149,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>8</v>
       </c>
@@ -2154,7 +2172,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -2165,7 +2183,7 @@
         <v>69</v>
       </c>
       <c r="D64">
-        <v>41.633</v>
+        <v>41.633000000000003</v>
       </c>
       <c r="E64">
         <v>105.0001189541551</v>
@@ -2177,7 +2195,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -2188,7 +2206,7 @@
         <v>64</v>
       </c>
       <c r="D65">
-        <v>23.658</v>
+        <v>23.658000000000001</v>
       </c>
       <c r="E65">
         <v>80</v>
@@ -2200,7 +2218,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -2211,10 +2229,10 @@
         <v>66</v>
       </c>
       <c r="D66">
-        <v>33.844</v>
+        <v>33.844000000000001</v>
       </c>
       <c r="E66">
-        <v>99.99999999999999</v>
+        <v>99.999999999999986</v>
       </c>
       <c r="F66">
         <v>3465.2</v>
@@ -2226,7 +2244,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -2240,7 +2258,7 @@
         <v>14.504</v>
       </c>
       <c r="E67">
-        <v>62.00013789299503</v>
+        <v>62.000137892995028</v>
       </c>
       <c r="F67">
         <v>899.25</v>
@@ -2249,7 +2267,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -2275,7 +2293,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -2286,7 +2304,7 @@
         <v>68</v>
       </c>
       <c r="D69">
-        <v>4.195</v>
+        <v>4.1950000000000003</v>
       </c>
       <c r="E69">
         <v>112</v>
@@ -2301,7 +2319,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -2312,7 +2330,7 @@
         <v>67</v>
       </c>
       <c r="D70">
-        <v>16.079</v>
+        <v>16.079000000000001</v>
       </c>
       <c r="E70">
         <v>50</v>
@@ -2324,7 +2342,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -2338,7 +2356,7 @@
         <v>14.065</v>
       </c>
       <c r="E71">
-        <v>95.00035549235692</v>
+        <v>95.000355492356917</v>
       </c>
       <c r="F71">
         <v>1336.18</v>
@@ -2347,7 +2365,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>8</v>
       </c>
@@ -2358,7 +2376,7 @@
         <v>66</v>
       </c>
       <c r="D72">
-        <v>16.889</v>
+        <v>16.888999999999999</v>
       </c>
       <c r="E72">
         <v>70</v>
@@ -2370,7 +2388,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -2381,10 +2399,10 @@
         <v>66</v>
       </c>
       <c r="D73">
-        <v>22.912</v>
+        <v>22.911999999999999</v>
       </c>
       <c r="E73">
-        <v>58.56007257959995</v>
+        <v>58.560072579599947</v>
       </c>
       <c r="F73">
         <v>1355.49</v>
@@ -2396,7 +2414,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -2419,7 +2437,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -2430,10 +2448,10 @@
         <v>67</v>
       </c>
       <c r="D75">
-        <v>24.804</v>
+        <v>24.803999999999998</v>
       </c>
       <c r="E75">
-        <v>82.00008063215611</v>
+        <v>82.000080632156113</v>
       </c>
       <c r="F75">
         <v>2033.93</v>
@@ -2442,7 +2460,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -2453,10 +2471,10 @@
         <v>66</v>
       </c>
       <c r="D76">
-        <v>19.15</v>
+        <v>19.149999999999999</v>
       </c>
       <c r="E76">
-        <v>50.00000000000001</v>
+        <v>50.000000000000007</v>
       </c>
       <c r="F76">
         <v>957.5</v>
@@ -2465,7 +2483,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -2476,7 +2494,7 @@
         <v>64</v>
       </c>
       <c r="D77">
-        <v>25.193</v>
+        <v>25.193000000000001</v>
       </c>
       <c r="E77">
         <v>80</v>
@@ -2488,7 +2506,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -2499,7 +2517,7 @@
         <v>66</v>
       </c>
       <c r="D78">
-        <v>18.325</v>
+        <v>18.324999999999999</v>
       </c>
       <c r="E78">
         <v>70</v>
@@ -2511,7 +2529,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -2522,7 +2540,7 @@
         <v>65</v>
       </c>
       <c r="D79">
-        <v>24.107</v>
+        <v>24.106999999999999</v>
       </c>
       <c r="E79">
         <v>70</v>
@@ -2534,7 +2552,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -2548,10 +2566,10 @@
         <v>13.993</v>
       </c>
       <c r="E80">
-        <v>86.99992853569643</v>
+        <v>86.999928535696426</v>
       </c>
       <c r="F80">
-        <v>1217.39</v>
+        <v>1217.3900000000001</v>
       </c>
       <c r="G80" t="s">
         <v>76</v>
@@ -2560,7 +2578,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -2571,7 +2589,7 @@
         <v>66</v>
       </c>
       <c r="D81">
-        <v>23.162</v>
+        <v>23.161999999999999</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2586,7 +2604,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -2597,7 +2615,7 @@
         <v>66</v>
       </c>
       <c r="D82">
-        <v>8.904</v>
+        <v>8.9039999999999999</v>
       </c>
       <c r="E82">
         <v>100</v>
@@ -2609,7 +2627,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -2620,7 +2638,7 @@
         <v>66</v>
       </c>
       <c r="D83">
-        <v>21.858</v>
+        <v>21.858000000000001</v>
       </c>
       <c r="E83">
         <v>70</v>
@@ -2635,7 +2653,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -2646,7 +2664,7 @@
         <v>67</v>
       </c>
       <c r="D84">
-        <v>25.047</v>
+        <v>25.047000000000001</v>
       </c>
       <c r="E84">
         <v>90</v>
@@ -2658,7 +2676,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>9</v>
       </c>
@@ -2669,7 +2687,7 @@
         <v>67</v>
       </c>
       <c r="D85">
-        <v>21.138</v>
+        <v>21.138000000000002</v>
       </c>
       <c r="E85">
         <v>85</v>
@@ -2681,7 +2699,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>9</v>
       </c>
@@ -2692,7 +2710,7 @@
         <v>65</v>
       </c>
       <c r="D86">
-        <v>24.543</v>
+        <v>24.542999999999999</v>
       </c>
       <c r="E86">
         <v>80</v>
@@ -2704,7 +2722,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
@@ -2715,13 +2733,13 @@
         <v>68</v>
       </c>
       <c r="D87">
-        <v>12.578</v>
+        <v>12.577999999999999</v>
       </c>
       <c r="E87">
-        <v>90.16030473771922</v>
+        <v>90.160304737719215</v>
       </c>
       <c r="F87">
-        <v>1136.11</v>
+        <v>1136.1099999999999</v>
       </c>
       <c r="G87" t="s">
         <v>75</v>
@@ -2730,7 +2748,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>9</v>
       </c>
@@ -2741,7 +2759,7 @@
         <v>66</v>
       </c>
       <c r="D88">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="E88">
         <v>70</v>
@@ -2756,7 +2774,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>9</v>
       </c>
@@ -2770,7 +2788,7 @@
         <v>11.125</v>
       </c>
       <c r="E89">
-        <v>79.90022471910112</v>
+        <v>79.900224719101118</v>
       </c>
       <c r="F89">
         <v>888.89</v>
@@ -2782,7 +2800,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
@@ -2799,13 +2817,13 @@
         <v>100</v>
       </c>
       <c r="F90">
-        <v>1043.9</v>
+        <v>1043.9000000000001</v>
       </c>
       <c r="H90" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>9</v>
       </c>
@@ -2816,10 +2834,10 @@
         <v>65</v>
       </c>
       <c r="D91">
-        <v>7.174</v>
+        <v>7.1740000000000004</v>
       </c>
       <c r="E91">
-        <v>99.99999999999999</v>
+        <v>99.999999999999986</v>
       </c>
       <c r="F91">
         <v>717.4</v>
@@ -2828,7 +2846,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>9</v>
       </c>
@@ -2839,7 +2857,7 @@
         <v>66</v>
       </c>
       <c r="D92">
-        <v>8.738</v>
+        <v>8.7379999999999995</v>
       </c>
       <c r="E92">
         <v>50</v>
@@ -2854,7 +2872,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>9</v>
       </c>
@@ -2877,7 +2895,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>9</v>
       </c>
@@ -2888,7 +2906,7 @@
         <v>66</v>
       </c>
       <c r="D94">
-        <v>13.906</v>
+        <v>13.906000000000001</v>
       </c>
       <c r="E94">
         <v>30</v>
@@ -2903,7 +2921,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>9</v>
       </c>
@@ -2914,7 +2932,7 @@
         <v>67</v>
       </c>
       <c r="D95">
-        <v>2.446</v>
+        <v>2.4460000000000002</v>
       </c>
       <c r="E95">
         <v>40</v>
@@ -2929,7 +2947,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
@@ -2955,7 +2973,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -2966,10 +2984,10 @@
         <v>67</v>
       </c>
       <c r="D97">
-        <v>7.445</v>
+        <v>7.4450000000000003</v>
       </c>
       <c r="E97">
-        <v>35.00067159167226</v>
+        <v>35.000671591672258</v>
       </c>
       <c r="F97">
         <v>260.58</v>
@@ -2978,7 +2996,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>9</v>
       </c>
@@ -3004,7 +3022,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -3015,19 +3033,19 @@
         <v>67</v>
       </c>
       <c r="D99">
-        <v>2.885</v>
+        <v>2.8849999999999998</v>
       </c>
       <c r="E99">
-        <v>45.00173310225304</v>
+        <v>45.001733102253041</v>
       </c>
       <c r="F99">
-        <v>129.83</v>
+        <v>129.83000000000001</v>
       </c>
       <c r="H99" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>9</v>
       </c>
@@ -3050,7 +3068,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>9</v>
       </c>
@@ -3061,7 +3079,7 @@
         <v>67</v>
       </c>
       <c r="D101">
-        <v>1.912</v>
+        <v>1.9119999999999999</v>
       </c>
       <c r="E101">
         <v>25</v>
@@ -3073,7 +3091,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>9</v>
       </c>
@@ -3084,10 +3102,10 @@
         <v>64</v>
       </c>
       <c r="D102">
-        <v>3.925</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="E102">
-        <v>55.00127388535032</v>
+        <v>55.001273885350322</v>
       </c>
       <c r="F102">
         <v>215.88</v>
@@ -3096,7 +3114,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -3110,7 +3128,7 @@
         <v>3.069</v>
       </c>
       <c r="E103">
-        <v>55.00162919517759</v>
+        <v>55.001629195177593</v>
       </c>
       <c r="F103">
         <v>168.8</v>
@@ -3119,7 +3137,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -3145,7 +3163,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>10</v>
       </c>
@@ -3156,7 +3174,7 @@
         <v>68</v>
       </c>
       <c r="D105">
-        <v>9.135</v>
+        <v>9.1349999999999998</v>
       </c>
       <c r="E105">
         <v>98</v>
@@ -3171,7 +3189,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -3197,7 +3215,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>10</v>
       </c>
@@ -3208,13 +3226,13 @@
         <v>65</v>
       </c>
       <c r="D107">
-        <v>11.141</v>
+        <v>16.341999999999999</v>
       </c>
       <c r="E107">
         <v>120</v>
       </c>
       <c r="F107">
-        <v>1336.92</v>
+        <v>1961.04</v>
       </c>
       <c r="G107" t="s">
         <v>83</v>
@@ -3223,7 +3241,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>10</v>
       </c>
@@ -3234,7 +3252,7 @@
         <v>65</v>
       </c>
       <c r="D108">
-        <v>17.328</v>
+        <v>17.327999999999999</v>
       </c>
       <c r="E108">
         <v>105</v>
@@ -3249,7 +3267,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>10</v>
       </c>
@@ -3275,7 +3293,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>10</v>
       </c>
@@ -3292,7 +3310,7 @@
         <v>110</v>
       </c>
       <c r="F110">
-        <v>2078.45</v>
+        <v>2078.4499999999998</v>
       </c>
       <c r="G110" t="s">
         <v>85</v>
@@ -3301,7 +3319,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>10</v>
       </c>
@@ -3312,7 +3330,7 @@
         <v>66</v>
       </c>
       <c r="D111">
-        <v>17.124</v>
+        <v>17.123999999999999</v>
       </c>
       <c r="E111">
         <v>103</v>
@@ -3327,7 +3345,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>10</v>
       </c>
@@ -3353,7 +3371,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>10</v>
       </c>
@@ -3370,7 +3388,7 @@
         <v>93</v>
       </c>
       <c r="F113">
-        <v>1996.24</v>
+        <v>1996.25</v>
       </c>
       <c r="G113" t="s">
         <v>88</v>
@@ -3379,7 +3397,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -3390,13 +3408,13 @@
         <v>69</v>
       </c>
       <c r="D114">
-        <v>41.633</v>
+        <v>42.033000000000001</v>
       </c>
       <c r="E114">
         <v>110</v>
       </c>
       <c r="F114">
-        <v>4579.63</v>
+        <v>4623.63</v>
       </c>
       <c r="G114" t="s">
         <v>89</v>
@@ -3405,7 +3423,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -3416,7 +3434,7 @@
         <v>66</v>
       </c>
       <c r="D115">
-        <v>33.844</v>
+        <v>33.844000000000001</v>
       </c>
       <c r="E115">
         <v>130</v>
@@ -3431,7 +3449,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -3457,7 +3475,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -3480,7 +3498,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -3491,7 +3509,7 @@
         <v>68</v>
       </c>
       <c r="D118">
-        <v>4.195</v>
+        <v>4.1950000000000003</v>
       </c>
       <c r="E118">
         <v>125</v>
@@ -3506,7 +3524,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -3517,13 +3535,13 @@
         <v>67</v>
       </c>
       <c r="D119">
-        <v>16.079</v>
+        <v>16.079000000000001</v>
       </c>
       <c r="E119">
         <v>61</v>
       </c>
       <c r="F119">
-        <v>980.8200000000001</v>
+        <v>980.82</v>
       </c>
       <c r="G119" t="s">
         <v>92</v>
@@ -3532,7 +3550,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -3558,7 +3576,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -3569,7 +3587,7 @@
         <v>66</v>
       </c>
       <c r="D121">
-        <v>16.889</v>
+        <v>16.888999999999999</v>
       </c>
       <c r="E121">
         <v>46</v>
@@ -3584,7 +3602,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -3595,13 +3613,13 @@
         <v>66</v>
       </c>
       <c r="D122">
-        <v>22.912</v>
+        <v>22.911999999999999</v>
       </c>
       <c r="E122">
         <v>110</v>
       </c>
       <c r="F122">
-        <v>2520.32</v>
+        <v>2520.3200000000002</v>
       </c>
       <c r="G122" t="s">
         <v>95</v>
@@ -3610,7 +3628,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -3633,7 +3651,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3644,7 +3662,7 @@
         <v>67</v>
       </c>
       <c r="D124">
-        <v>24.804</v>
+        <v>24.803999999999998</v>
       </c>
       <c r="E124">
         <v>83</v>
@@ -3656,7 +3674,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -3667,7 +3685,7 @@
         <v>66</v>
       </c>
       <c r="D125">
-        <v>19.15</v>
+        <v>19.149999999999999</v>
       </c>
       <c r="E125">
         <v>55</v>
@@ -3679,7 +3697,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -3690,7 +3708,7 @@
         <v>64</v>
       </c>
       <c r="D126">
-        <v>25.193</v>
+        <v>25.193000000000001</v>
       </c>
       <c r="E126">
         <v>80</v>
@@ -3702,7 +3720,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -3713,7 +3731,7 @@
         <v>66</v>
       </c>
       <c r="D127">
-        <v>18.325</v>
+        <v>18.324999999999999</v>
       </c>
       <c r="E127">
         <v>90</v>
@@ -3725,7 +3743,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -3736,7 +3754,7 @@
         <v>65</v>
       </c>
       <c r="D128">
-        <v>24.107</v>
+        <v>24.106999999999999</v>
       </c>
       <c r="E128">
         <v>65</v>
@@ -3751,7 +3769,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -3777,7 +3795,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>11</v>
       </c>
@@ -3788,7 +3806,7 @@
         <v>66</v>
       </c>
       <c r="D130">
-        <v>23.162</v>
+        <v>23.161999999999999</v>
       </c>
       <c r="E130">
         <v>65</v>
@@ -3803,7 +3821,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>11</v>
       </c>
@@ -3814,13 +3832,13 @@
         <v>66</v>
       </c>
       <c r="D131">
-        <v>8.904</v>
+        <v>8.9039999999999999</v>
       </c>
       <c r="E131">
         <v>106</v>
       </c>
       <c r="F131">
-        <v>943.8200000000001</v>
+        <v>943.82</v>
       </c>
       <c r="G131" t="s">
         <v>99</v>
@@ -3829,7 +3847,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>11</v>
       </c>
@@ -3840,7 +3858,7 @@
         <v>66</v>
       </c>
       <c r="D132">
-        <v>21.858</v>
+        <v>21.858000000000001</v>
       </c>
       <c r="E132">
         <v>75</v>
@@ -3852,7 +3870,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>11</v>
       </c>
@@ -3863,7 +3881,7 @@
         <v>67</v>
       </c>
       <c r="D133">
-        <v>25.047</v>
+        <v>25.047000000000001</v>
       </c>
       <c r="E133">
         <v>97</v>
@@ -3875,7 +3893,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>11</v>
       </c>
@@ -3886,7 +3904,7 @@
         <v>67</v>
       </c>
       <c r="D134">
-        <v>21.138</v>
+        <v>21.138000000000002</v>
       </c>
       <c r="E134">
         <v>92</v>
@@ -3901,7 +3919,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>11</v>
       </c>
@@ -3912,7 +3930,7 @@
         <v>65</v>
       </c>
       <c r="D135">
-        <v>24.543</v>
+        <v>24.542999999999999</v>
       </c>
       <c r="E135">
         <v>95</v>
@@ -3924,7 +3942,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>11</v>
       </c>
@@ -3935,19 +3953,19 @@
         <v>68</v>
       </c>
       <c r="D136">
-        <v>12.578</v>
+        <v>12.601000000000001</v>
       </c>
       <c r="E136">
         <v>105</v>
       </c>
       <c r="F136">
-        <v>1320.69</v>
+        <v>1323.11</v>
       </c>
       <c r="H136" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>11</v>
       </c>
@@ -3958,7 +3976,7 @@
         <v>66</v>
       </c>
       <c r="D137">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="E137">
         <v>95</v>
@@ -3973,7 +3991,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>11</v>
       </c>
@@ -3990,13 +4008,13 @@
         <v>95</v>
       </c>
       <c r="F138">
-        <v>1056.88</v>
+        <v>1056.8800000000001</v>
       </c>
       <c r="H138" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>11</v>
       </c>
@@ -4013,13 +4031,13 @@
         <v>115</v>
       </c>
       <c r="F139">
-        <v>1200.48</v>
+        <v>1200.49</v>
       </c>
       <c r="H139" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>11</v>
       </c>
@@ -4030,7 +4048,7 @@
         <v>65</v>
       </c>
       <c r="D140">
-        <v>7.174</v>
+        <v>7.1740000000000004</v>
       </c>
       <c r="E140">
         <v>115</v>
@@ -4042,7 +4060,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>11</v>
       </c>
@@ -4053,7 +4071,7 @@
         <v>66</v>
       </c>
       <c r="D141">
-        <v>8.738</v>
+        <v>8.7379999999999995</v>
       </c>
       <c r="E141">
         <v>60</v>

--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -331,16 +331,47 @@
   </si>
   <si>
     <t>2026/27</t>
+  </si>
+  <si>
+    <t>2020/21</t>
+  </si>
+  <si>
+    <t>2021/22</t>
+  </si>
+  <si>
+    <t>2022/23</t>
+  </si>
+  <si>
+    <t>2023/24</t>
+  </si>
+  <si>
+    <t>2020-01-28</t>
+  </si>
+  <si>
+    <t>2021-01-30</t>
+  </si>
+  <si>
+    <t>2022-01-27</t>
+  </si>
+  <si>
+    <t>2023-01-26</t>
+  </si>
+  <si>
+    <t>90F0613</t>
+  </si>
+  <si>
+    <t>N14</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,6 +381,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -389,17 +427,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -702,10 +744,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H338"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -735,8 +778,8 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>45376</v>
+      <c r="A2" t="s">
+        <v>108</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -748,18 +791,18 @@
         <v>19.686</v>
       </c>
       <c r="E2">
-        <v>95</v>
-      </c>
-      <c r="F2">
-        <v>1870.17</v>
+        <v>120</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2362.3200000000002</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>45376</v>
+      <c r="A3" t="s">
+        <v>108</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -771,18 +814,18 @@
         <v>9.1349999999999998</v>
       </c>
       <c r="E3">
-        <v>70</v>
-      </c>
-      <c r="F3">
-        <v>639.44999999999993</v>
+        <v>120</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1096.2</v>
       </c>
       <c r="H3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>45376</v>
+      <c r="A4" t="s">
+        <v>108</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -794,18 +837,18 @@
         <v>11.3</v>
       </c>
       <c r="E4">
-        <v>82</v>
-      </c>
-      <c r="F4">
-        <v>926.6</v>
+        <v>62</v>
+      </c>
+      <c r="F4" s="3">
+        <v>700.6</v>
       </c>
       <c r="H4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>45376</v>
+      <c r="A5" t="s">
+        <v>108</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -817,18 +860,18 @@
         <v>16.341999999999999</v>
       </c>
       <c r="E5">
-        <v>34.08701505323706</v>
-      </c>
-      <c r="F5">
-        <v>557.04999999999995</v>
+        <v>90</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1470.78</v>
       </c>
       <c r="H5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>45376</v>
+      <c r="A6" t="s">
+        <v>108</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -840,18 +883,18 @@
         <v>17.327999999999999</v>
       </c>
       <c r="E6">
-        <v>85.000000000000014</v>
-      </c>
-      <c r="F6">
-        <v>1472.88</v>
+        <v>87</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1501.2719999999997</v>
       </c>
       <c r="H6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>45376</v>
+      <c r="A7" t="s">
+        <v>108</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -863,18 +906,18 @@
         <v>15.696999999999999</v>
       </c>
       <c r="E7">
-        <v>93.438555137924439</v>
-      </c>
-      <c r="F7">
-        <v>1466.7049999999999</v>
+        <v>85</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1334.2449999999999</v>
       </c>
       <c r="H7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>45376</v>
+      <c r="A8" t="s">
+        <v>108</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
@@ -883,21 +926,21 @@
         <v>68</v>
       </c>
       <c r="D8">
-        <v>19.280999999999999</v>
+        <v>18.895</v>
       </c>
       <c r="E8">
-        <v>84.529329391629062</v>
-      </c>
-      <c r="F8">
-        <v>1629.81</v>
+        <v>50</v>
+      </c>
+      <c r="F8" s="3">
+        <v>944.75</v>
       </c>
       <c r="H8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>45376</v>
+      <c r="A9" t="s">
+        <v>108</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -906,21 +949,21 @@
         <v>66</v>
       </c>
       <c r="D9">
-        <v>17.605</v>
+        <v>17.123999999999999</v>
       </c>
       <c r="E9">
-        <v>77.814257313263283</v>
-      </c>
-      <c r="F9">
-        <v>1369.92</v>
+        <v>55</v>
+      </c>
+      <c r="F9" s="3">
+        <v>941.81999999999994</v>
       </c>
       <c r="H9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>45376</v>
+      <c r="A10" t="s">
+        <v>108</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
@@ -932,18 +975,18 @@
         <v>31.706</v>
       </c>
       <c r="E10">
-        <v>75</v>
-      </c>
-      <c r="F10">
-        <v>2377.9499999999998</v>
+        <v>110</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3487.6599999999994</v>
       </c>
       <c r="H10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>45376</v>
+      <c r="A11" t="s">
+        <v>108</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
@@ -952,21 +995,21 @@
         <v>64</v>
       </c>
       <c r="D11">
-        <v>21.465</v>
+        <v>21.88</v>
       </c>
       <c r="E11">
-        <v>70</v>
-      </c>
-      <c r="F11">
-        <v>1502.55</v>
+        <v>92</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2012.9599999999998</v>
       </c>
       <c r="H11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>45376</v>
+      <c r="A12" t="s">
+        <v>108</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
@@ -978,18 +1021,18 @@
         <v>42.033000000000001</v>
       </c>
       <c r="E12">
-        <v>90.000000000000028</v>
-      </c>
-      <c r="F12">
-        <v>3782.9700000000012</v>
+        <v>75</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3152.4750000000008</v>
       </c>
       <c r="H12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>45376</v>
+      <c r="A13" t="s">
+        <v>108</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
@@ -998,21 +1041,21 @@
         <v>64</v>
       </c>
       <c r="D13">
-        <v>23.658000000000001</v>
+        <v>8.2080000000000002</v>
       </c>
       <c r="E13">
-        <v>74.999999999999986</v>
-      </c>
-      <c r="F13">
-        <v>1774.35</v>
+        <v>65</v>
+      </c>
+      <c r="F13" s="3">
+        <v>533.52</v>
       </c>
       <c r="H13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>45376</v>
+      <c r="A14" t="s">
+        <v>108</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1021,21 +1064,21 @@
         <v>66</v>
       </c>
       <c r="D14">
-        <v>33.844000000000001</v>
+        <v>34.654000000000003</v>
       </c>
       <c r="E14">
-        <v>92.407927240062875</v>
-      </c>
-      <c r="F14">
-        <v>3291.94</v>
+        <v>70</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2425.6399999999994</v>
       </c>
       <c r="H14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>45376</v>
+      <c r="A15" t="s">
+        <v>108</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
@@ -1044,21 +1087,21 @@
         <v>66</v>
       </c>
       <c r="D15">
-        <v>14.504</v>
+        <v>15.156000000000001</v>
       </c>
       <c r="E15">
-        <v>50.000000000000007</v>
-      </c>
-      <c r="F15">
-        <v>725.2</v>
+        <v>90</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1364.04</v>
       </c>
       <c r="H15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>45376</v>
+      <c r="A16" t="s">
+        <v>108</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -1070,18 +1113,18 @@
         <v>25.122</v>
       </c>
       <c r="E16">
-        <v>13.88822545975639</v>
-      </c>
-      <c r="F16">
-        <v>348.9</v>
+        <v>87</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2185.6139999999996</v>
       </c>
       <c r="H16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>45376</v>
+      <c r="A17" t="s">
+        <v>108</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
@@ -1090,21 +1133,21 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>4.1950000000000003</v>
+        <v>4.3520000000000003</v>
       </c>
       <c r="E17">
-        <v>84.999999999999986</v>
-      </c>
-      <c r="F17">
-        <v>356.57499999999999</v>
+        <v>67</v>
+      </c>
+      <c r="F17" s="3">
+        <v>291.584</v>
       </c>
       <c r="H17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>45376</v>
+      <c r="A18" t="s">
+        <v>108</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
@@ -1113,21 +1156,21 @@
         <v>67</v>
       </c>
       <c r="D18">
-        <v>16.079000000000001</v>
+        <v>15.65</v>
       </c>
       <c r="E18">
-        <v>60</v>
-      </c>
-      <c r="F18">
-        <v>964.74</v>
+        <v>76</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1190.0260000000001</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>45376</v>
+      <c r="A19" t="s">
+        <v>108</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
@@ -1136,21 +1179,21 @@
         <v>67</v>
       </c>
       <c r="D19">
-        <v>14.065</v>
+        <v>14.959</v>
       </c>
       <c r="E19">
-        <v>90</v>
-      </c>
-      <c r="F19">
-        <v>1265.8499999999999</v>
+        <v>70</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1047.1299999999999</v>
       </c>
       <c r="H19" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>45376</v>
+      <c r="A20" t="s">
+        <v>108</v>
       </c>
       <c r="B20" t="s">
         <v>30</v>
@@ -1164,16 +1207,16 @@
       <c r="E20">
         <v>70</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="3">
         <v>1182.23</v>
       </c>
       <c r="H20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>45376</v>
+      <c r="A21" t="s">
+        <v>108</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -1185,18 +1228,18 @@
         <v>23.146999999999998</v>
       </c>
       <c r="E21">
-        <v>70</v>
-      </c>
-      <c r="F21">
-        <v>1620.29</v>
+        <v>92</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2129.5239999999999</v>
       </c>
       <c r="H21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>45376</v>
+      <c r="A22" t="s">
+        <v>108</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
@@ -1208,18 +1251,18 @@
         <v>18.552</v>
       </c>
       <c r="E22">
-        <v>59.999999999999993</v>
-      </c>
-      <c r="F22">
-        <v>1113.1199999999999</v>
+        <v>45</v>
+      </c>
+      <c r="F22" s="3">
+        <v>834.84</v>
       </c>
       <c r="H22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>45376</v>
+      <c r="A23" t="s">
+        <v>108</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
@@ -1231,18 +1274,18 @@
         <v>24.803999999999998</v>
       </c>
       <c r="E23">
-        <v>90.000000000000014</v>
-      </c>
-      <c r="F23">
-        <v>2232.36</v>
+        <v>82</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2033.9279999999999</v>
       </c>
       <c r="H23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>45376</v>
+      <c r="A24" t="s">
+        <v>108</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -1251,21 +1294,21 @@
         <v>66</v>
       </c>
       <c r="D24">
-        <v>19.149999999999999</v>
+        <v>13.741</v>
       </c>
       <c r="E24">
-        <v>55.000000000000007</v>
-      </c>
-      <c r="F24">
-        <v>1053.25</v>
+        <v>50</v>
+      </c>
+      <c r="F24" s="3">
+        <v>687.05</v>
       </c>
       <c r="H24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>45376</v>
+      <c r="A25" t="s">
+        <v>108</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
@@ -1274,21 +1317,21 @@
         <v>67</v>
       </c>
       <c r="D25">
-        <v>25.193000000000001</v>
+        <v>25.326000000000001</v>
       </c>
       <c r="E25">
-        <v>81.626046917794625</v>
-      </c>
-      <c r="F25">
-        <v>2056.4050000000002</v>
+        <v>60</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1519.56</v>
       </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>45376</v>
+      <c r="A26" t="s">
+        <v>108</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
@@ -1300,18 +1343,18 @@
         <v>18.324999999999999</v>
       </c>
       <c r="E26">
-        <v>80</v>
-      </c>
-      <c r="F26">
-        <v>1466</v>
+        <v>90</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1649.25</v>
       </c>
       <c r="H26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>45376</v>
+      <c r="A27" t="s">
+        <v>108</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -1323,18 +1366,18 @@
         <v>24.106999999999999</v>
       </c>
       <c r="E27">
-        <v>75</v>
-      </c>
-      <c r="F27">
-        <v>1808.0250000000001</v>
+        <v>80</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1928.56</v>
       </c>
       <c r="H27" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>45376</v>
+      <c r="A28" t="s">
+        <v>108</v>
       </c>
       <c r="B28" t="s">
         <v>38</v>
@@ -1346,18 +1389,18 @@
         <v>13.993</v>
       </c>
       <c r="E28">
-        <v>89.999999999999986</v>
-      </c>
-      <c r="F28">
-        <v>1259.3699999999999</v>
+        <v>88</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1231.384</v>
       </c>
       <c r="H28" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>45376</v>
+      <c r="A29" t="s">
+        <v>108</v>
       </c>
       <c r="B29" t="s">
         <v>39</v>
@@ -1369,18 +1412,18 @@
         <v>23.161999999999999</v>
       </c>
       <c r="E29">
-        <v>50</v>
-      </c>
-      <c r="F29">
-        <v>1158.0999999999999</v>
+        <v>82</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1899.2839999999999</v>
       </c>
       <c r="H29" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>45376</v>
+      <c r="A30" t="s">
+        <v>108</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
@@ -1389,21 +1432,21 @@
         <v>66</v>
       </c>
       <c r="D30">
-        <v>8.423</v>
+        <v>8.9039999999999999</v>
       </c>
       <c r="E30">
-        <v>95.139498990858371</v>
-      </c>
-      <c r="F30">
-        <v>801.36</v>
+        <v>75</v>
+      </c>
+      <c r="F30" s="3">
+        <v>667.8</v>
       </c>
       <c r="H30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>45376</v>
+      <c r="A31" t="s">
+        <v>108</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
@@ -1415,18 +1458,18 @@
         <v>21.858000000000001</v>
       </c>
       <c r="E31">
-        <v>43.043736846921043</v>
-      </c>
-      <c r="F31">
-        <v>940.85</v>
+        <v>70</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1530.06</v>
       </c>
       <c r="H31" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>45376</v>
+      <c r="A32" t="s">
+        <v>108</v>
       </c>
       <c r="B32" t="s">
         <v>42</v>
@@ -1438,18 +1481,18 @@
         <v>25.047000000000001</v>
       </c>
       <c r="E32">
-        <v>90</v>
-      </c>
-      <c r="F32">
-        <v>2254.23</v>
+        <v>87</v>
+      </c>
+      <c r="F32" s="3">
+        <v>2179.0889999999999</v>
       </c>
       <c r="H32" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>45376</v>
+      <c r="A33" t="s">
+        <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -1458,21 +1501,21 @@
         <v>67</v>
       </c>
       <c r="D33">
-        <v>21.138000000000002</v>
+        <v>20.818000000000001</v>
       </c>
       <c r="E33">
-        <v>70</v>
-      </c>
-      <c r="F33">
-        <v>1479.66</v>
+        <v>65</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1353.1699999999998</v>
       </c>
       <c r="H33" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>45376</v>
+      <c r="A34" t="s">
+        <v>108</v>
       </c>
       <c r="B34" t="s">
         <v>44</v>
@@ -1484,18 +1527,18 @@
         <v>24.542999999999999</v>
       </c>
       <c r="E34">
-        <v>80</v>
-      </c>
-      <c r="F34">
-        <v>1963.44</v>
+        <v>65</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1595.2949999999998</v>
       </c>
       <c r="H34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>45376</v>
+      <c r="A35" t="s">
+        <v>108</v>
       </c>
       <c r="B35" t="s">
         <v>45</v>
@@ -1504,21 +1547,21 @@
         <v>67</v>
       </c>
       <c r="D35">
-        <v>12.795999999999999</v>
+        <v>12.601000000000001</v>
       </c>
       <c r="E35">
-        <v>78.780869021569245</v>
-      </c>
-      <c r="F35">
-        <v>1008.08</v>
+        <v>77</v>
+      </c>
+      <c r="F35" s="3">
+        <v>970.27699999999993</v>
       </c>
       <c r="H35" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>45376</v>
+      <c r="A36" t="s">
+        <v>108</v>
       </c>
       <c r="B36" t="s">
         <v>46</v>
@@ -1530,18 +1573,18 @@
         <v>9.7799999999999994</v>
       </c>
       <c r="E36">
-        <v>60</v>
-      </c>
-      <c r="F36">
-        <v>586.79999999999995</v>
+        <v>65</v>
+      </c>
+      <c r="F36" s="3">
+        <v>635.69999999999993</v>
       </c>
       <c r="H36" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>45376</v>
+      <c r="A37" t="s">
+        <v>108</v>
       </c>
       <c r="B37" t="s">
         <v>47</v>
@@ -1550,21 +1593,21 @@
         <v>65</v>
       </c>
       <c r="D37">
-        <v>11.125</v>
+        <v>11.17</v>
       </c>
       <c r="E37">
         <v>80</v>
       </c>
-      <c r="F37">
-        <v>890</v>
+      <c r="F37" s="3">
+        <v>893.6</v>
       </c>
       <c r="H37" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>45376</v>
+      <c r="A38" t="s">
+        <v>108</v>
       </c>
       <c r="B38" t="s">
         <v>48</v>
@@ -1576,18 +1619,18 @@
         <v>10.439</v>
       </c>
       <c r="E38">
-        <v>90</v>
-      </c>
-      <c r="F38">
-        <v>939.51</v>
+        <v>115</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1200.4849999999999</v>
       </c>
       <c r="H38" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>45376</v>
+      <c r="A39" t="s">
+        <v>108</v>
       </c>
       <c r="B39" t="s">
         <v>49</v>
@@ -1599,18 +1642,18 @@
         <v>7.1740000000000004</v>
       </c>
       <c r="E39">
-        <v>89.999999999999986</v>
-      </c>
-      <c r="F39">
-        <v>645.66</v>
+        <v>80</v>
+      </c>
+      <c r="F39" s="3">
+        <v>573.6</v>
       </c>
       <c r="H39" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>45376</v>
+      <c r="A40" t="s">
+        <v>108</v>
       </c>
       <c r="B40" t="s">
         <v>50</v>
@@ -1619,21 +1662,21 @@
         <v>66</v>
       </c>
       <c r="D40">
-        <v>8.7379999999999995</v>
+        <v>8.6750000000000007</v>
       </c>
       <c r="E40">
-        <v>65</v>
-      </c>
-      <c r="F40">
-        <v>567.97</v>
+        <v>70</v>
+      </c>
+      <c r="F40" s="3">
+        <v>607.25</v>
       </c>
       <c r="H40" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>45376</v>
+      <c r="A41" t="s">
+        <v>108</v>
       </c>
       <c r="B41" t="s">
         <v>51</v>
@@ -1642,21 +1685,21 @@
         <v>67</v>
       </c>
       <c r="D41">
-        <v>13.321</v>
+        <v>12.457000000000001</v>
       </c>
       <c r="E41">
-        <v>54.999999999999993</v>
-      </c>
-      <c r="F41">
-        <v>732.65499999999986</v>
+        <v>40</v>
+      </c>
+      <c r="F41" s="3">
+        <v>498.28000000000003</v>
       </c>
       <c r="H41" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>45376</v>
+      <c r="A42" t="s">
+        <v>108</v>
       </c>
       <c r="B42" t="s">
         <v>52</v>
@@ -1668,18 +1711,18 @@
         <v>18.931000000000001</v>
       </c>
       <c r="E42">
-        <v>45</v>
-      </c>
-      <c r="F42">
-        <v>851.8950000000001</v>
+        <v>53</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1003.3430000000001</v>
       </c>
       <c r="H42" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>45376</v>
+      <c r="A43" t="s">
+        <v>108</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
@@ -1688,21 +1731,21 @@
         <v>67</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>8.6980000000000004</v>
       </c>
       <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="F43" s="3">
+        <v>130.47</v>
       </c>
       <c r="H43" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>45376</v>
+      <c r="A44" t="s">
+        <v>108</v>
       </c>
       <c r="B44" t="s">
         <v>54</v>
@@ -1711,21 +1754,21 @@
         <v>67</v>
       </c>
       <c r="D44">
-        <v>25.213999999999999</v>
+        <v>21.687000000000001</v>
       </c>
       <c r="E44">
-        <v>35.339097326881877</v>
-      </c>
-      <c r="F44">
-        <v>891.03999999999985</v>
+        <v>45</v>
+      </c>
+      <c r="F44" s="3">
+        <v>975.91499999999985</v>
       </c>
       <c r="H44" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>45376</v>
+      <c r="A45" t="s">
+        <v>108</v>
       </c>
       <c r="B45" t="s">
         <v>55</v>
@@ -1734,2359 +1777,6893 @@
         <v>67</v>
       </c>
       <c r="D45">
-        <v>7.4450000000000003</v>
+        <v>2.8660000000000001</v>
       </c>
       <c r="E45">
-        <v>44.999999999999993</v>
-      </c>
-      <c r="F45">
-        <v>335.02499999999998</v>
+        <v>30</v>
+      </c>
+      <c r="F45" s="3">
+        <v>85.98</v>
       </c>
       <c r="H45" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>45376</v>
+      <c r="A46" t="s">
+        <v>108</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
         <v>67</v>
       </c>
       <c r="D46">
-        <v>1.27</v>
+        <v>1.988</v>
       </c>
       <c r="E46">
-        <v>56.480314960629933</v>
-      </c>
-      <c r="F46">
-        <v>71.73</v>
+        <v>57.49</v>
+      </c>
+      <c r="F46" s="3">
+        <v>114.29012</v>
       </c>
       <c r="H46" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>45376</v>
+      <c r="A47" t="s">
+        <v>108</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
         <v>67</v>
       </c>
       <c r="D47">
-        <v>2.8849999999999998</v>
+        <v>21.244</v>
       </c>
       <c r="E47">
-        <v>30</v>
-      </c>
-      <c r="F47">
-        <v>86.55</v>
+        <v>33</v>
+      </c>
+      <c r="F47" s="3">
+        <v>701.05199999999991</v>
       </c>
       <c r="H47" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>45376</v>
+      <c r="A48" t="s">
+        <v>108</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="C48" t="s">
+        <v>67</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
+        <v>70.5</v>
+      </c>
+      <c r="F48" s="3">
+        <v>176.25</v>
       </c>
       <c r="H48" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>45376</v>
+      <c r="A49" t="s">
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D49">
-        <v>15.798</v>
+        <v>2.0489999999999999</v>
       </c>
       <c r="E49">
-        <v>34.538549183440942</v>
-      </c>
-      <c r="F49">
-        <v>545.64</v>
+        <v>40</v>
+      </c>
+      <c r="F49" s="3">
+        <v>81.96</v>
       </c>
       <c r="H49" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>45376</v>
+      <c r="A50" t="s">
+        <v>108</v>
       </c>
       <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D50">
+        <v>1.034</v>
+      </c>
+      <c r="E50">
+        <v>15</v>
+      </c>
+      <c r="F50" s="3">
+        <v>15.51</v>
+      </c>
+      <c r="H50" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51">
+        <v>3.077</v>
+      </c>
+      <c r="E51">
+        <v>40</v>
+      </c>
+      <c r="F51" s="3">
+        <v>123.08</v>
+      </c>
+      <c r="H51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52">
+        <v>19.686</v>
+      </c>
+      <c r="E52">
+        <v>118</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2322.9479999999999</v>
+      </c>
+      <c r="H52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53">
+        <v>9.1349999999999998</v>
+      </c>
+      <c r="E53">
+        <v>115</v>
+      </c>
+      <c r="F53" s="3">
+        <v>1050.5249999999999</v>
+      </c>
+      <c r="H53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" t="s">
+        <v>66</v>
+      </c>
+      <c r="D54">
+        <v>11.3</v>
+      </c>
+      <c r="E54">
         <v>60</v>
       </c>
-      <c r="C50" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50">
-        <v>5.3449999999999998</v>
-      </c>
-      <c r="E50">
-        <v>24.658559401309638</v>
-      </c>
-      <c r="F50">
-        <v>131.80000000000001</v>
-      </c>
-      <c r="H50" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>45376</v>
-      </c>
-      <c r="B51" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" t="s">
-        <v>66</v>
-      </c>
-      <c r="D51">
-        <v>4.0940000000000003</v>
-      </c>
-      <c r="E51">
-        <v>47.936003908158277</v>
-      </c>
-      <c r="F51">
-        <v>196.25</v>
-      </c>
-      <c r="H51" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>45376</v>
-      </c>
-      <c r="B52" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="H52" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>45376</v>
-      </c>
-      <c r="B53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" t="s">
-        <v>66</v>
-      </c>
-      <c r="D53">
-        <v>3.07</v>
-      </c>
-      <c r="E53">
-        <v>48.371335504885998</v>
-      </c>
-      <c r="F53">
-        <v>148.5</v>
-      </c>
-      <c r="H53" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>45736</v>
-      </c>
-      <c r="B54" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D54">
-        <v>19.686</v>
-      </c>
-      <c r="E54">
+      <c r="F54" s="3">
+        <v>678</v>
+      </c>
+      <c r="H54" t="s">
         <v>105</v>
       </c>
-      <c r="F54">
-        <v>2067.0300000000002</v>
-      </c>
-      <c r="G54" t="s">
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55">
+        <v>16.341999999999999</v>
+      </c>
+      <c r="E55">
+        <v>40</v>
+      </c>
+      <c r="F55" s="3">
+        <v>653.67999999999995</v>
+      </c>
+      <c r="H55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56">
+        <v>17.327999999999999</v>
+      </c>
+      <c r="E56">
+        <v>80</v>
+      </c>
+      <c r="F56" s="3">
+        <v>1386.24</v>
+      </c>
+      <c r="H56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>113</v>
+      </c>
+      <c r="D57">
+        <v>15.696999999999999</v>
+      </c>
+      <c r="E57">
+        <v>93</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1459.8209999999999</v>
+      </c>
+      <c r="H57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58">
+        <v>18.895</v>
+      </c>
+      <c r="E58">
         <v>70</v>
       </c>
-      <c r="H54" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>45736</v>
-      </c>
-      <c r="B55" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" t="s">
-        <v>68</v>
-      </c>
-      <c r="D55">
-        <v>9.1349999999999998</v>
-      </c>
-      <c r="E55">
-        <v>88</v>
-      </c>
-      <c r="F55">
-        <v>803.88</v>
-      </c>
-      <c r="G55" t="s">
-        <v>71</v>
-      </c>
-      <c r="H55" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>45736</v>
-      </c>
-      <c r="B56" t="s">
-        <v>14</v>
-      </c>
-      <c r="C56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56">
-        <v>11.3</v>
-      </c>
-      <c r="E56">
-        <v>89.899999999999991</v>
-      </c>
-      <c r="F56">
-        <v>1015.87</v>
-      </c>
-      <c r="G56" t="s">
-        <v>72</v>
-      </c>
-      <c r="H56" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>45736</v>
-      </c>
-      <c r="B57" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57">
-        <v>11.141</v>
-      </c>
-      <c r="E57">
-        <v>89.925056700522632</v>
-      </c>
-      <c r="F57">
-        <v>911.93</v>
-      </c>
-      <c r="G57" t="s">
-        <v>73</v>
-      </c>
-      <c r="H57" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>45736</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="s">
-        <v>65</v>
-      </c>
-      <c r="D58">
-        <v>17.327999999999999</v>
-      </c>
-      <c r="E58">
-        <v>96.000115420129276</v>
-      </c>
-      <c r="F58">
-        <v>1663.49</v>
-      </c>
-      <c r="G58" t="s">
-        <v>70</v>
+      <c r="F58" s="3">
+        <v>1322.6499999999999</v>
       </c>
       <c r="H58" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="D59">
-        <v>15.439</v>
+        <v>17.605</v>
       </c>
       <c r="E59">
-        <v>97.999870457931209</v>
-      </c>
-      <c r="F59">
-        <v>1513.02</v>
+        <v>80</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1408.4</v>
       </c>
       <c r="H59" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D60">
-        <v>18.895</v>
+        <v>31.706</v>
       </c>
       <c r="E60">
-        <v>90</v>
-      </c>
-      <c r="F60">
-        <v>1700.55</v>
-      </c>
-      <c r="G60" t="s">
-        <v>74</v>
+        <v>120</v>
+      </c>
+      <c r="F60" s="3">
+        <v>3804.7199999999993</v>
       </c>
       <c r="H60" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B61" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D61">
-        <v>17.123999999999999</v>
+        <v>21.88</v>
       </c>
       <c r="E61">
-        <v>90.000000000000014</v>
-      </c>
-      <c r="F61">
-        <v>1541.16</v>
+        <v>95</v>
+      </c>
+      <c r="F61" s="3">
+        <v>2078.6</v>
       </c>
       <c r="H61" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D62">
-        <v>31.706</v>
+        <v>42.033000000000001</v>
       </c>
       <c r="E62">
-        <v>90</v>
-      </c>
-      <c r="F62">
-        <v>2853.54</v>
+        <v>92</v>
+      </c>
+      <c r="F62" s="3">
+        <v>3867.036000000001</v>
       </c>
       <c r="H62" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B63" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D63">
-        <v>21.465</v>
+        <v>2.0449999999999999</v>
       </c>
       <c r="E63">
-        <v>85.00023293733986</v>
-      </c>
-      <c r="F63">
-        <v>1824.53</v>
+        <v>0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
         <v>69</v>
       </c>
       <c r="D64">
-        <v>41.633000000000003</v>
+        <v>34.652000000000001</v>
       </c>
       <c r="E64">
-        <v>105.0001189541551</v>
-      </c>
-      <c r="F64">
-        <v>4413.47</v>
+        <v>73</v>
+      </c>
+      <c r="F64" s="3">
+        <v>2529.5959999999995</v>
       </c>
       <c r="H64" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D65">
-        <v>23.658000000000001</v>
+        <v>14.504</v>
       </c>
       <c r="E65">
-        <v>80</v>
-      </c>
-      <c r="F65">
-        <v>1892.64</v>
+        <v>125</v>
+      </c>
+      <c r="F65" s="3">
+        <v>1813.0000000000002</v>
       </c>
       <c r="H65" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="D66">
-        <v>33.844000000000001</v>
+        <v>25.122</v>
       </c>
       <c r="E66">
-        <v>99.999999999999986</v>
-      </c>
-      <c r="F66">
-        <v>3465.2</v>
-      </c>
-      <c r="G66" t="s">
-        <v>74</v>
+        <v>100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2512.1999999999998</v>
       </c>
       <c r="H66" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C67" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="D67">
-        <v>14.504</v>
+        <v>4.3520000000000003</v>
       </c>
       <c r="E67">
-        <v>62.000137892995028</v>
-      </c>
-      <c r="F67">
-        <v>899.25</v>
+        <v>80</v>
+      </c>
+      <c r="F67" s="3">
+        <v>348.16</v>
       </c>
       <c r="H67" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C68" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="D68">
-        <v>25.122</v>
+        <v>9.2189999999999994</v>
       </c>
       <c r="E68">
-        <v>65</v>
-      </c>
-      <c r="F68">
-        <v>1632.93</v>
-      </c>
-      <c r="G68" t="s">
-        <v>74</v>
+        <v>30</v>
+      </c>
+      <c r="F68" s="3">
+        <v>276.57</v>
       </c>
       <c r="H68" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C69" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="D69">
-        <v>4.1950000000000003</v>
+        <v>14.959</v>
       </c>
       <c r="E69">
-        <v>112</v>
-      </c>
-      <c r="F69">
-        <v>469.84</v>
-      </c>
-      <c r="G69" t="s">
-        <v>74</v>
+        <v>80</v>
+      </c>
+      <c r="F69" s="3">
+        <v>1196.72</v>
       </c>
       <c r="H69" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C70" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D70">
-        <v>16.079000000000001</v>
+        <v>16.388999999999999</v>
       </c>
       <c r="E70">
         <v>50</v>
       </c>
-      <c r="F70">
-        <v>803.95</v>
+      <c r="F70" s="3">
+        <v>819.44999999999993</v>
       </c>
       <c r="H70" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B71" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D71">
-        <v>14.065</v>
+        <v>23.146999999999998</v>
       </c>
       <c r="E71">
-        <v>95.000355492356917</v>
-      </c>
-      <c r="F71">
-        <v>1336.18</v>
+        <v>98</v>
+      </c>
+      <c r="F71" s="3">
+        <v>2268.4059999999999</v>
       </c>
       <c r="H71" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C72" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D72">
-        <v>16.888999999999999</v>
+        <v>18.552</v>
       </c>
       <c r="E72">
-        <v>70</v>
-      </c>
-      <c r="F72">
-        <v>1182.23</v>
+        <v>60</v>
+      </c>
+      <c r="F72" s="3">
+        <v>1113.1200000000001</v>
       </c>
       <c r="H72" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B73" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C73" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D73">
-        <v>22.911999999999999</v>
+        <v>24.803999999999998</v>
       </c>
       <c r="E73">
-        <v>58.560072579599947</v>
-      </c>
-      <c r="F73">
-        <v>1355.49</v>
-      </c>
-      <c r="G73" t="s">
-        <v>75</v>
+        <v>103</v>
+      </c>
+      <c r="F73" s="3">
+        <v>2554.8119999999999</v>
       </c>
       <c r="H73" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C74" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D74">
-        <v>18.552</v>
+        <v>19.149999999999999</v>
       </c>
       <c r="E74">
-        <v>50</v>
-      </c>
-      <c r="F74">
-        <v>927.6</v>
+        <v>80</v>
+      </c>
+      <c r="F74" s="3">
+        <v>1532</v>
       </c>
       <c r="H74" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C75" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="D75">
-        <v>24.803999999999998</v>
+        <v>25.326000000000001</v>
       </c>
       <c r="E75">
-        <v>82.000080632156113</v>
-      </c>
-      <c r="F75">
-        <v>2033.93</v>
+        <v>80</v>
+      </c>
+      <c r="F75" s="3">
+        <v>2026.08</v>
       </c>
       <c r="H75" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C76" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D76">
-        <v>19.149999999999999</v>
+        <v>18.324999999999999</v>
       </c>
       <c r="E76">
-        <v>50.000000000000007</v>
-      </c>
-      <c r="F76">
-        <v>957.5</v>
+        <v>118</v>
+      </c>
+      <c r="F76" s="3">
+        <v>2162.35</v>
       </c>
       <c r="H76" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B77" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C77" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D77">
-        <v>25.193000000000001</v>
+        <v>24.106999999999999</v>
       </c>
       <c r="E77">
-        <v>80</v>
-      </c>
-      <c r="F77">
-        <v>2015.44</v>
+        <v>90</v>
+      </c>
+      <c r="F77" s="3">
+        <v>2169.63</v>
       </c>
       <c r="H77" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C78" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D78">
-        <v>18.324999999999999</v>
+        <v>13.993</v>
       </c>
       <c r="E78">
-        <v>70</v>
-      </c>
-      <c r="F78">
-        <v>1282.75</v>
+        <v>105</v>
+      </c>
+      <c r="F78" s="3">
+        <v>1469.2650000000001</v>
       </c>
       <c r="H78" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B79" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C79" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D79">
-        <v>24.106999999999999</v>
+        <v>21.137</v>
       </c>
       <c r="E79">
-        <v>70</v>
-      </c>
-      <c r="F79">
-        <v>1687.49</v>
+        <v>90</v>
+      </c>
+      <c r="F79" s="3">
+        <v>1902.33</v>
       </c>
       <c r="H79" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C80" t="s">
         <v>67</v>
       </c>
       <c r="D80">
-        <v>13.993</v>
+        <v>8.9039999999999999</v>
       </c>
       <c r="E80">
-        <v>86.999928535696426</v>
-      </c>
-      <c r="F80">
-        <v>1217.3900000000001</v>
-      </c>
-      <c r="G80" t="s">
-        <v>76</v>
+        <v>98</v>
+      </c>
+      <c r="F80" s="3">
+        <v>872.59199999999998</v>
       </c>
       <c r="H80" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D81">
-        <v>23.161999999999999</v>
+        <v>21.858000000000001</v>
       </c>
       <c r="E81">
-        <v>80</v>
-      </c>
-      <c r="F81">
-        <v>1852.96</v>
-      </c>
-      <c r="G81" t="s">
-        <v>75</v>
+        <v>60</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1311.48</v>
       </c>
       <c r="H81" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C82" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D82">
-        <v>8.9039999999999999</v>
+        <v>25.047000000000001</v>
       </c>
       <c r="E82">
-        <v>100</v>
-      </c>
-      <c r="F82">
-        <v>890.4</v>
+        <v>103</v>
+      </c>
+      <c r="F82" s="3">
+        <v>2579.8409999999999</v>
       </c>
       <c r="H82" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B83" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D83">
-        <v>21.858000000000001</v>
+        <v>21.138000000000002</v>
       </c>
       <c r="E83">
-        <v>70</v>
-      </c>
-      <c r="F83">
-        <v>1530.06</v>
-      </c>
-      <c r="G83" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="F83" s="3">
+        <v>1585.3500000000001</v>
       </c>
       <c r="H83" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B84" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D84">
-        <v>25.047000000000001</v>
+        <v>24.542999999999999</v>
       </c>
       <c r="E84">
-        <v>90</v>
-      </c>
-      <c r="F84">
-        <v>2254.23</v>
+        <v>46</v>
+      </c>
+      <c r="F84" s="3">
+        <v>1128.9780000000001</v>
       </c>
       <c r="H84" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B85" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C85" t="s">
         <v>67</v>
       </c>
       <c r="D85">
-        <v>21.138000000000002</v>
+        <v>12.601000000000001</v>
       </c>
       <c r="E85">
-        <v>85</v>
-      </c>
-      <c r="F85">
-        <v>1796.73</v>
+        <v>90</v>
+      </c>
+      <c r="F85" s="3">
+        <v>1134.0899999999999</v>
       </c>
       <c r="H85" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B86" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C86" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D86">
-        <v>24.542999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="E86">
-        <v>80</v>
-      </c>
-      <c r="F86">
-        <v>1963.44</v>
+        <v>60</v>
+      </c>
+      <c r="F86" s="3">
+        <v>586.80000000000007</v>
       </c>
       <c r="H86" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B87" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C87" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D87">
-        <v>12.577999999999999</v>
+        <v>11.125</v>
       </c>
       <c r="E87">
-        <v>90.160304737719215</v>
-      </c>
-      <c r="F87">
-        <v>1136.1099999999999</v>
-      </c>
-      <c r="G87" t="s">
-        <v>75</v>
+        <v>60</v>
+      </c>
+      <c r="F87" s="3">
+        <v>667.5</v>
       </c>
       <c r="H87" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B88" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C88" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D88">
-        <v>9.7799999999999994</v>
+        <v>10.439</v>
       </c>
       <c r="E88">
-        <v>70</v>
-      </c>
-      <c r="F88">
-        <v>684.6</v>
-      </c>
-      <c r="G88" t="s">
-        <v>77</v>
+        <v>103</v>
+      </c>
+      <c r="F88" s="3">
+        <v>1075.2170000000001</v>
       </c>
       <c r="H88" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B89" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C89" t="s">
         <v>65</v>
       </c>
       <c r="D89">
-        <v>11.125</v>
+        <v>7.1740000000000004</v>
       </c>
       <c r="E89">
-        <v>79.900224719101118</v>
-      </c>
-      <c r="F89">
-        <v>888.89</v>
-      </c>
-      <c r="G89" t="s">
-        <v>77</v>
+        <v>115</v>
+      </c>
+      <c r="F89" s="3">
+        <v>825.01</v>
       </c>
       <c r="H89" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B90" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C90" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D90">
-        <v>10.439</v>
+        <v>6.05</v>
       </c>
       <c r="E90">
-        <v>100</v>
-      </c>
-      <c r="F90">
-        <v>1043.9000000000001</v>
+        <v>85</v>
+      </c>
+      <c r="F90" s="3">
+        <v>514.24999999999989</v>
       </c>
       <c r="H90" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B91" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C91" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D91">
-        <v>7.1740000000000004</v>
+        <v>12.97</v>
       </c>
       <c r="E91">
-        <v>99.999999999999986</v>
-      </c>
-      <c r="F91">
-        <v>717.4</v>
+        <v>40</v>
+      </c>
+      <c r="F91" s="3">
+        <v>518.79999999999995</v>
       </c>
       <c r="H91" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C92" t="s">
         <v>66</v>
       </c>
       <c r="D92">
-        <v>8.7379999999999995</v>
+        <v>18.931000000000001</v>
       </c>
       <c r="E92">
-        <v>50</v>
-      </c>
-      <c r="F92">
-        <v>436.9</v>
-      </c>
-      <c r="G92" t="s">
-        <v>76</v>
+        <v>33</v>
+      </c>
+      <c r="F92" s="3">
+        <v>624.72300000000007</v>
       </c>
       <c r="H92" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B93" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C93" t="s">
         <v>67</v>
       </c>
       <c r="D93">
-        <v>13.321</v>
+        <v>6.0449999999999999</v>
       </c>
       <c r="E93">
-        <v>60</v>
-      </c>
-      <c r="F93">
-        <v>799.26</v>
+        <v>20</v>
+      </c>
+      <c r="F93" s="3">
+        <v>120.9</v>
       </c>
       <c r="H93" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D94">
-        <v>13.906000000000001</v>
+        <v>20.724</v>
       </c>
       <c r="E94">
-        <v>30</v>
-      </c>
-      <c r="F94">
-        <v>417.18</v>
-      </c>
-      <c r="G94" t="s">
-        <v>78</v>
+        <v>33</v>
+      </c>
+      <c r="F94" s="3">
+        <v>683.89199999999994</v>
       </c>
       <c r="H94" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C95" t="s">
         <v>67</v>
       </c>
       <c r="D95">
-        <v>2.4460000000000002</v>
+        <v>10.311</v>
       </c>
       <c r="E95">
-        <v>40</v>
-      </c>
-      <c r="F95">
-        <v>97.84</v>
-      </c>
-      <c r="G95" t="s">
-        <v>75</v>
+        <v>50</v>
+      </c>
+      <c r="F95" s="3">
+        <v>515.54999999999995</v>
       </c>
       <c r="H95" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B96" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C96" t="s">
         <v>67</v>
       </c>
       <c r="D96">
-        <v>8.907</v>
+        <v>1.27</v>
       </c>
       <c r="E96">
-        <v>25.00056135623667</v>
-      </c>
-      <c r="F96">
-        <v>222.68</v>
-      </c>
-      <c r="G96" t="s">
-        <v>78</v>
+        <v>50</v>
+      </c>
+      <c r="F96" s="3">
+        <v>63.5</v>
       </c>
       <c r="H96" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B97" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C97" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D97">
-        <v>7.4450000000000003</v>
+        <v>1.988</v>
       </c>
       <c r="E97">
-        <v>35.000671591672258</v>
-      </c>
-      <c r="F97">
-        <v>260.58</v>
+        <v>35</v>
+      </c>
+      <c r="F97" s="3">
+        <v>69.58</v>
       </c>
       <c r="H97" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B98" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D98">
-        <v>1.27</v>
+        <v>15.798</v>
       </c>
       <c r="E98">
-        <v>35</v>
-      </c>
-      <c r="F98">
-        <v>83.69</v>
-      </c>
-      <c r="G98" t="s">
-        <v>79</v>
+        <v>50</v>
+      </c>
+      <c r="F98" s="3">
+        <v>789.9</v>
       </c>
       <c r="H98" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C99" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D99">
-        <v>2.8849999999999998</v>
+        <v>2.7490000000000001</v>
       </c>
       <c r="E99">
-        <v>45.001733102253041</v>
-      </c>
-      <c r="F99">
-        <v>129.83000000000001</v>
+        <v>45</v>
+      </c>
+      <c r="F99" s="3">
+        <v>123.70499999999998</v>
       </c>
       <c r="H99" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B100" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C100" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D100">
-        <v>19.189</v>
+        <v>2.0419999999999998</v>
       </c>
       <c r="E100">
-        <v>25</v>
-      </c>
-      <c r="F100">
-        <v>473.95</v>
+        <v>40</v>
+      </c>
+      <c r="F100" s="3">
+        <v>81.679999999999993</v>
       </c>
       <c r="H100" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B101" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C101" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D101">
-        <v>1.9119999999999999</v>
+        <v>1.577</v>
       </c>
       <c r="E101">
-        <v>25</v>
-      </c>
-      <c r="F101">
-        <v>47.8</v>
+        <v>28</v>
+      </c>
+      <c r="F101" s="3">
+        <v>44.156000000000006</v>
       </c>
       <c r="H101" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="B102" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C102" t="s">
         <v>64</v>
       </c>
       <c r="D102">
-        <v>3.9249999999999998</v>
-      </c>
-      <c r="E102">
-        <v>55.001273885350322</v>
+        <v>19.686</v>
+      </c>
+      <c r="E102" s="4">
+        <v>120</v>
       </c>
       <c r="F102">
-        <v>215.88</v>
+        <v>2103.2200000000003</v>
       </c>
       <c r="H102" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D103">
-        <v>3.069</v>
-      </c>
-      <c r="E103">
-        <v>55.001629195177593</v>
+        <v>9.1349999999999998</v>
+      </c>
+      <c r="E103" s="4">
+        <v>115</v>
       </c>
       <c r="F103">
-        <v>168.8</v>
+        <v>989.46</v>
       </c>
       <c r="H103" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D104">
-        <v>19.686</v>
-      </c>
-      <c r="E104">
-        <v>119</v>
+        <v>9.98</v>
+      </c>
+      <c r="E104" s="4">
+        <v>75</v>
       </c>
       <c r="F104">
-        <v>2342.63</v>
-      </c>
-      <c r="G104" t="s">
-        <v>80</v>
+        <v>702.74000000000012</v>
       </c>
       <c r="H104" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C105" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D105">
-        <v>9.1349999999999998</v>
-      </c>
-      <c r="E105">
-        <v>98</v>
+        <v>9.3940000000000001</v>
+      </c>
+      <c r="E105" s="4">
+        <v>55</v>
       </c>
       <c r="F105">
-        <v>895.23</v>
-      </c>
-      <c r="G105" t="s">
-        <v>81</v>
+        <v>540.54</v>
       </c>
       <c r="H105" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B106" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C106" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D106">
-        <v>11.3</v>
-      </c>
-      <c r="E106">
-        <v>105</v>
+        <v>15.101000000000001</v>
+      </c>
+      <c r="E106" s="4">
+        <v>80</v>
       </c>
       <c r="F106">
-        <v>1186.5</v>
-      </c>
-      <c r="G106" t="s">
-        <v>82</v>
+        <v>1125.28</v>
       </c>
       <c r="H106" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D107">
-        <v>16.341999999999999</v>
-      </c>
-      <c r="E107">
-        <v>120</v>
+        <v>15.696999999999999</v>
+      </c>
+      <c r="E107" s="4">
+        <v>87.17</v>
       </c>
       <c r="F107">
-        <v>1961.04</v>
-      </c>
-      <c r="G107" t="s">
-        <v>83</v>
+        <v>1368.38</v>
       </c>
       <c r="H107" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C108" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D108">
-        <v>17.327999999999999</v>
-      </c>
-      <c r="E108">
-        <v>105</v>
+        <v>18.895</v>
+      </c>
+      <c r="E108" s="4">
+        <v>80</v>
       </c>
       <c r="F108">
-        <v>1819.44</v>
-      </c>
-      <c r="G108" t="s">
-        <v>82</v>
+        <v>1536.3799999999999</v>
       </c>
       <c r="H108" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C109" t="s">
         <v>66</v>
       </c>
       <c r="D109">
-        <v>15.439</v>
-      </c>
-      <c r="E109">
-        <v>121</v>
+        <v>17.605</v>
+      </c>
+      <c r="E109" s="4">
+        <v>100</v>
       </c>
       <c r="F109">
-        <v>1868.12</v>
-      </c>
-      <c r="G109" t="s">
-        <v>84</v>
+        <v>1850.1399999999999</v>
       </c>
       <c r="H109" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C110" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D110">
-        <v>18.895</v>
-      </c>
-      <c r="E110">
-        <v>110</v>
+        <v>31.706</v>
+      </c>
+      <c r="E110" s="4">
+        <v>105</v>
       </c>
       <c r="F110">
-        <v>2078.4499999999998</v>
-      </c>
-      <c r="G110" t="s">
-        <v>85</v>
+        <v>3751.8199999999997</v>
       </c>
       <c r="H110" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C111" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D111">
-        <v>17.123999999999999</v>
-      </c>
-      <c r="E111">
-        <v>103</v>
+        <v>21.88</v>
+      </c>
+      <c r="E111" s="4">
+        <v>80</v>
       </c>
       <c r="F111">
-        <v>1763.77</v>
-      </c>
-      <c r="G111" t="s">
-        <v>86</v>
+        <v>1942.3200000000002</v>
       </c>
       <c r="H111" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C112" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D112">
-        <v>31.706</v>
-      </c>
-      <c r="E112">
-        <v>100</v>
+        <v>42.033000000000001</v>
+      </c>
+      <c r="E112" s="4">
+        <v>98.19</v>
       </c>
       <c r="F112">
-        <v>3170.6</v>
-      </c>
-      <c r="G112" t="s">
-        <v>87</v>
+        <v>4127.1600000000008</v>
       </c>
       <c r="H112" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C113" t="s">
         <v>64</v>
       </c>
       <c r="D113">
-        <v>21.465</v>
-      </c>
-      <c r="E113">
-        <v>93</v>
+        <v>23.658000000000001</v>
+      </c>
+      <c r="E113" s="4">
+        <v>90</v>
       </c>
       <c r="F113">
-        <v>1996.25</v>
-      </c>
-      <c r="G113" t="s">
-        <v>88</v>
+        <v>1942.3200000000004</v>
       </c>
       <c r="H113" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C114" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D114">
-        <v>42.033000000000001</v>
-      </c>
-      <c r="E114">
-        <v>110</v>
+        <v>34.652000000000001</v>
+      </c>
+      <c r="E114" s="4">
+        <v>92.94</v>
       </c>
       <c r="F114">
-        <v>4623.63</v>
-      </c>
-      <c r="G114" t="s">
-        <v>89</v>
+        <v>3220.6800000000003</v>
       </c>
       <c r="H114" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C115" t="s">
         <v>66</v>
       </c>
       <c r="D115">
-        <v>33.844000000000001</v>
-      </c>
-      <c r="E115">
-        <v>130</v>
+        <v>14.504</v>
+      </c>
+      <c r="E115" s="4">
+        <v>90</v>
       </c>
       <c r="F115">
-        <v>4399.72</v>
-      </c>
-      <c r="G115" t="s">
-        <v>90</v>
+        <v>1089.74</v>
       </c>
       <c r="H115" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B116" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D116">
-        <v>14.504</v>
-      </c>
-      <c r="E116">
-        <v>96</v>
+        <v>25.122</v>
+      </c>
+      <c r="E116" s="4">
+        <v>100</v>
       </c>
       <c r="F116">
-        <v>1392.38</v>
-      </c>
-      <c r="G116" t="s">
-        <v>82</v>
+        <v>2119.86</v>
       </c>
       <c r="H116" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B117" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C117" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D117">
-        <v>25.122</v>
-      </c>
-      <c r="E117">
-        <v>85</v>
+        <v>4.1950000000000003</v>
+      </c>
+      <c r="E117" s="4">
+        <v>75.930000000000007</v>
       </c>
       <c r="F117">
-        <v>2135.37</v>
+        <v>330.46</v>
       </c>
       <c r="H117" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B118" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C118" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D118">
-        <v>4.1950000000000003</v>
-      </c>
-      <c r="E118">
-        <v>125</v>
+        <v>19.959</v>
+      </c>
+      <c r="E118" s="4">
+        <v>75</v>
       </c>
       <c r="F118">
-        <v>524.38</v>
-      </c>
-      <c r="G118" t="s">
-        <v>91</v>
+        <v>1097.8</v>
       </c>
       <c r="H118" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B119" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C119" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D119">
-        <v>16.079000000000001</v>
-      </c>
-      <c r="E119">
-        <v>61</v>
+        <v>23.146999999999998</v>
+      </c>
+      <c r="E119" s="4">
+        <v>100</v>
       </c>
       <c r="F119">
-        <v>980.82</v>
-      </c>
-      <c r="G119" t="s">
-        <v>92</v>
+        <v>2324.96</v>
       </c>
       <c r="H119" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B120" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C120" t="s">
         <v>66</v>
       </c>
       <c r="D120">
-        <v>14.065</v>
-      </c>
-      <c r="E120">
-        <v>98</v>
+        <v>18.552</v>
+      </c>
+      <c r="E120" s="4">
+        <v>55</v>
       </c>
       <c r="F120">
-        <v>1378.37</v>
-      </c>
-      <c r="G120" t="s">
-        <v>93</v>
+        <v>1020.59</v>
       </c>
       <c r="H120" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B121" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C121" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D121">
-        <v>16.888999999999999</v>
-      </c>
-      <c r="E121">
-        <v>46</v>
+        <v>24.803999999999998</v>
+      </c>
+      <c r="E121" s="4">
+        <v>95</v>
       </c>
       <c r="F121">
-        <v>776.89</v>
-      </c>
-      <c r="G121" t="s">
-        <v>94</v>
+        <v>2446.2699999999995</v>
       </c>
       <c r="H121" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B122" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C122" t="s">
         <v>66</v>
       </c>
       <c r="D122">
-        <v>22.911999999999999</v>
-      </c>
-      <c r="E122">
-        <v>110</v>
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E122" s="4">
+        <v>80</v>
       </c>
       <c r="F122">
-        <v>2520.3200000000002</v>
-      </c>
-      <c r="G122" t="s">
-        <v>95</v>
+        <v>1369.63</v>
       </c>
       <c r="H122" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B123" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C123" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D123">
-        <v>18.552</v>
-      </c>
-      <c r="E123">
-        <v>73</v>
+        <v>25.193000000000001</v>
+      </c>
+      <c r="E123" s="4">
+        <v>80</v>
       </c>
       <c r="F123">
-        <v>1354.3</v>
+        <v>1317.6200000000001</v>
       </c>
       <c r="H123" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B124" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C124" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D124">
-        <v>24.803999999999998</v>
-      </c>
-      <c r="E124">
-        <v>83</v>
+        <v>18.324999999999999</v>
+      </c>
+      <c r="E124" s="4">
+        <v>105</v>
       </c>
       <c r="F124">
-        <v>2058.73</v>
+        <v>1732.7999999999997</v>
       </c>
       <c r="H124" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B125" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C125" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D125">
-        <v>19.149999999999999</v>
-      </c>
-      <c r="E125">
-        <v>55</v>
+        <v>24.106999999999999</v>
+      </c>
+      <c r="E125" s="4">
+        <v>70</v>
       </c>
       <c r="F125">
-        <v>1053.25</v>
+        <v>1200.8599999999999</v>
       </c>
       <c r="H125" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B126" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D126">
-        <v>25.193000000000001</v>
-      </c>
-      <c r="E126">
-        <v>80</v>
+        <v>13.993</v>
+      </c>
+      <c r="E126" s="4">
+        <v>104.27</v>
       </c>
       <c r="F126">
-        <v>2015.44</v>
+        <v>1459.1000000000001</v>
       </c>
       <c r="H126" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B127" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C127" t="s">
         <v>66</v>
       </c>
       <c r="D127">
-        <v>18.324999999999999</v>
-      </c>
-      <c r="E127">
-        <v>90</v>
+        <v>21.137</v>
+      </c>
+      <c r="E127" s="4">
+        <v>80</v>
       </c>
       <c r="F127">
-        <v>1649.25</v>
+        <v>1390.73</v>
       </c>
       <c r="H127" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B128" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C128" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D128">
-        <v>24.106999999999999</v>
-      </c>
-      <c r="E128">
-        <v>65</v>
+        <v>8.9039999999999999</v>
+      </c>
+      <c r="E128" s="4">
+        <v>96.79</v>
       </c>
       <c r="F128">
-        <v>1566.95</v>
-      </c>
-      <c r="G128" t="s">
-        <v>96</v>
+        <v>861.8599999999999</v>
       </c>
       <c r="H128" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B129" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C129" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D129">
-        <v>13.993</v>
-      </c>
-      <c r="E129">
-        <v>95</v>
+        <v>21.858000000000001</v>
+      </c>
+      <c r="E129" s="4">
+        <v>50</v>
       </c>
       <c r="F129">
-        <v>1329.34</v>
-      </c>
-      <c r="G129" t="s">
-        <v>97</v>
+        <v>1103.9000000000001</v>
       </c>
       <c r="H129" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B130" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C130" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D130">
-        <v>23.161999999999999</v>
-      </c>
-      <c r="E130">
-        <v>65</v>
+        <v>25.047000000000001</v>
+      </c>
+      <c r="E130" s="4">
+        <v>98.57</v>
       </c>
       <c r="F130">
-        <v>1505.53</v>
-      </c>
-      <c r="G130" t="s">
-        <v>98</v>
+        <v>2468.8200000000002</v>
       </c>
       <c r="H130" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B131" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C131" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D131">
-        <v>8.9039999999999999</v>
-      </c>
-      <c r="E131">
+        <v>21.138000000000002</v>
+      </c>
+      <c r="E131" s="4">
+        <v>90</v>
+      </c>
+      <c r="F131">
+        <v>1784.6000000000004</v>
+      </c>
+      <c r="H131" t="s">
         <v>106</v>
-      </c>
-      <c r="F131">
-        <v>943.82</v>
-      </c>
-      <c r="G131" t="s">
-        <v>99</v>
-      </c>
-      <c r="H131" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B132" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C132" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D132">
-        <v>21.858000000000001</v>
-      </c>
-      <c r="E132">
-        <v>75</v>
+        <v>24.542999999999999</v>
+      </c>
+      <c r="E132" s="4">
+        <v>80</v>
       </c>
       <c r="F132">
-        <v>1639.35</v>
+        <v>2102.2399999999998</v>
       </c>
       <c r="H132" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B133" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C133" t="s">
         <v>67</v>
       </c>
       <c r="D133">
-        <v>25.047000000000001</v>
-      </c>
-      <c r="E133">
-        <v>97</v>
+        <v>12.795999999999999</v>
+      </c>
+      <c r="E133" s="4">
+        <v>92.54</v>
       </c>
       <c r="F133">
-        <v>2429.56</v>
+        <v>1166.06</v>
       </c>
       <c r="H133" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B134" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C134" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D134">
-        <v>21.138000000000002</v>
-      </c>
-      <c r="E134">
-        <v>92</v>
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="E134" s="4">
+        <v>65</v>
       </c>
       <c r="F134">
-        <v>1944.7</v>
-      </c>
-      <c r="G134" t="s">
-        <v>100</v>
+        <v>609.66</v>
       </c>
       <c r="H134" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B135" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C135" t="s">
         <v>65</v>
       </c>
       <c r="D135">
-        <v>24.542999999999999</v>
-      </c>
-      <c r="E135">
-        <v>95</v>
+        <v>11.125</v>
+      </c>
+      <c r="E135" s="4">
+        <v>65</v>
       </c>
       <c r="F135">
-        <v>2331.59</v>
+        <v>692.95</v>
       </c>
       <c r="H135" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B136" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C136" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D136">
-        <v>12.601000000000001</v>
-      </c>
-      <c r="E136">
-        <v>105</v>
+        <v>10.439</v>
+      </c>
+      <c r="E136" s="4">
+        <v>103</v>
       </c>
       <c r="F136">
-        <v>1323.11</v>
+        <v>1119.48</v>
       </c>
       <c r="H136" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B137" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C137" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D137">
-        <v>9.7799999999999994</v>
-      </c>
-      <c r="E137">
-        <v>95</v>
+        <v>7.1740000000000004</v>
+      </c>
+      <c r="E137" s="4">
+        <v>100</v>
       </c>
       <c r="F137">
-        <v>929.1</v>
-      </c>
-      <c r="G137" t="s">
-        <v>82</v>
+        <v>706.03999999999985</v>
       </c>
       <c r="H137" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B138" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D138">
-        <v>11.125</v>
-      </c>
-      <c r="E138">
-        <v>95</v>
+        <v>8.7379999999999995</v>
+      </c>
+      <c r="E138" s="4">
+        <v>80</v>
       </c>
       <c r="F138">
-        <v>1056.8800000000001</v>
+        <v>799.81999999999994</v>
       </c>
       <c r="H138" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B139" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C139" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D139">
-        <v>10.439</v>
-      </c>
-      <c r="E139">
-        <v>115</v>
+        <v>12.704000000000001</v>
+      </c>
+      <c r="E139" s="4">
+        <v>33</v>
       </c>
       <c r="F139">
-        <v>1200.49</v>
+        <v>603.26</v>
       </c>
       <c r="H139" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B140" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C140" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D140">
-        <v>7.1740000000000004</v>
-      </c>
-      <c r="E140">
-        <v>115</v>
+        <v>18.931000000000001</v>
+      </c>
+      <c r="E140" s="4">
+        <v>45</v>
       </c>
       <c r="F140">
-        <v>825.01</v>
+        <v>786.16000000000008</v>
       </c>
       <c r="H140" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>110</v>
+      </c>
+      <c r="B141" t="s">
+        <v>53</v>
+      </c>
+      <c r="C141" t="s">
+        <v>67</v>
+      </c>
+      <c r="D141">
+        <v>2.4460000000000002</v>
+      </c>
+      <c r="E141" s="4">
+        <v>10</v>
+      </c>
+      <c r="F141">
+        <v>62.03</v>
+      </c>
+      <c r="H141" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>110</v>
+      </c>
+      <c r="B142" t="s">
+        <v>54</v>
+      </c>
+      <c r="C142" t="s">
+        <v>67</v>
+      </c>
+      <c r="D142">
+        <v>22.870999999999999</v>
+      </c>
+      <c r="E142" s="4">
+        <v>35</v>
+      </c>
+      <c r="F142">
+        <v>1034.05</v>
+      </c>
+      <c r="H142" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>110</v>
+      </c>
+      <c r="B143" t="s">
+        <v>55</v>
+      </c>
+      <c r="C143" t="s">
+        <v>67</v>
+      </c>
+      <c r="D143">
+        <v>10.311</v>
+      </c>
+      <c r="E143" s="4">
+        <v>40</v>
+      </c>
+      <c r="F143">
+        <v>457.9</v>
+      </c>
+      <c r="H143" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>110</v>
+      </c>
+      <c r="B144" t="s">
+        <v>56</v>
+      </c>
+      <c r="C144" t="s">
+        <v>67</v>
+      </c>
+      <c r="D144">
+        <v>1.27</v>
+      </c>
+      <c r="E144" s="4">
+        <v>40</v>
+      </c>
+      <c r="F144">
+        <v>17.510000000000002</v>
+      </c>
+      <c r="H144" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>110</v>
+      </c>
+      <c r="B145" t="s">
+        <v>57</v>
+      </c>
+      <c r="C145" t="s">
+        <v>67</v>
+      </c>
+      <c r="D145">
+        <v>2.8849999999999998</v>
+      </c>
+      <c r="E145" s="4">
+        <v>40</v>
+      </c>
+      <c r="F145">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="H145" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>110</v>
+      </c>
+      <c r="B146" t="s">
+        <v>59</v>
+      </c>
+      <c r="C146" t="s">
+        <v>67</v>
+      </c>
+      <c r="D146">
+        <v>14.134</v>
+      </c>
+      <c r="E146" s="4">
+        <v>55</v>
+      </c>
+      <c r="F146">
+        <v>369.86999999999995</v>
+      </c>
+      <c r="H146" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>110</v>
+      </c>
+      <c r="B147" t="s">
+        <v>60</v>
+      </c>
+      <c r="C147" t="s">
+        <v>67</v>
+      </c>
+      <c r="D147">
+        <v>4.0179999999999998</v>
+      </c>
+      <c r="E147" s="4">
+        <v>35</v>
+      </c>
+      <c r="F147">
+        <v>98.4</v>
+      </c>
+      <c r="H147" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>110</v>
+      </c>
+      <c r="B148" t="s">
+        <v>61</v>
+      </c>
+      <c r="C148" t="s">
+        <v>66</v>
+      </c>
+      <c r="D148">
+        <v>4.0940000000000003</v>
+      </c>
+      <c r="E148" s="4">
+        <v>40</v>
+      </c>
+      <c r="F148">
+        <v>145.21</v>
+      </c>
+      <c r="H148" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>110</v>
+      </c>
+      <c r="B149" t="s">
+        <v>63</v>
+      </c>
+      <c r="C149" t="s">
+        <v>66</v>
+      </c>
+      <c r="D149">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="E149" s="4">
+        <v>15</v>
+      </c>
+      <c r="F149">
+        <v>66.490000000000009</v>
+      </c>
+      <c r="H149" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>111</v>
+      </c>
+      <c r="B150" t="s">
+        <v>12</v>
+      </c>
+      <c r="C150" t="s">
+        <v>64</v>
+      </c>
+      <c r="D150">
+        <v>19.686</v>
+      </c>
+      <c r="E150" s="4">
+        <v>87.45</v>
+      </c>
+      <c r="F150" s="3">
+        <v>1721.5407</v>
+      </c>
+      <c r="H150" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>111</v>
+      </c>
+      <c r="B151" t="s">
+        <v>13</v>
+      </c>
+      <c r="C151" t="s">
+        <v>65</v>
+      </c>
+      <c r="D151">
+        <v>9.1349999999999998</v>
+      </c>
+      <c r="E151" s="4">
+        <v>87.45</v>
+      </c>
+      <c r="F151" s="3">
+        <v>798.85575000000006</v>
+      </c>
+      <c r="H151" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>111</v>
+      </c>
+      <c r="B152" t="s">
+        <v>14</v>
+      </c>
+      <c r="C152" t="s">
+        <v>66</v>
+      </c>
+      <c r="D152">
+        <v>4.24</v>
+      </c>
+      <c r="E152" s="4">
+        <v>83.475000000000009</v>
+      </c>
+      <c r="F152" s="3">
+        <v>353.93400000000003</v>
+      </c>
+      <c r="H152" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>111</v>
+      </c>
+      <c r="B153" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" t="s">
+        <v>67</v>
+      </c>
+      <c r="D153">
+        <v>8.3460000000000001</v>
+      </c>
+      <c r="E153" s="4">
+        <v>63.6</v>
+      </c>
+      <c r="F153" s="3">
+        <v>530.80559999999991</v>
+      </c>
+      <c r="H153" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>111</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="s">
+        <v>65</v>
+      </c>
+      <c r="D154">
+        <v>16.827999999999999</v>
+      </c>
+      <c r="E154" s="4">
+        <v>55.650000000000006</v>
+      </c>
+      <c r="F154" s="3">
+        <v>936.47820000000002</v>
+      </c>
+      <c r="H154" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>111</v>
+      </c>
+      <c r="B155" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" t="s">
+        <v>66</v>
+      </c>
+      <c r="D155">
+        <v>15.696999999999999</v>
+      </c>
+      <c r="E155" s="4">
+        <v>59.625</v>
+      </c>
+      <c r="F155" s="3">
+        <v>935.93362500000001</v>
+      </c>
+      <c r="H155" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>111</v>
+      </c>
+      <c r="B156" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156">
+        <v>18.895</v>
+      </c>
+      <c r="E156" s="4">
+        <v>67.575000000000003</v>
+      </c>
+      <c r="F156" s="3">
+        <v>1276.8296250000001</v>
+      </c>
+      <c r="H156" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>111</v>
+      </c>
+      <c r="B157" t="s">
+        <v>19</v>
+      </c>
+      <c r="C157" t="s">
+        <v>66</v>
+      </c>
+      <c r="D157">
+        <v>17.605</v>
+      </c>
+      <c r="E157" s="4">
+        <v>87.45</v>
+      </c>
+      <c r="F157" s="3">
+        <v>1539.5572500000001</v>
+      </c>
+      <c r="H157" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>111</v>
+      </c>
+      <c r="B158" t="s">
+        <v>20</v>
+      </c>
+      <c r="C158" t="s">
+        <v>65</v>
+      </c>
+      <c r="D158">
+        <v>31.706</v>
+      </c>
+      <c r="E158" s="4">
+        <v>55.650000000000006</v>
+      </c>
+      <c r="F158" s="3">
+        <v>1764.4388999999999</v>
+      </c>
+      <c r="H158" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>111</v>
+      </c>
+      <c r="B159" t="s">
+        <v>21</v>
+      </c>
+      <c r="C159" t="s">
+        <v>64</v>
+      </c>
+      <c r="D159">
+        <v>21.88</v>
+      </c>
+      <c r="E159" s="4">
+        <v>79.5</v>
+      </c>
+      <c r="F159" s="3">
+        <v>1739.4599999999998</v>
+      </c>
+      <c r="H159" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>111</v>
+      </c>
+      <c r="B160" t="s">
+        <v>22</v>
+      </c>
+      <c r="C160" t="s">
+        <v>69</v>
+      </c>
+      <c r="D160">
+        <v>42.033000000000001</v>
+      </c>
+      <c r="E160" s="4">
+        <v>71.55</v>
+      </c>
+      <c r="F160" s="3">
+        <v>3007.4611500000005</v>
+      </c>
+      <c r="H160" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>111</v>
+      </c>
+      <c r="B161" t="s">
+        <v>23</v>
+      </c>
+      <c r="C161" t="s">
+        <v>64</v>
+      </c>
+      <c r="D161">
+        <v>23.658000000000001</v>
+      </c>
+      <c r="E161" s="4">
+        <v>79.5</v>
+      </c>
+      <c r="F161" s="3">
+        <v>1880.8110000000004</v>
+      </c>
+      <c r="H161" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>111</v>
+      </c>
+      <c r="B162" t="s">
+        <v>24</v>
+      </c>
+      <c r="C162" t="s">
+        <v>66</v>
+      </c>
+      <c r="D162">
+        <v>34.652000000000001</v>
+      </c>
+      <c r="E162" s="4">
+        <v>63.6</v>
+      </c>
+      <c r="F162" s="3">
+        <v>2203.8671999999997</v>
+      </c>
+      <c r="H162" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>111</v>
+      </c>
+      <c r="B163" t="s">
+        <v>25</v>
+      </c>
+      <c r="C163" t="s">
+        <v>66</v>
+      </c>
+      <c r="D163">
+        <v>14.504</v>
+      </c>
+      <c r="E163" s="4">
+        <v>51.675000000000004</v>
+      </c>
+      <c r="F163" s="3">
+        <v>749.49420000000009</v>
+      </c>
+      <c r="H163" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>111</v>
+      </c>
+      <c r="B164" t="s">
+        <v>26</v>
+      </c>
+      <c r="C164" t="s">
+        <v>65</v>
+      </c>
+      <c r="D164">
+        <v>25.122</v>
+      </c>
+      <c r="E164" s="4">
+        <v>55.650000000000006</v>
+      </c>
+      <c r="F164" s="3">
+        <v>1398.0392999999999</v>
+      </c>
+      <c r="H164" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>111</v>
+      </c>
+      <c r="B165" t="s">
+        <v>27</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165">
+        <v>4.1950000000000003</v>
+      </c>
+      <c r="E165" s="4">
+        <v>83.475000000000009</v>
+      </c>
+      <c r="F165" s="3">
+        <v>350.17762500000003</v>
+      </c>
+      <c r="H165" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>111</v>
+      </c>
+      <c r="B166" t="s">
+        <v>28</v>
+      </c>
+      <c r="C166" t="s">
+        <v>67</v>
+      </c>
+      <c r="D166">
+        <v>16.079000000000001</v>
+      </c>
+      <c r="E166" s="4">
+        <v>68.962642924558892</v>
+      </c>
+      <c r="F166" s="3">
+        <v>1108.8503355839825</v>
+      </c>
+      <c r="H166" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>111</v>
+      </c>
+      <c r="B167" t="s">
+        <v>30</v>
+      </c>
+      <c r="C167" t="s">
+        <v>66</v>
+      </c>
+      <c r="D167">
+        <v>16.888999999999999</v>
+      </c>
+      <c r="E167" s="4">
+        <v>47.7</v>
+      </c>
+      <c r="F167" s="3">
+        <v>805.60530000000006</v>
+      </c>
+      <c r="H167" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>111</v>
+      </c>
+      <c r="B168" t="s">
+        <v>31</v>
+      </c>
+      <c r="C168" t="s">
+        <v>65</v>
+      </c>
+      <c r="D168">
+        <v>23.146999999999998</v>
+      </c>
+      <c r="E168" s="4">
+        <v>71.55</v>
+      </c>
+      <c r="F168" s="3">
+        <v>1656.1678499999998</v>
+      </c>
+      <c r="H168" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>111</v>
+      </c>
+      <c r="B169" t="s">
+        <v>32</v>
+      </c>
+      <c r="C169" t="s">
+        <v>66</v>
+      </c>
+      <c r="D169">
+        <v>18.552</v>
+      </c>
+      <c r="E169" s="4">
+        <v>39.75</v>
+      </c>
+      <c r="F169" s="3">
+        <v>737.44200000000012</v>
+      </c>
+      <c r="H169" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>111</v>
+      </c>
+      <c r="B170" t="s">
+        <v>33</v>
+      </c>
+      <c r="C170" t="s">
+        <v>67</v>
+      </c>
+      <c r="D170">
+        <v>24.803999999999998</v>
+      </c>
+      <c r="E170" s="4">
+        <v>71.55</v>
+      </c>
+      <c r="F170" s="3">
+        <v>1774.7261999999998</v>
+      </c>
+      <c r="H170" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>111</v>
+      </c>
+      <c r="B171" t="s">
+        <v>34</v>
+      </c>
+      <c r="C171" t="s">
+        <v>66</v>
+      </c>
+      <c r="D171">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E171" s="4">
+        <v>59.625</v>
+      </c>
+      <c r="F171" s="3">
+        <v>1141.8187499999999</v>
+      </c>
+      <c r="H171" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>111</v>
+      </c>
+      <c r="B172" t="s">
+        <v>35</v>
+      </c>
+      <c r="C172" t="s">
+        <v>67</v>
+      </c>
+      <c r="D172">
+        <v>25.193000000000001</v>
+      </c>
+      <c r="E172" s="4">
+        <v>91.425000000000011</v>
+      </c>
+      <c r="F172" s="3">
+        <v>2028.9950249999999</v>
+      </c>
+      <c r="H172" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>111</v>
+      </c>
+      <c r="B173" t="s">
+        <v>36</v>
+      </c>
+      <c r="C173" t="s">
+        <v>66</v>
+      </c>
+      <c r="D173">
+        <v>18.324999999999999</v>
+      </c>
+      <c r="E173" s="4">
+        <v>75.525000000000006</v>
+      </c>
+      <c r="F173" s="3">
+        <v>1383.995625</v>
+      </c>
+      <c r="H173" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>111</v>
+      </c>
+      <c r="B174" t="s">
+        <v>37</v>
+      </c>
+      <c r="C174" t="s">
+        <v>65</v>
+      </c>
+      <c r="D174">
+        <v>24.106999999999999</v>
+      </c>
+      <c r="E174" s="4">
+        <v>79.5</v>
+      </c>
+      <c r="F174" s="3">
+        <v>1916.5065</v>
+      </c>
+      <c r="H174" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>111</v>
+      </c>
+      <c r="B175" t="s">
+        <v>38</v>
+      </c>
+      <c r="C175" t="s">
+        <v>67</v>
+      </c>
+      <c r="D175">
+        <v>13.993</v>
+      </c>
+      <c r="E175" s="4">
+        <v>71.55</v>
+      </c>
+      <c r="F175" s="3">
+        <v>1001.19915</v>
+      </c>
+      <c r="H175" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>111</v>
+      </c>
+      <c r="B176" t="s">
+        <v>39</v>
+      </c>
+      <c r="C176" t="s">
+        <v>66</v>
+      </c>
+      <c r="D176">
+        <v>23.161999999999999</v>
+      </c>
+      <c r="E176" s="4">
+        <v>43.725000000000001</v>
+      </c>
+      <c r="F176" s="3">
+        <v>1012.75845</v>
+      </c>
+      <c r="H176" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>111</v>
+      </c>
+      <c r="B177" t="s">
+        <v>40</v>
+      </c>
+      <c r="C177" t="s">
+        <v>66</v>
+      </c>
+      <c r="D177">
+        <v>8.9039999999999999</v>
+      </c>
+      <c r="E177" s="4">
+        <v>71.55</v>
+      </c>
+      <c r="F177" s="3">
+        <v>637.08119999999997</v>
+      </c>
+      <c r="H177" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>111</v>
+      </c>
+      <c r="B178" t="s">
+        <v>41</v>
+      </c>
+      <c r="C178" t="s">
+        <v>66</v>
+      </c>
+      <c r="D178">
+        <v>21.858000000000001</v>
+      </c>
+      <c r="E178" s="4">
+        <v>47.7</v>
+      </c>
+      <c r="F178" s="3">
+        <v>1042.6266000000001</v>
+      </c>
+      <c r="H178" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>111</v>
+      </c>
+      <c r="B179" t="s">
+        <v>42</v>
+      </c>
+      <c r="C179" t="s">
+        <v>67</v>
+      </c>
+      <c r="D179">
+        <v>25.047000000000001</v>
+      </c>
+      <c r="E179" s="4">
+        <v>79.5</v>
+      </c>
+      <c r="F179" s="3">
+        <v>1991.2364999999998</v>
+      </c>
+      <c r="H179" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>111</v>
+      </c>
+      <c r="B180" t="s">
+        <v>43</v>
+      </c>
+      <c r="C180" t="s">
+        <v>67</v>
+      </c>
+      <c r="D180">
+        <v>21.138000000000002</v>
+      </c>
+      <c r="E180" s="4">
+        <v>75.525000000000006</v>
+      </c>
+      <c r="F180" s="3">
+        <v>1596.4474499999999</v>
+      </c>
+      <c r="H180" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>111</v>
+      </c>
+      <c r="B181" t="s">
+        <v>44</v>
+      </c>
+      <c r="C181" t="s">
+        <v>65</v>
+      </c>
+      <c r="D181">
+        <v>24.542999999999999</v>
+      </c>
+      <c r="E181" s="4">
+        <v>83.475000000000009</v>
+      </c>
+      <c r="F181" s="3">
+        <v>2048.7269249999999</v>
+      </c>
+      <c r="H181" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>111</v>
+      </c>
+      <c r="B182" t="s">
+        <v>45</v>
+      </c>
+      <c r="C182" t="s">
+        <v>67</v>
+      </c>
+      <c r="D182">
+        <v>12.795999999999999</v>
+      </c>
+      <c r="E182" s="4">
+        <v>75.525000000000006</v>
+      </c>
+      <c r="F182" s="3">
+        <v>966.41790000000003</v>
+      </c>
+      <c r="H182" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>111</v>
+      </c>
+      <c r="B183" t="s">
+        <v>46</v>
+      </c>
+      <c r="C183" t="s">
+        <v>66</v>
+      </c>
+      <c r="D183">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="E183" s="4">
+        <v>39.75</v>
+      </c>
+      <c r="F183" s="3">
+        <v>388.755</v>
+      </c>
+      <c r="H183" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>111</v>
+      </c>
+      <c r="B184" t="s">
+        <v>47</v>
+      </c>
+      <c r="C184" t="s">
+        <v>65</v>
+      </c>
+      <c r="D184">
+        <v>11.125</v>
+      </c>
+      <c r="E184" s="4">
+        <v>55.650000000000006</v>
+      </c>
+      <c r="F184" s="3">
+        <v>619.10625000000005</v>
+      </c>
+      <c r="H184" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>111</v>
+      </c>
+      <c r="B185" t="s">
+        <v>48</v>
+      </c>
+      <c r="C185" t="s">
+        <v>65</v>
+      </c>
+      <c r="D185">
+        <v>10.439</v>
+      </c>
+      <c r="E185" s="4">
+        <v>87.45</v>
+      </c>
+      <c r="F185" s="3">
+        <v>912.89055000000008</v>
+      </c>
+      <c r="H185" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>111</v>
+      </c>
+      <c r="B186" t="s">
+        <v>49</v>
+      </c>
+      <c r="C186" t="s">
+        <v>65</v>
+      </c>
+      <c r="D186">
+        <v>6.05</v>
+      </c>
+      <c r="E186" s="4">
+        <v>67.575000000000003</v>
+      </c>
+      <c r="F186" s="3">
+        <v>408.82874999999996</v>
+      </c>
+      <c r="H186" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>111</v>
+      </c>
+      <c r="B187" t="s">
+        <v>50</v>
+      </c>
+      <c r="C187" t="s">
+        <v>66</v>
+      </c>
+      <c r="D187">
+        <v>8.7379999999999995</v>
+      </c>
+      <c r="E187" s="4">
+        <v>71.55</v>
+      </c>
+      <c r="F187" s="3">
+        <v>625.20389999999998</v>
+      </c>
+      <c r="H187" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>111</v>
+      </c>
+      <c r="B188" t="s">
+        <v>51</v>
+      </c>
+      <c r="C188" t="s">
+        <v>67</v>
+      </c>
+      <c r="D188">
+        <v>7.5679999999999996</v>
+      </c>
+      <c r="E188" s="4">
+        <v>23.85</v>
+      </c>
+      <c r="F188" s="3">
+        <v>180.49680000000001</v>
+      </c>
+      <c r="H188" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>111</v>
+      </c>
+      <c r="B189" t="s">
+        <v>52</v>
+      </c>
+      <c r="C189" t="s">
+        <v>66</v>
+      </c>
+      <c r="D189">
+        <v>18.931000000000001</v>
+      </c>
+      <c r="E189" s="4">
+        <v>35.774999999999999</v>
+      </c>
+      <c r="F189" s="3">
+        <v>677.25652500000001</v>
+      </c>
+      <c r="H189" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>111</v>
+      </c>
+      <c r="B190" t="s">
+        <v>53</v>
+      </c>
+      <c r="C190" t="s">
+        <v>67</v>
+      </c>
+      <c r="D190">
+        <v>2.4460000000000002</v>
+      </c>
+      <c r="E190" s="4">
+        <v>23.85</v>
+      </c>
+      <c r="F190" s="3">
+        <v>58.337100000000007</v>
+      </c>
+      <c r="H190" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>111</v>
+      </c>
+      <c r="B191" t="s">
+        <v>54</v>
+      </c>
+      <c r="C191" t="s">
+        <v>67</v>
+      </c>
+      <c r="D191">
+        <v>25.206</v>
+      </c>
+      <c r="E191" s="4">
+        <v>39.75</v>
+      </c>
+      <c r="F191" s="3">
+        <v>1001.9384999999999</v>
+      </c>
+      <c r="H191" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>111</v>
+      </c>
+      <c r="B192" t="s">
+        <v>55</v>
+      </c>
+      <c r="C192" t="s">
+        <v>67</v>
+      </c>
+      <c r="D192">
+        <v>7.4450000000000003</v>
+      </c>
+      <c r="E192" s="4">
+        <v>35.774999999999999</v>
+      </c>
+      <c r="F192" s="3">
+        <v>266.344875</v>
+      </c>
+      <c r="H192" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>111</v>
+      </c>
+      <c r="B193" t="s">
+        <v>56</v>
+      </c>
+      <c r="C193" t="s">
+        <v>67</v>
+      </c>
+      <c r="D193">
+        <v>1.27</v>
+      </c>
+      <c r="E193" s="4">
+        <v>15.9</v>
+      </c>
+      <c r="F193" s="3">
+        <v>20.193000000000001</v>
+      </c>
+      <c r="H193" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>111</v>
+      </c>
+      <c r="B194" t="s">
+        <v>57</v>
+      </c>
+      <c r="C194" t="s">
+        <v>67</v>
+      </c>
+      <c r="D194">
+        <v>1.548</v>
+      </c>
+      <c r="E194" s="4">
+        <v>39.75</v>
+      </c>
+      <c r="F194" s="3">
+        <v>61.532999999999994</v>
+      </c>
+      <c r="H194" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>111</v>
+      </c>
+      <c r="B195" t="s">
+        <v>59</v>
+      </c>
+      <c r="C195" t="s">
+        <v>67</v>
+      </c>
+      <c r="D195">
+        <v>11.738</v>
+      </c>
+      <c r="E195" s="4">
+        <v>39.75</v>
+      </c>
+      <c r="F195" s="3">
+        <v>466.58549999999991</v>
+      </c>
+      <c r="H195" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>111</v>
+      </c>
+      <c r="B196" t="s">
+        <v>60</v>
+      </c>
+      <c r="C196" t="s">
+        <v>67</v>
+      </c>
+      <c r="D196">
+        <v>5.2720000000000002</v>
+      </c>
+      <c r="E196" s="4">
+        <v>23.85</v>
+      </c>
+      <c r="F196" s="3">
+        <v>125.73719999999999</v>
+      </c>
+      <c r="H196" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>111</v>
+      </c>
+      <c r="B197" t="s">
+        <v>61</v>
+      </c>
+      <c r="C197" t="s">
+        <v>66</v>
+      </c>
+      <c r="D197">
+        <v>3.9249999999999998</v>
+      </c>
+      <c r="E197" s="4">
+        <v>40</v>
+      </c>
+      <c r="F197" s="3">
+        <v>157</v>
+      </c>
+      <c r="H197" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>111</v>
+      </c>
+      <c r="B198" t="s">
+        <v>63</v>
+      </c>
+      <c r="C198" t="s">
+        <v>66</v>
+      </c>
+      <c r="D198">
+        <v>3.07</v>
+      </c>
+      <c r="E198" s="4">
+        <v>35</v>
+      </c>
+      <c r="F198" s="3">
+        <v>107.45000000000002</v>
+      </c>
+      <c r="H198" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B199" t="s">
+        <v>12</v>
+      </c>
+      <c r="C199" t="s">
+        <v>64</v>
+      </c>
+      <c r="D199">
+        <v>19.686</v>
+      </c>
+      <c r="E199">
+        <v>95</v>
+      </c>
+      <c r="F199">
+        <v>1870.17</v>
+      </c>
+      <c r="H199" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B200" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" t="s">
+        <v>65</v>
+      </c>
+      <c r="D200">
+        <v>9.1349999999999998</v>
+      </c>
+      <c r="E200">
+        <v>70</v>
+      </c>
+      <c r="F200">
+        <v>639.44999999999993</v>
+      </c>
+      <c r="H200" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B201" t="s">
+        <v>14</v>
+      </c>
+      <c r="C201" t="s">
+        <v>66</v>
+      </c>
+      <c r="D201">
+        <v>11.3</v>
+      </c>
+      <c r="E201">
+        <v>82</v>
+      </c>
+      <c r="F201">
+        <v>926.6</v>
+      </c>
+      <c r="H201" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B202" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202" t="s">
+        <v>67</v>
+      </c>
+      <c r="D202">
+        <v>16.341999999999999</v>
+      </c>
+      <c r="E202">
+        <v>34.08701505323706</v>
+      </c>
+      <c r="F202">
+        <v>557.04999999999995</v>
+      </c>
+      <c r="H202" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B203" t="s">
+        <v>16</v>
+      </c>
+      <c r="C203" t="s">
+        <v>65</v>
+      </c>
+      <c r="D203">
+        <v>17.327999999999999</v>
+      </c>
+      <c r="E203">
+        <v>85.000000000000014</v>
+      </c>
+      <c r="F203">
+        <v>1472.88</v>
+      </c>
+      <c r="H203" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B204" t="s">
+        <v>17</v>
+      </c>
+      <c r="C204" t="s">
+        <v>66</v>
+      </c>
+      <c r="D204">
+        <v>15.696999999999999</v>
+      </c>
+      <c r="E204">
+        <v>93.438555137924439</v>
+      </c>
+      <c r="F204">
+        <v>1466.7049999999999</v>
+      </c>
+      <c r="H204" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B205" t="s">
+        <v>18</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205">
+        <v>19.280999999999999</v>
+      </c>
+      <c r="E205">
+        <v>84.529329391629062</v>
+      </c>
+      <c r="F205">
+        <v>1629.81</v>
+      </c>
+      <c r="H205" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B206" t="s">
+        <v>19</v>
+      </c>
+      <c r="C206" t="s">
+        <v>66</v>
+      </c>
+      <c r="D206">
+        <v>17.605</v>
+      </c>
+      <c r="E206">
+        <v>77.814257313263283</v>
+      </c>
+      <c r="F206">
+        <v>1369.92</v>
+      </c>
+      <c r="H206" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B207" t="s">
+        <v>20</v>
+      </c>
+      <c r="C207" t="s">
+        <v>65</v>
+      </c>
+      <c r="D207">
+        <v>31.706</v>
+      </c>
+      <c r="E207">
+        <v>75</v>
+      </c>
+      <c r="F207">
+        <v>2377.9499999999998</v>
+      </c>
+      <c r="H207" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B208" t="s">
+        <v>21</v>
+      </c>
+      <c r="C208" t="s">
+        <v>64</v>
+      </c>
+      <c r="D208">
+        <v>21.465</v>
+      </c>
+      <c r="E208">
+        <v>70</v>
+      </c>
+      <c r="F208">
+        <v>1502.55</v>
+      </c>
+      <c r="H208" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B209" t="s">
+        <v>22</v>
+      </c>
+      <c r="C209" t="s">
+        <v>69</v>
+      </c>
+      <c r="D209">
+        <v>42.033000000000001</v>
+      </c>
+      <c r="E209">
+        <v>90.000000000000028</v>
+      </c>
+      <c r="F209">
+        <v>3782.9700000000012</v>
+      </c>
+      <c r="H209" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B210" t="s">
+        <v>23</v>
+      </c>
+      <c r="C210" t="s">
+        <v>64</v>
+      </c>
+      <c r="D210">
+        <v>23.658000000000001</v>
+      </c>
+      <c r="E210">
+        <v>74.999999999999986</v>
+      </c>
+      <c r="F210">
+        <v>1774.35</v>
+      </c>
+      <c r="H210" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B211" t="s">
+        <v>24</v>
+      </c>
+      <c r="C211" t="s">
+        <v>66</v>
+      </c>
+      <c r="D211">
+        <v>33.844000000000001</v>
+      </c>
+      <c r="E211">
+        <v>92.407927240062875</v>
+      </c>
+      <c r="F211">
+        <v>3291.94</v>
+      </c>
+      <c r="H211" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B212" t="s">
+        <v>25</v>
+      </c>
+      <c r="C212" t="s">
+        <v>66</v>
+      </c>
+      <c r="D212">
+        <v>14.504</v>
+      </c>
+      <c r="E212">
+        <v>50.000000000000007</v>
+      </c>
+      <c r="F212">
+        <v>725.2</v>
+      </c>
+      <c r="H212" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B213" t="s">
+        <v>26</v>
+      </c>
+      <c r="C213" t="s">
+        <v>65</v>
+      </c>
+      <c r="D213">
+        <v>25.122</v>
+      </c>
+      <c r="E213">
+        <v>13.88822545975639</v>
+      </c>
+      <c r="F213">
+        <v>348.9</v>
+      </c>
+      <c r="H213" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B214" t="s">
+        <v>27</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214">
+        <v>4.1950000000000003</v>
+      </c>
+      <c r="E214">
+        <v>84.999999999999986</v>
+      </c>
+      <c r="F214">
+        <v>356.57499999999999</v>
+      </c>
+      <c r="H214" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B215" t="s">
+        <v>28</v>
+      </c>
+      <c r="C215" t="s">
+        <v>67</v>
+      </c>
+      <c r="D215">
+        <v>16.079000000000001</v>
+      </c>
+      <c r="E215">
+        <v>60</v>
+      </c>
+      <c r="F215">
+        <v>964.74</v>
+      </c>
+      <c r="H215" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B216" t="s">
+        <v>29</v>
+      </c>
+      <c r="C216" t="s">
+        <v>67</v>
+      </c>
+      <c r="D216">
+        <v>14.065</v>
+      </c>
+      <c r="E216">
+        <v>90</v>
+      </c>
+      <c r="F216">
+        <v>1265.8499999999999</v>
+      </c>
+      <c r="H216" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B217" t="s">
+        <v>30</v>
+      </c>
+      <c r="C217" t="s">
+        <v>66</v>
+      </c>
+      <c r="D217">
+        <v>16.888999999999999</v>
+      </c>
+      <c r="E217">
+        <v>70</v>
+      </c>
+      <c r="F217">
+        <v>1182.23</v>
+      </c>
+      <c r="H217" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B218" t="s">
+        <v>31</v>
+      </c>
+      <c r="C218" t="s">
+        <v>65</v>
+      </c>
+      <c r="D218">
+        <v>23.146999999999998</v>
+      </c>
+      <c r="E218">
+        <v>70</v>
+      </c>
+      <c r="F218">
+        <v>1620.29</v>
+      </c>
+      <c r="H218" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B219" t="s">
+        <v>32</v>
+      </c>
+      <c r="C219" t="s">
+        <v>66</v>
+      </c>
+      <c r="D219">
+        <v>18.552</v>
+      </c>
+      <c r="E219">
+        <v>59.999999999999993</v>
+      </c>
+      <c r="F219">
+        <v>1113.1199999999999</v>
+      </c>
+      <c r="H219" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B220" t="s">
+        <v>33</v>
+      </c>
+      <c r="C220" t="s">
+        <v>67</v>
+      </c>
+      <c r="D220">
+        <v>24.803999999999998</v>
+      </c>
+      <c r="E220">
+        <v>90.000000000000014</v>
+      </c>
+      <c r="F220">
+        <v>2232.36</v>
+      </c>
+      <c r="H220" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B221" t="s">
+        <v>34</v>
+      </c>
+      <c r="C221" t="s">
+        <v>66</v>
+      </c>
+      <c r="D221">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E221">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="F221">
+        <v>1053.25</v>
+      </c>
+      <c r="H221" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B222" t="s">
+        <v>35</v>
+      </c>
+      <c r="C222" t="s">
+        <v>67</v>
+      </c>
+      <c r="D222">
+        <v>25.193000000000001</v>
+      </c>
+      <c r="E222">
+        <v>81.626046917794625</v>
+      </c>
+      <c r="F222">
+        <v>2056.4050000000002</v>
+      </c>
+      <c r="H222" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B223" t="s">
+        <v>36</v>
+      </c>
+      <c r="C223" t="s">
+        <v>66</v>
+      </c>
+      <c r="D223">
+        <v>18.324999999999999</v>
+      </c>
+      <c r="E223">
+        <v>80</v>
+      </c>
+      <c r="F223">
+        <v>1466</v>
+      </c>
+      <c r="H223" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B224" t="s">
+        <v>37</v>
+      </c>
+      <c r="C224" t="s">
+        <v>65</v>
+      </c>
+      <c r="D224">
+        <v>24.106999999999999</v>
+      </c>
+      <c r="E224">
+        <v>75</v>
+      </c>
+      <c r="F224">
+        <v>1808.0250000000001</v>
+      </c>
+      <c r="H224" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B225" t="s">
+        <v>38</v>
+      </c>
+      <c r="C225" t="s">
+        <v>67</v>
+      </c>
+      <c r="D225">
+        <v>13.993</v>
+      </c>
+      <c r="E225">
+        <v>89.999999999999986</v>
+      </c>
+      <c r="F225">
+        <v>1259.3699999999999</v>
+      </c>
+      <c r="H225" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B226" t="s">
+        <v>39</v>
+      </c>
+      <c r="C226" t="s">
+        <v>66</v>
+      </c>
+      <c r="D226">
+        <v>23.161999999999999</v>
+      </c>
+      <c r="E226">
+        <v>50</v>
+      </c>
+      <c r="F226">
+        <v>1158.0999999999999</v>
+      </c>
+      <c r="H226" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B227" t="s">
+        <v>40</v>
+      </c>
+      <c r="C227" t="s">
+        <v>66</v>
+      </c>
+      <c r="D227">
+        <v>8.423</v>
+      </c>
+      <c r="E227">
+        <v>95.139498990858371</v>
+      </c>
+      <c r="F227">
+        <v>801.36</v>
+      </c>
+      <c r="H227" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B228" t="s">
+        <v>41</v>
+      </c>
+      <c r="C228" t="s">
+        <v>66</v>
+      </c>
+      <c r="D228">
+        <v>21.858000000000001</v>
+      </c>
+      <c r="E228">
+        <v>43.043736846921043</v>
+      </c>
+      <c r="F228">
+        <v>940.85</v>
+      </c>
+      <c r="H228" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B229" t="s">
+        <v>42</v>
+      </c>
+      <c r="C229" t="s">
+        <v>67</v>
+      </c>
+      <c r="D229">
+        <v>25.047000000000001</v>
+      </c>
+      <c r="E229">
+        <v>90</v>
+      </c>
+      <c r="F229">
+        <v>2254.23</v>
+      </c>
+      <c r="H229" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B230" t="s">
+        <v>43</v>
+      </c>
+      <c r="C230" t="s">
+        <v>67</v>
+      </c>
+      <c r="D230">
+        <v>21.138000000000002</v>
+      </c>
+      <c r="E230">
+        <v>70</v>
+      </c>
+      <c r="F230">
+        <v>1479.66</v>
+      </c>
+      <c r="H230" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B231" t="s">
+        <v>44</v>
+      </c>
+      <c r="C231" t="s">
+        <v>65</v>
+      </c>
+      <c r="D231">
+        <v>24.542999999999999</v>
+      </c>
+      <c r="E231">
+        <v>80</v>
+      </c>
+      <c r="F231">
+        <v>1963.44</v>
+      </c>
+      <c r="H231" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B232" t="s">
+        <v>45</v>
+      </c>
+      <c r="C232" t="s">
+        <v>67</v>
+      </c>
+      <c r="D232">
+        <v>12.795999999999999</v>
+      </c>
+      <c r="E232">
+        <v>78.780869021569245</v>
+      </c>
+      <c r="F232">
+        <v>1008.08</v>
+      </c>
+      <c r="H232" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B233" t="s">
+        <v>46</v>
+      </c>
+      <c r="C233" t="s">
+        <v>66</v>
+      </c>
+      <c r="D233">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="E233">
+        <v>60</v>
+      </c>
+      <c r="F233">
+        <v>586.79999999999995</v>
+      </c>
+      <c r="H233" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B234" t="s">
+        <v>47</v>
+      </c>
+      <c r="C234" t="s">
+        <v>65</v>
+      </c>
+      <c r="D234">
+        <v>11.125</v>
+      </c>
+      <c r="E234">
+        <v>80</v>
+      </c>
+      <c r="F234">
+        <v>890</v>
+      </c>
+      <c r="H234" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B235" t="s">
+        <v>48</v>
+      </c>
+      <c r="C235" t="s">
+        <v>65</v>
+      </c>
+      <c r="D235">
+        <v>10.439</v>
+      </c>
+      <c r="E235">
+        <v>90</v>
+      </c>
+      <c r="F235">
+        <v>939.51</v>
+      </c>
+      <c r="H235" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B236" t="s">
+        <v>49</v>
+      </c>
+      <c r="C236" t="s">
+        <v>65</v>
+      </c>
+      <c r="D236">
+        <v>7.1740000000000004</v>
+      </c>
+      <c r="E236">
+        <v>89.999999999999986</v>
+      </c>
+      <c r="F236">
+        <v>645.66</v>
+      </c>
+      <c r="H236" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B237" t="s">
+        <v>50</v>
+      </c>
+      <c r="C237" t="s">
+        <v>66</v>
+      </c>
+      <c r="D237">
+        <v>8.7379999999999995</v>
+      </c>
+      <c r="E237">
+        <v>65</v>
+      </c>
+      <c r="F237">
+        <v>567.97</v>
+      </c>
+      <c r="H237" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B238" t="s">
+        <v>51</v>
+      </c>
+      <c r="C238" t="s">
+        <v>67</v>
+      </c>
+      <c r="D238">
+        <v>13.321</v>
+      </c>
+      <c r="E238">
+        <v>54.999999999999993</v>
+      </c>
+      <c r="F238">
+        <v>732.65499999999986</v>
+      </c>
+      <c r="H238" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B239" t="s">
+        <v>52</v>
+      </c>
+      <c r="C239" t="s">
+        <v>66</v>
+      </c>
+      <c r="D239">
+        <v>18.931000000000001</v>
+      </c>
+      <c r="E239">
+        <v>45</v>
+      </c>
+      <c r="F239">
+        <v>851.8950000000001</v>
+      </c>
+      <c r="H239" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B240" t="s">
+        <v>53</v>
+      </c>
+      <c r="C240" t="s">
+        <v>67</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>0</v>
+      </c>
+      <c r="H240" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B241" t="s">
+        <v>54</v>
+      </c>
+      <c r="C241" t="s">
+        <v>67</v>
+      </c>
+      <c r="D241">
+        <v>25.213999999999999</v>
+      </c>
+      <c r="E241">
+        <v>35.339097326881877</v>
+      </c>
+      <c r="F241">
+        <v>891.03999999999985</v>
+      </c>
+      <c r="H241" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B242" t="s">
+        <v>55</v>
+      </c>
+      <c r="C242" t="s">
+        <v>67</v>
+      </c>
+      <c r="D242">
+        <v>7.4450000000000003</v>
+      </c>
+      <c r="E242">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="F242">
+        <v>335.02499999999998</v>
+      </c>
+      <c r="H242" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B243" t="s">
+        <v>56</v>
+      </c>
+      <c r="C243" t="s">
+        <v>67</v>
+      </c>
+      <c r="D243">
+        <v>1.27</v>
+      </c>
+      <c r="E243">
+        <v>56.480314960629933</v>
+      </c>
+      <c r="F243">
+        <v>71.73</v>
+      </c>
+      <c r="H243" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B244" t="s">
+        <v>57</v>
+      </c>
+      <c r="C244" t="s">
+        <v>67</v>
+      </c>
+      <c r="D244">
+        <v>2.8849999999999998</v>
+      </c>
+      <c r="E244">
+        <v>30</v>
+      </c>
+      <c r="F244">
+        <v>86.55</v>
+      </c>
+      <c r="H244" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B245" t="s">
+        <v>58</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+      <c r="F245">
+        <v>0</v>
+      </c>
+      <c r="H245" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B246" t="s">
+        <v>59</v>
+      </c>
+      <c r="C246" t="s">
+        <v>67</v>
+      </c>
+      <c r="D246">
+        <v>15.798</v>
+      </c>
+      <c r="E246">
+        <v>34.538549183440942</v>
+      </c>
+      <c r="F246">
+        <v>545.64</v>
+      </c>
+      <c r="H246" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B247" t="s">
+        <v>60</v>
+      </c>
+      <c r="C247" t="s">
+        <v>67</v>
+      </c>
+      <c r="D247">
+        <v>5.3449999999999998</v>
+      </c>
+      <c r="E247">
+        <v>24.658559401309638</v>
+      </c>
+      <c r="F247">
+        <v>131.80000000000001</v>
+      </c>
+      <c r="H247" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B248" t="s">
+        <v>61</v>
+      </c>
+      <c r="C248" t="s">
+        <v>66</v>
+      </c>
+      <c r="D248">
+        <v>4.0940000000000003</v>
+      </c>
+      <c r="E248">
+        <v>47.936003908158277</v>
+      </c>
+      <c r="F248">
+        <v>196.25</v>
+      </c>
+      <c r="H248" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B249" t="s">
+        <v>62</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
+      <c r="F249">
+        <v>0</v>
+      </c>
+      <c r="H249" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B250" t="s">
+        <v>63</v>
+      </c>
+      <c r="C250" t="s">
+        <v>66</v>
+      </c>
+      <c r="D250">
+        <v>3.07</v>
+      </c>
+      <c r="E250">
+        <v>48.371335504885998</v>
+      </c>
+      <c r="F250">
+        <v>148.5</v>
+      </c>
+      <c r="H250" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <v>45736</v>
+      </c>
+      <c r="B251" t="s">
+        <v>12</v>
+      </c>
+      <c r="C251" t="s">
+        <v>64</v>
+      </c>
+      <c r="D251">
+        <v>19.686</v>
+      </c>
+      <c r="E251">
+        <v>105</v>
+      </c>
+      <c r="F251">
+        <v>2067.0300000000002</v>
+      </c>
+      <c r="G251" t="s">
+        <v>70</v>
+      </c>
+      <c r="H251" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" s="2">
+        <v>45736</v>
+      </c>
+      <c r="B252" t="s">
+        <v>13</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252">
+        <v>9.1349999999999998</v>
+      </c>
+      <c r="E252">
+        <v>88</v>
+      </c>
+      <c r="F252">
+        <v>803.88</v>
+      </c>
+      <c r="G252" t="s">
+        <v>71</v>
+      </c>
+      <c r="H252" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253" s="2">
+        <v>45736</v>
+      </c>
+      <c r="B253" t="s">
+        <v>14</v>
+      </c>
+      <c r="C253" t="s">
+        <v>66</v>
+      </c>
+      <c r="D253">
+        <v>11.3</v>
+      </c>
+      <c r="E253">
+        <v>89.899999999999991</v>
+      </c>
+      <c r="F253">
+        <v>1015.87</v>
+      </c>
+      <c r="G253" t="s">
+        <v>72</v>
+      </c>
+      <c r="H253" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" s="2">
+        <v>45736</v>
+      </c>
+      <c r="B254" t="s">
+        <v>15</v>
+      </c>
+      <c r="C254" t="s">
+        <v>67</v>
+      </c>
+      <c r="D254">
+        <v>11.141</v>
+      </c>
+      <c r="E254">
+        <v>89.925056700522632</v>
+      </c>
+      <c r="F254">
+        <v>911.93</v>
+      </c>
+      <c r="G254" t="s">
+        <v>73</v>
+      </c>
+      <c r="H254" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" s="2">
+        <v>45736</v>
+      </c>
+      <c r="B255" t="s">
+        <v>16</v>
+      </c>
+      <c r="C255" t="s">
+        <v>65</v>
+      </c>
+      <c r="D255">
+        <v>17.327999999999999</v>
+      </c>
+      <c r="E255">
+        <v>96.000115420129276</v>
+      </c>
+      <c r="F255">
+        <v>1663.49</v>
+      </c>
+      <c r="G255" t="s">
+        <v>70</v>
+      </c>
+      <c r="H255" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>8</v>
+      </c>
+      <c r="B256" t="s">
+        <v>17</v>
+      </c>
+      <c r="C256" t="s">
+        <v>66</v>
+      </c>
+      <c r="D256">
+        <v>15.439</v>
+      </c>
+      <c r="E256">
+        <v>97.999870457931209</v>
+      </c>
+      <c r="F256">
+        <v>1513.02</v>
+      </c>
+      <c r="H256" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>8</v>
+      </c>
+      <c r="B257" t="s">
+        <v>18</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257">
+        <v>18.895</v>
+      </c>
+      <c r="E257">
+        <v>90</v>
+      </c>
+      <c r="F257">
+        <v>1700.55</v>
+      </c>
+      <c r="G257" t="s">
+        <v>74</v>
+      </c>
+      <c r="H257" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>8</v>
+      </c>
+      <c r="B258" t="s">
+        <v>19</v>
+      </c>
+      <c r="C258" t="s">
+        <v>66</v>
+      </c>
+      <c r="D258">
+        <v>17.123999999999999</v>
+      </c>
+      <c r="E258">
+        <v>90.000000000000014</v>
+      </c>
+      <c r="F258">
+        <v>1541.16</v>
+      </c>
+      <c r="H258" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>8</v>
+      </c>
+      <c r="B259" t="s">
+        <v>20</v>
+      </c>
+      <c r="C259" t="s">
+        <v>65</v>
+      </c>
+      <c r="D259">
+        <v>31.706</v>
+      </c>
+      <c r="E259">
+        <v>90</v>
+      </c>
+      <c r="F259">
+        <v>2853.54</v>
+      </c>
+      <c r="H259" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>8</v>
+      </c>
+      <c r="B260" t="s">
+        <v>21</v>
+      </c>
+      <c r="C260" t="s">
+        <v>64</v>
+      </c>
+      <c r="D260">
+        <v>21.465</v>
+      </c>
+      <c r="E260">
+        <v>85.00023293733986</v>
+      </c>
+      <c r="F260">
+        <v>1824.53</v>
+      </c>
+      <c r="H260" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>8</v>
+      </c>
+      <c r="B261" t="s">
+        <v>22</v>
+      </c>
+      <c r="C261" t="s">
+        <v>69</v>
+      </c>
+      <c r="D261">
+        <v>41.633000000000003</v>
+      </c>
+      <c r="E261">
+        <v>105.0001189541551</v>
+      </c>
+      <c r="F261">
+        <v>4413.47</v>
+      </c>
+      <c r="H261" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>8</v>
+      </c>
+      <c r="B262" t="s">
+        <v>23</v>
+      </c>
+      <c r="C262" t="s">
+        <v>64</v>
+      </c>
+      <c r="D262">
+        <v>23.658000000000001</v>
+      </c>
+      <c r="E262">
+        <v>80</v>
+      </c>
+      <c r="F262">
+        <v>1892.64</v>
+      </c>
+      <c r="H262" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>8</v>
+      </c>
+      <c r="B263" t="s">
+        <v>24</v>
+      </c>
+      <c r="C263" t="s">
+        <v>66</v>
+      </c>
+      <c r="D263">
+        <v>33.844000000000001</v>
+      </c>
+      <c r="E263">
+        <v>99.999999999999986</v>
+      </c>
+      <c r="F263">
+        <v>3465.2</v>
+      </c>
+      <c r="G263" t="s">
+        <v>74</v>
+      </c>
+      <c r="H263" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>8</v>
+      </c>
+      <c r="B264" t="s">
+        <v>25</v>
+      </c>
+      <c r="C264" t="s">
+        <v>66</v>
+      </c>
+      <c r="D264">
+        <v>14.504</v>
+      </c>
+      <c r="E264">
+        <v>62.000137892995028</v>
+      </c>
+      <c r="F264">
+        <v>899.25</v>
+      </c>
+      <c r="H264" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>8</v>
+      </c>
+      <c r="B265" t="s">
+        <v>26</v>
+      </c>
+      <c r="C265" t="s">
+        <v>66</v>
+      </c>
+      <c r="D265">
+        <v>25.122</v>
+      </c>
+      <c r="E265">
+        <v>65</v>
+      </c>
+      <c r="F265">
+        <v>1632.93</v>
+      </c>
+      <c r="G265" t="s">
+        <v>74</v>
+      </c>
+      <c r="H265" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>8</v>
+      </c>
+      <c r="B266" t="s">
+        <v>27</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266">
+        <v>4.1950000000000003</v>
+      </c>
+      <c r="E266">
+        <v>112</v>
+      </c>
+      <c r="F266">
+        <v>469.84</v>
+      </c>
+      <c r="G266" t="s">
+        <v>74</v>
+      </c>
+      <c r="H266" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>8</v>
+      </c>
+      <c r="B267" t="s">
+        <v>28</v>
+      </c>
+      <c r="C267" t="s">
+        <v>67</v>
+      </c>
+      <c r="D267">
+        <v>16.079000000000001</v>
+      </c>
+      <c r="E267">
+        <v>50</v>
+      </c>
+      <c r="F267">
+        <v>803.95</v>
+      </c>
+      <c r="H267" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>8</v>
+      </c>
+      <c r="B268" t="s">
+        <v>29</v>
+      </c>
+      <c r="C268" t="s">
+        <v>66</v>
+      </c>
+      <c r="D268">
+        <v>14.065</v>
+      </c>
+      <c r="E268">
+        <v>95.000355492356917</v>
+      </c>
+      <c r="F268">
+        <v>1336.18</v>
+      </c>
+      <c r="H268" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>8</v>
+      </c>
+      <c r="B269" t="s">
+        <v>30</v>
+      </c>
+      <c r="C269" t="s">
+        <v>66</v>
+      </c>
+      <c r="D269">
+        <v>16.888999999999999</v>
+      </c>
+      <c r="E269">
+        <v>70</v>
+      </c>
+      <c r="F269">
+        <v>1182.23</v>
+      </c>
+      <c r="H269" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>9</v>
+      </c>
+      <c r="B270" t="s">
+        <v>31</v>
+      </c>
+      <c r="C270" t="s">
+        <v>66</v>
+      </c>
+      <c r="D270">
+        <v>22.911999999999999</v>
+      </c>
+      <c r="E270">
+        <v>58.560072579599947</v>
+      </c>
+      <c r="F270">
+        <v>1355.49</v>
+      </c>
+      <c r="G270" t="s">
+        <v>75</v>
+      </c>
+      <c r="H270" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>9</v>
+      </c>
+      <c r="B271" t="s">
+        <v>32</v>
+      </c>
+      <c r="C271" t="s">
+        <v>66</v>
+      </c>
+      <c r="D271">
+        <v>18.552</v>
+      </c>
+      <c r="E271">
+        <v>50</v>
+      </c>
+      <c r="F271">
+        <v>927.6</v>
+      </c>
+      <c r="H271" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>9</v>
+      </c>
+      <c r="B272" t="s">
+        <v>33</v>
+      </c>
+      <c r="C272" t="s">
+        <v>67</v>
+      </c>
+      <c r="D272">
+        <v>24.803999999999998</v>
+      </c>
+      <c r="E272">
+        <v>82.000080632156113</v>
+      </c>
+      <c r="F272">
+        <v>2033.93</v>
+      </c>
+      <c r="H272" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>9</v>
+      </c>
+      <c r="B273" t="s">
+        <v>34</v>
+      </c>
+      <c r="C273" t="s">
+        <v>66</v>
+      </c>
+      <c r="D273">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E273">
+        <v>50.000000000000007</v>
+      </c>
+      <c r="F273">
+        <v>957.5</v>
+      </c>
+      <c r="H273" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>9</v>
+      </c>
+      <c r="B274" t="s">
+        <v>35</v>
+      </c>
+      <c r="C274" t="s">
+        <v>64</v>
+      </c>
+      <c r="D274">
+        <v>25.193000000000001</v>
+      </c>
+      <c r="E274">
+        <v>80</v>
+      </c>
+      <c r="F274">
+        <v>2015.44</v>
+      </c>
+      <c r="H274" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>9</v>
+      </c>
+      <c r="B275" t="s">
+        <v>36</v>
+      </c>
+      <c r="C275" t="s">
+        <v>66</v>
+      </c>
+      <c r="D275">
+        <v>18.324999999999999</v>
+      </c>
+      <c r="E275">
+        <v>70</v>
+      </c>
+      <c r="F275">
+        <v>1282.75</v>
+      </c>
+      <c r="H275" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>9</v>
+      </c>
+      <c r="B276" t="s">
+        <v>37</v>
+      </c>
+      <c r="C276" t="s">
+        <v>65</v>
+      </c>
+      <c r="D276">
+        <v>24.106999999999999</v>
+      </c>
+      <c r="E276">
+        <v>70</v>
+      </c>
+      <c r="F276">
+        <v>1687.49</v>
+      </c>
+      <c r="H276" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>9</v>
+      </c>
+      <c r="B277" t="s">
+        <v>38</v>
+      </c>
+      <c r="C277" t="s">
+        <v>67</v>
+      </c>
+      <c r="D277">
+        <v>13.993</v>
+      </c>
+      <c r="E277">
+        <v>86.999928535696426</v>
+      </c>
+      <c r="F277">
+        <v>1217.3900000000001</v>
+      </c>
+      <c r="G277" t="s">
+        <v>76</v>
+      </c>
+      <c r="H277" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>9</v>
+      </c>
+      <c r="B278" t="s">
+        <v>39</v>
+      </c>
+      <c r="C278" t="s">
+        <v>66</v>
+      </c>
+      <c r="D278">
+        <v>23.161999999999999</v>
+      </c>
+      <c r="E278">
+        <v>80</v>
+      </c>
+      <c r="F278">
+        <v>1852.96</v>
+      </c>
+      <c r="G278" t="s">
+        <v>75</v>
+      </c>
+      <c r="H278" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>9</v>
+      </c>
+      <c r="B279" t="s">
+        <v>40</v>
+      </c>
+      <c r="C279" t="s">
+        <v>66</v>
+      </c>
+      <c r="D279">
+        <v>8.9039999999999999</v>
+      </c>
+      <c r="E279">
+        <v>100</v>
+      </c>
+      <c r="F279">
+        <v>890.4</v>
+      </c>
+      <c r="H279" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>9</v>
+      </c>
+      <c r="B280" t="s">
+        <v>41</v>
+      </c>
+      <c r="C280" t="s">
+        <v>66</v>
+      </c>
+      <c r="D280">
+        <v>21.858000000000001</v>
+      </c>
+      <c r="E280">
+        <v>70</v>
+      </c>
+      <c r="F280">
+        <v>1530.06</v>
+      </c>
+      <c r="G280" t="s">
+        <v>74</v>
+      </c>
+      <c r="H280" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>9</v>
+      </c>
+      <c r="B281" t="s">
+        <v>42</v>
+      </c>
+      <c r="C281" t="s">
+        <v>67</v>
+      </c>
+      <c r="D281">
+        <v>25.047000000000001</v>
+      </c>
+      <c r="E281">
+        <v>90</v>
+      </c>
+      <c r="F281">
+        <v>2254.23</v>
+      </c>
+      <c r="H281" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>9</v>
+      </c>
+      <c r="B282" t="s">
+        <v>43</v>
+      </c>
+      <c r="C282" t="s">
+        <v>67</v>
+      </c>
+      <c r="D282">
+        <v>21.138000000000002</v>
+      </c>
+      <c r="E282">
+        <v>85</v>
+      </c>
+      <c r="F282">
+        <v>1796.73</v>
+      </c>
+      <c r="H282" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>9</v>
+      </c>
+      <c r="B283" t="s">
+        <v>44</v>
+      </c>
+      <c r="C283" t="s">
+        <v>65</v>
+      </c>
+      <c r="D283">
+        <v>24.542999999999999</v>
+      </c>
+      <c r="E283">
+        <v>80</v>
+      </c>
+      <c r="F283">
+        <v>1963.44</v>
+      </c>
+      <c r="H283" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>9</v>
+      </c>
+      <c r="B284" t="s">
+        <v>45</v>
+      </c>
+      <c r="C284" t="s">
+        <v>68</v>
+      </c>
+      <c r="D284">
+        <v>12.577999999999999</v>
+      </c>
+      <c r="E284">
+        <v>90.160304737719215</v>
+      </c>
+      <c r="F284">
+        <v>1136.1099999999999</v>
+      </c>
+      <c r="G284" t="s">
+        <v>75</v>
+      </c>
+      <c r="H284" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>9</v>
+      </c>
+      <c r="B285" t="s">
+        <v>46</v>
+      </c>
+      <c r="C285" t="s">
+        <v>66</v>
+      </c>
+      <c r="D285">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="E285">
+        <v>70</v>
+      </c>
+      <c r="F285">
+        <v>684.6</v>
+      </c>
+      <c r="G285" t="s">
+        <v>77</v>
+      </c>
+      <c r="H285" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>9</v>
+      </c>
+      <c r="B286" t="s">
+        <v>47</v>
+      </c>
+      <c r="C286" t="s">
+        <v>65</v>
+      </c>
+      <c r="D286">
+        <v>11.125</v>
+      </c>
+      <c r="E286">
+        <v>79.900224719101118</v>
+      </c>
+      <c r="F286">
+        <v>888.89</v>
+      </c>
+      <c r="G286" t="s">
+        <v>77</v>
+      </c>
+      <c r="H286" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>9</v>
+      </c>
+      <c r="B287" t="s">
+        <v>48</v>
+      </c>
+      <c r="C287" t="s">
+        <v>65</v>
+      </c>
+      <c r="D287">
+        <v>10.439</v>
+      </c>
+      <c r="E287">
+        <v>100</v>
+      </c>
+      <c r="F287">
+        <v>1043.9000000000001</v>
+      </c>
+      <c r="H287" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>9</v>
+      </c>
+      <c r="B288" t="s">
+        <v>49</v>
+      </c>
+      <c r="C288" t="s">
+        <v>65</v>
+      </c>
+      <c r="D288">
+        <v>7.1740000000000004</v>
+      </c>
+      <c r="E288">
+        <v>99.999999999999986</v>
+      </c>
+      <c r="F288">
+        <v>717.4</v>
+      </c>
+      <c r="H288" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>9</v>
+      </c>
+      <c r="B289" t="s">
+        <v>50</v>
+      </c>
+      <c r="C289" t="s">
+        <v>66</v>
+      </c>
+      <c r="D289">
+        <v>8.7379999999999995</v>
+      </c>
+      <c r="E289">
+        <v>50</v>
+      </c>
+      <c r="F289">
+        <v>436.9</v>
+      </c>
+      <c r="G289" t="s">
+        <v>76</v>
+      </c>
+      <c r="H289" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>9</v>
+      </c>
+      <c r="B290" t="s">
+        <v>51</v>
+      </c>
+      <c r="C290" t="s">
+        <v>67</v>
+      </c>
+      <c r="D290">
+        <v>13.321</v>
+      </c>
+      <c r="E290">
+        <v>60</v>
+      </c>
+      <c r="F290">
+        <v>799.26</v>
+      </c>
+      <c r="H290" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>9</v>
+      </c>
+      <c r="B291" t="s">
+        <v>52</v>
+      </c>
+      <c r="C291" t="s">
+        <v>66</v>
+      </c>
+      <c r="D291">
+        <v>13.906000000000001</v>
+      </c>
+      <c r="E291">
+        <v>30</v>
+      </c>
+      <c r="F291">
+        <v>417.18</v>
+      </c>
+      <c r="G291" t="s">
+        <v>78</v>
+      </c>
+      <c r="H291" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>9</v>
+      </c>
+      <c r="B292" t="s">
+        <v>53</v>
+      </c>
+      <c r="C292" t="s">
+        <v>67</v>
+      </c>
+      <c r="D292">
+        <v>2.4460000000000002</v>
+      </c>
+      <c r="E292">
+        <v>40</v>
+      </c>
+      <c r="F292">
+        <v>97.84</v>
+      </c>
+      <c r="G292" t="s">
+        <v>75</v>
+      </c>
+      <c r="H292" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>9</v>
+      </c>
+      <c r="B293" t="s">
+        <v>54</v>
+      </c>
+      <c r="C293" t="s">
+        <v>67</v>
+      </c>
+      <c r="D293">
+        <v>8.907</v>
+      </c>
+      <c r="E293">
+        <v>25.00056135623667</v>
+      </c>
+      <c r="F293">
+        <v>222.68</v>
+      </c>
+      <c r="G293" t="s">
+        <v>78</v>
+      </c>
+      <c r="H293" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>9</v>
+      </c>
+      <c r="B294" t="s">
+        <v>55</v>
+      </c>
+      <c r="C294" t="s">
+        <v>67</v>
+      </c>
+      <c r="D294">
+        <v>7.4450000000000003</v>
+      </c>
+      <c r="E294">
+        <v>35.000671591672258</v>
+      </c>
+      <c r="F294">
+        <v>260.58</v>
+      </c>
+      <c r="H294" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>9</v>
+      </c>
+      <c r="B295" t="s">
+        <v>56</v>
+      </c>
+      <c r="C295" t="s">
+        <v>67</v>
+      </c>
+      <c r="D295">
+        <v>1.27</v>
+      </c>
+      <c r="E295">
+        <v>35</v>
+      </c>
+      <c r="F295">
+        <v>83.69</v>
+      </c>
+      <c r="G295" t="s">
+        <v>79</v>
+      </c>
+      <c r="H295" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>9</v>
+      </c>
+      <c r="B296" t="s">
+        <v>57</v>
+      </c>
+      <c r="C296" t="s">
+        <v>67</v>
+      </c>
+      <c r="D296">
+        <v>2.8849999999999998</v>
+      </c>
+      <c r="E296">
+        <v>45.001733102253041</v>
+      </c>
+      <c r="F296">
+        <v>129.83000000000001</v>
+      </c>
+      <c r="H296" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>9</v>
+      </c>
+      <c r="B297" t="s">
+        <v>59</v>
+      </c>
+      <c r="C297" t="s">
+        <v>67</v>
+      </c>
+      <c r="D297">
+        <v>19.189</v>
+      </c>
+      <c r="E297">
+        <v>25</v>
+      </c>
+      <c r="F297">
+        <v>473.95</v>
+      </c>
+      <c r="H297" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>9</v>
+      </c>
+      <c r="B298" t="s">
+        <v>60</v>
+      </c>
+      <c r="C298" t="s">
+        <v>67</v>
+      </c>
+      <c r="D298">
+        <v>1.9119999999999999</v>
+      </c>
+      <c r="E298">
+        <v>25</v>
+      </c>
+      <c r="F298">
+        <v>47.8</v>
+      </c>
+      <c r="H298" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>9</v>
+      </c>
+      <c r="B299" t="s">
+        <v>61</v>
+      </c>
+      <c r="C299" t="s">
+        <v>64</v>
+      </c>
+      <c r="D299">
+        <v>3.9249999999999998</v>
+      </c>
+      <c r="E299">
+        <v>55.001273885350322</v>
+      </c>
+      <c r="F299">
+        <v>215.88</v>
+      </c>
+      <c r="H299" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>9</v>
+      </c>
+      <c r="B300" t="s">
+        <v>63</v>
+      </c>
+      <c r="C300" t="s">
+        <v>64</v>
+      </c>
+      <c r="D300">
+        <v>3.069</v>
+      </c>
+      <c r="E300">
+        <v>55.001629195177593</v>
+      </c>
+      <c r="F300">
+        <v>168.8</v>
+      </c>
+      <c r="H300" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>10</v>
+      </c>
+      <c r="B301" t="s">
+        <v>12</v>
+      </c>
+      <c r="C301" t="s">
+        <v>64</v>
+      </c>
+      <c r="D301">
+        <v>19.686</v>
+      </c>
+      <c r="E301">
+        <v>119</v>
+      </c>
+      <c r="F301">
+        <v>2342.63</v>
+      </c>
+      <c r="G301" t="s">
+        <v>80</v>
+      </c>
+      <c r="H301" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>10</v>
+      </c>
+      <c r="B302" t="s">
+        <v>13</v>
+      </c>
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302">
+        <v>9.1349999999999998</v>
+      </c>
+      <c r="E302">
+        <v>98</v>
+      </c>
+      <c r="F302">
+        <v>895.23</v>
+      </c>
+      <c r="G302" t="s">
+        <v>81</v>
+      </c>
+      <c r="H302" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>10</v>
+      </c>
+      <c r="B303" t="s">
+        <v>14</v>
+      </c>
+      <c r="C303" t="s">
+        <v>66</v>
+      </c>
+      <c r="D303">
+        <v>11.3</v>
+      </c>
+      <c r="E303">
+        <v>105</v>
+      </c>
+      <c r="F303">
+        <v>1186.5</v>
+      </c>
+      <c r="G303" t="s">
+        <v>82</v>
+      </c>
+      <c r="H303" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>10</v>
+      </c>
+      <c r="B304" t="s">
+        <v>15</v>
+      </c>
+      <c r="C304" t="s">
+        <v>65</v>
+      </c>
+      <c r="D304">
+        <v>16.341999999999999</v>
+      </c>
+      <c r="E304">
+        <v>120</v>
+      </c>
+      <c r="F304">
+        <v>1961.04</v>
+      </c>
+      <c r="G304" t="s">
+        <v>83</v>
+      </c>
+      <c r="H304" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>10</v>
+      </c>
+      <c r="B305" t="s">
+        <v>16</v>
+      </c>
+      <c r="C305" t="s">
+        <v>65</v>
+      </c>
+      <c r="D305">
+        <v>17.327999999999999</v>
+      </c>
+      <c r="E305">
+        <v>105</v>
+      </c>
+      <c r="F305">
+        <v>1819.44</v>
+      </c>
+      <c r="G305" t="s">
+        <v>82</v>
+      </c>
+      <c r="H305" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>10</v>
+      </c>
+      <c r="B306" t="s">
+        <v>17</v>
+      </c>
+      <c r="C306" t="s">
+        <v>66</v>
+      </c>
+      <c r="D306">
+        <v>15.439</v>
+      </c>
+      <c r="E306">
+        <v>121</v>
+      </c>
+      <c r="F306">
+        <v>1868.12</v>
+      </c>
+      <c r="G306" t="s">
+        <v>84</v>
+      </c>
+      <c r="H306" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>10</v>
+      </c>
+      <c r="B307" t="s">
+        <v>18</v>
+      </c>
+      <c r="C307" t="s">
+        <v>68</v>
+      </c>
+      <c r="D307">
+        <v>18.895</v>
+      </c>
+      <c r="E307">
+        <v>110</v>
+      </c>
+      <c r="F307">
+        <v>2078.4499999999998</v>
+      </c>
+      <c r="G307" t="s">
+        <v>85</v>
+      </c>
+      <c r="H307" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>10</v>
+      </c>
+      <c r="B308" t="s">
+        <v>19</v>
+      </c>
+      <c r="C308" t="s">
+        <v>66</v>
+      </c>
+      <c r="D308">
+        <v>17.123999999999999</v>
+      </c>
+      <c r="E308">
+        <v>103</v>
+      </c>
+      <c r="F308">
+        <v>1763.77</v>
+      </c>
+      <c r="G308" t="s">
+        <v>86</v>
+      </c>
+      <c r="H308" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>10</v>
+      </c>
+      <c r="B309" t="s">
+        <v>20</v>
+      </c>
+      <c r="C309" t="s">
+        <v>65</v>
+      </c>
+      <c r="D309">
+        <v>31.706</v>
+      </c>
+      <c r="E309">
+        <v>100</v>
+      </c>
+      <c r="F309">
+        <v>3170.6</v>
+      </c>
+      <c r="G309" t="s">
+        <v>87</v>
+      </c>
+      <c r="H309" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>10</v>
+      </c>
+      <c r="B310" t="s">
+        <v>21</v>
+      </c>
+      <c r="C310" t="s">
+        <v>64</v>
+      </c>
+      <c r="D310">
+        <v>21.465</v>
+      </c>
+      <c r="E310">
+        <v>93</v>
+      </c>
+      <c r="F310">
+        <v>1996.25</v>
+      </c>
+      <c r="G310" t="s">
+        <v>88</v>
+      </c>
+      <c r="H310" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>10</v>
+      </c>
+      <c r="B311" t="s">
+        <v>22</v>
+      </c>
+      <c r="C311" t="s">
+        <v>69</v>
+      </c>
+      <c r="D311">
+        <v>42.033000000000001</v>
+      </c>
+      <c r="E311">
+        <v>110</v>
+      </c>
+      <c r="F311">
+        <v>4623.63</v>
+      </c>
+      <c r="G311" t="s">
+        <v>89</v>
+      </c>
+      <c r="H311" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>10</v>
+      </c>
+      <c r="B312" t="s">
+        <v>24</v>
+      </c>
+      <c r="C312" t="s">
+        <v>66</v>
+      </c>
+      <c r="D312">
+        <v>33.844000000000001</v>
+      </c>
+      <c r="E312">
+        <v>130</v>
+      </c>
+      <c r="F312">
+        <v>4399.72</v>
+      </c>
+      <c r="G312" t="s">
+        <v>90</v>
+      </c>
+      <c r="H312" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
         <v>11</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B313" t="s">
+        <v>25</v>
+      </c>
+      <c r="C313" t="s">
+        <v>66</v>
+      </c>
+      <c r="D313">
+        <v>14.504</v>
+      </c>
+      <c r="E313">
+        <v>96</v>
+      </c>
+      <c r="F313">
+        <v>1392.38</v>
+      </c>
+      <c r="G313" t="s">
+        <v>82</v>
+      </c>
+      <c r="H313" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>11</v>
+      </c>
+      <c r="B314" t="s">
+        <v>26</v>
+      </c>
+      <c r="C314" t="s">
+        <v>65</v>
+      </c>
+      <c r="D314">
+        <v>25.122</v>
+      </c>
+      <c r="E314">
+        <v>85</v>
+      </c>
+      <c r="F314">
+        <v>2135.37</v>
+      </c>
+      <c r="H314" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>11</v>
+      </c>
+      <c r="B315" t="s">
+        <v>27</v>
+      </c>
+      <c r="C315" t="s">
+        <v>68</v>
+      </c>
+      <c r="D315">
+        <v>4.1950000000000003</v>
+      </c>
+      <c r="E315">
+        <v>125</v>
+      </c>
+      <c r="F315">
+        <v>524.38</v>
+      </c>
+      <c r="G315" t="s">
+        <v>91</v>
+      </c>
+      <c r="H315" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>11</v>
+      </c>
+      <c r="B316" t="s">
+        <v>28</v>
+      </c>
+      <c r="C316" t="s">
+        <v>67</v>
+      </c>
+      <c r="D316">
+        <v>16.079000000000001</v>
+      </c>
+      <c r="E316">
+        <v>61</v>
+      </c>
+      <c r="F316">
+        <v>980.82</v>
+      </c>
+      <c r="G316" t="s">
+        <v>92</v>
+      </c>
+      <c r="H316" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>11</v>
+      </c>
+      <c r="B317" t="s">
+        <v>29</v>
+      </c>
+      <c r="C317" t="s">
+        <v>66</v>
+      </c>
+      <c r="D317">
+        <v>14.065</v>
+      </c>
+      <c r="E317">
+        <v>98</v>
+      </c>
+      <c r="F317">
+        <v>1378.37</v>
+      </c>
+      <c r="G317" t="s">
+        <v>93</v>
+      </c>
+      <c r="H317" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>11</v>
+      </c>
+      <c r="B318" t="s">
+        <v>30</v>
+      </c>
+      <c r="C318" t="s">
+        <v>66</v>
+      </c>
+      <c r="D318">
+        <v>16.888999999999999</v>
+      </c>
+      <c r="E318">
+        <v>46</v>
+      </c>
+      <c r="F318">
+        <v>776.89</v>
+      </c>
+      <c r="G318" t="s">
+        <v>94</v>
+      </c>
+      <c r="H318" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>11</v>
+      </c>
+      <c r="B319" t="s">
+        <v>31</v>
+      </c>
+      <c r="C319" t="s">
+        <v>66</v>
+      </c>
+      <c r="D319">
+        <v>22.911999999999999</v>
+      </c>
+      <c r="E319">
+        <v>110</v>
+      </c>
+      <c r="F319">
+        <v>2520.3200000000002</v>
+      </c>
+      <c r="G319" t="s">
+        <v>95</v>
+      </c>
+      <c r="H319" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>11</v>
+      </c>
+      <c r="B320" t="s">
+        <v>32</v>
+      </c>
+      <c r="C320" t="s">
+        <v>66</v>
+      </c>
+      <c r="D320">
+        <v>18.552</v>
+      </c>
+      <c r="E320">
+        <v>73</v>
+      </c>
+      <c r="F320">
+        <v>1354.3</v>
+      </c>
+      <c r="H320" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>11</v>
+      </c>
+      <c r="B321" t="s">
+        <v>33</v>
+      </c>
+      <c r="C321" t="s">
+        <v>67</v>
+      </c>
+      <c r="D321">
+        <v>24.803999999999998</v>
+      </c>
+      <c r="E321">
+        <v>83</v>
+      </c>
+      <c r="F321">
+        <v>2058.73</v>
+      </c>
+      <c r="H321" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>11</v>
+      </c>
+      <c r="B322" t="s">
+        <v>34</v>
+      </c>
+      <c r="C322" t="s">
+        <v>66</v>
+      </c>
+      <c r="D322">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E322">
+        <v>55</v>
+      </c>
+      <c r="F322">
+        <v>1053.25</v>
+      </c>
+      <c r="H322" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>11</v>
+      </c>
+      <c r="B323" t="s">
+        <v>35</v>
+      </c>
+      <c r="C323" t="s">
+        <v>64</v>
+      </c>
+      <c r="D323">
+        <v>25.193000000000001</v>
+      </c>
+      <c r="E323">
+        <v>80</v>
+      </c>
+      <c r="F323">
+        <v>2015.44</v>
+      </c>
+      <c r="H323" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>11</v>
+      </c>
+      <c r="B324" t="s">
+        <v>36</v>
+      </c>
+      <c r="C324" t="s">
+        <v>66</v>
+      </c>
+      <c r="D324">
+        <v>18.324999999999999</v>
+      </c>
+      <c r="E324">
+        <v>90</v>
+      </c>
+      <c r="F324">
+        <v>1649.25</v>
+      </c>
+      <c r="H324" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>11</v>
+      </c>
+      <c r="B325" t="s">
+        <v>37</v>
+      </c>
+      <c r="C325" t="s">
+        <v>65</v>
+      </c>
+      <c r="D325">
+        <v>24.106999999999999</v>
+      </c>
+      <c r="E325">
+        <v>65</v>
+      </c>
+      <c r="F325">
+        <v>1566.95</v>
+      </c>
+      <c r="G325" t="s">
+        <v>96</v>
+      </c>
+      <c r="H325" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>11</v>
+      </c>
+      <c r="B326" t="s">
+        <v>38</v>
+      </c>
+      <c r="C326" t="s">
+        <v>65</v>
+      </c>
+      <c r="D326">
+        <v>13.993</v>
+      </c>
+      <c r="E326">
+        <v>95</v>
+      </c>
+      <c r="F326">
+        <v>1329.34</v>
+      </c>
+      <c r="G326" t="s">
+        <v>97</v>
+      </c>
+      <c r="H326" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>11</v>
+      </c>
+      <c r="B327" t="s">
+        <v>39</v>
+      </c>
+      <c r="C327" t="s">
+        <v>66</v>
+      </c>
+      <c r="D327">
+        <v>23.161999999999999</v>
+      </c>
+      <c r="E327">
+        <v>65</v>
+      </c>
+      <c r="F327">
+        <v>1505.53</v>
+      </c>
+      <c r="G327" t="s">
+        <v>98</v>
+      </c>
+      <c r="H327" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>11</v>
+      </c>
+      <c r="B328" t="s">
+        <v>40</v>
+      </c>
+      <c r="C328" t="s">
+        <v>66</v>
+      </c>
+      <c r="D328">
+        <v>8.9039999999999999</v>
+      </c>
+      <c r="E328">
+        <v>106</v>
+      </c>
+      <c r="F328">
+        <v>943.82</v>
+      </c>
+      <c r="G328" t="s">
+        <v>99</v>
+      </c>
+      <c r="H328" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>11</v>
+      </c>
+      <c r="B329" t="s">
+        <v>41</v>
+      </c>
+      <c r="C329" t="s">
+        <v>66</v>
+      </c>
+      <c r="D329">
+        <v>21.858000000000001</v>
+      </c>
+      <c r="E329">
+        <v>75</v>
+      </c>
+      <c r="F329">
+        <v>1639.35</v>
+      </c>
+      <c r="H329" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>11</v>
+      </c>
+      <c r="B330" t="s">
+        <v>42</v>
+      </c>
+      <c r="C330" t="s">
+        <v>67</v>
+      </c>
+      <c r="D330">
+        <v>25.047000000000001</v>
+      </c>
+      <c r="E330">
+        <v>97</v>
+      </c>
+      <c r="F330">
+        <v>2429.56</v>
+      </c>
+      <c r="H330" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>11</v>
+      </c>
+      <c r="B331" t="s">
+        <v>43</v>
+      </c>
+      <c r="C331" t="s">
+        <v>67</v>
+      </c>
+      <c r="D331">
+        <v>21.138000000000002</v>
+      </c>
+      <c r="E331">
+        <v>92</v>
+      </c>
+      <c r="F331">
+        <v>1944.7</v>
+      </c>
+      <c r="G331" t="s">
+        <v>100</v>
+      </c>
+      <c r="H331" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>11</v>
+      </c>
+      <c r="B332" t="s">
+        <v>44</v>
+      </c>
+      <c r="C332" t="s">
+        <v>65</v>
+      </c>
+      <c r="D332">
+        <v>24.542999999999999</v>
+      </c>
+      <c r="E332">
+        <v>95</v>
+      </c>
+      <c r="F332">
+        <v>2331.59</v>
+      </c>
+      <c r="H332" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>11</v>
+      </c>
+      <c r="B333" t="s">
+        <v>45</v>
+      </c>
+      <c r="C333" t="s">
+        <v>68</v>
+      </c>
+      <c r="D333">
+        <v>12.601000000000001</v>
+      </c>
+      <c r="E333">
+        <v>105</v>
+      </c>
+      <c r="F333">
+        <v>1323.11</v>
+      </c>
+      <c r="H333" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>11</v>
+      </c>
+      <c r="B334" t="s">
+        <v>46</v>
+      </c>
+      <c r="C334" t="s">
+        <v>66</v>
+      </c>
+      <c r="D334">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="E334">
+        <v>95</v>
+      </c>
+      <c r="F334">
+        <v>929.1</v>
+      </c>
+      <c r="G334" t="s">
+        <v>82</v>
+      </c>
+      <c r="H334" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>11</v>
+      </c>
+      <c r="B335" t="s">
+        <v>47</v>
+      </c>
+      <c r="C335" t="s">
+        <v>65</v>
+      </c>
+      <c r="D335">
+        <v>11.125</v>
+      </c>
+      <c r="E335">
+        <v>95</v>
+      </c>
+      <c r="F335">
+        <v>1056.8800000000001</v>
+      </c>
+      <c r="H335" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>11</v>
+      </c>
+      <c r="B336" t="s">
+        <v>48</v>
+      </c>
+      <c r="C336" t="s">
+        <v>65</v>
+      </c>
+      <c r="D336">
+        <v>10.439</v>
+      </c>
+      <c r="E336">
+        <v>115</v>
+      </c>
+      <c r="F336">
+        <v>1200.49</v>
+      </c>
+      <c r="H336" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>11</v>
+      </c>
+      <c r="B337" t="s">
+        <v>49</v>
+      </c>
+      <c r="C337" t="s">
+        <v>65</v>
+      </c>
+      <c r="D337">
+        <v>7.1740000000000004</v>
+      </c>
+      <c r="E337">
+        <v>115</v>
+      </c>
+      <c r="F337">
+        <v>825.01</v>
+      </c>
+      <c r="H337" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>11</v>
+      </c>
+      <c r="B338" t="s">
         <v>50</v>
       </c>
-      <c r="C141" t="s">
-        <v>66</v>
-      </c>
-      <c r="D141">
+      <c r="C338" t="s">
+        <v>66</v>
+      </c>
+      <c r="D338">
         <v>8.7379999999999995</v>
       </c>
-      <c r="E141">
+      <c r="E338">
         <v>60</v>
       </c>
-      <c r="F141">
+      <c r="F338">
         <v>524.28</v>
       </c>
-      <c r="G141" t="s">
+      <c r="G338" t="s">
         <v>82</v>
       </c>
-      <c r="H141" t="s">
+      <c r="H338" t="s">
         <v>103</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:H338">
+    <sortCondition ref="H2"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -4212,7 +4212,7 @@
         <v>13</v>
       </c>
       <c r="C151" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D151">
         <v>9.1349999999999998</v>
@@ -4281,7 +4281,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="D154">
         <v>16.827999999999999</v>
@@ -4304,7 +4304,7 @@
         <v>17</v>
       </c>
       <c r="C155" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="D155">
         <v>15.696999999999999</v>
@@ -4327,7 +4327,7 @@
         <v>18</v>
       </c>
       <c r="C156" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D156">
         <v>18.895</v>
@@ -4373,7 +4373,7 @@
         <v>20</v>
       </c>
       <c r="C158" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D158">
         <v>31.706</v>
@@ -4396,7 +4396,7 @@
         <v>21</v>
       </c>
       <c r="C159" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D159">
         <v>21.88</v>
@@ -4465,7 +4465,7 @@
         <v>24</v>
       </c>
       <c r="C162" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D162">
         <v>34.652000000000001</v>
@@ -4534,7 +4534,7 @@
         <v>27</v>
       </c>
       <c r="C165" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="D165">
         <v>4.1950000000000003</v>
@@ -4557,7 +4557,7 @@
         <v>28</v>
       </c>
       <c r="C166" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D166">
         <v>16.079000000000001</v>
@@ -4580,7 +4580,7 @@
         <v>30</v>
       </c>
       <c r="C167" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D167">
         <v>16.888999999999999</v>
@@ -4626,7 +4626,7 @@
         <v>32</v>
       </c>
       <c r="C169" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D169">
         <v>18.552</v>
@@ -4695,7 +4695,7 @@
         <v>35</v>
       </c>
       <c r="C172" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D172">
         <v>25.193000000000001</v>
@@ -4718,7 +4718,7 @@
         <v>36</v>
       </c>
       <c r="C173" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D173">
         <v>18.324999999999999</v>
@@ -4810,7 +4810,7 @@
         <v>40</v>
       </c>
       <c r="C177" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D177">
         <v>8.9039999999999999</v>
@@ -4833,7 +4833,7 @@
         <v>41</v>
       </c>
       <c r="C178" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D178">
         <v>21.858000000000001</v>
@@ -4948,7 +4948,7 @@
         <v>46</v>
       </c>
       <c r="C183" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D183">
         <v>9.7799999999999994</v>
@@ -5155,7 +5155,7 @@
         <v>55</v>
       </c>
       <c r="C192" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D192">
         <v>7.4450000000000003</v>
@@ -5201,7 +5201,7 @@
         <v>57</v>
       </c>
       <c r="C194" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D194">
         <v>1.548</v>
@@ -5224,7 +5224,7 @@
         <v>59</v>
       </c>
       <c r="C195" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D195">
         <v>11.738</v>
@@ -5247,7 +5247,7 @@
         <v>60</v>
       </c>
       <c r="C196" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D196">
         <v>5.2720000000000002</v>
@@ -5270,7 +5270,7 @@
         <v>61</v>
       </c>
       <c r="C197" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D197">
         <v>3.9249999999999998</v>
@@ -5293,7 +5293,7 @@
         <v>63</v>
       </c>
       <c r="C198" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D198">
         <v>3.07</v>
